--- a/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{93E32453-6AF3-4421-8F1C-B60B5F625A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{61A75C8A-ED05-43FE-8EED-46AD54C89BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1498,18 +1498,18 @@
     <t>onshore wind resource -- CF class won-JPN_33 -- cost class 1</t>
   </si>
   <si>
+    <t>e_won-JPN_33_c5</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-JPN_33 -- cost class 5</t>
+  </si>
+  <si>
     <t>e_won-JPN_33_c4</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-JPN_33 -- cost class 4</t>
   </si>
   <si>
-    <t>e_won-JPN_33_c5</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-JPN_33 -- cost class 5</t>
-  </si>
-  <si>
     <t>e_won-JPN_32_c3</t>
   </si>
   <si>
@@ -1540,18 +1540,18 @@
     <t>onshore wind resource -- CF class won-JPN_32 -- cost class 5</t>
   </si>
   <si>
+    <t>e_won-JPN_31_c4</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-JPN_31 -- cost class 4</t>
+  </si>
+  <si>
     <t>e_won-JPN_31_c2</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-JPN_31 -- cost class 2</t>
   </si>
   <si>
-    <t>e_won-JPN_31_c4</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-JPN_31 -- cost class 4</t>
-  </si>
-  <si>
     <t>e_won-JPN_31_c3</t>
   </si>
   <si>
@@ -1732,18 +1732,18 @@
     <t>onshore wind resource -- CF class won-JPN_24 -- cost class 5</t>
   </si>
   <si>
+    <t>e_won-JPN_24_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-JPN_24 -- cost class 1</t>
+  </si>
+  <si>
     <t>e_won-JPN_24_c3</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-JPN_24 -- cost class 3</t>
   </si>
   <si>
-    <t>e_won-JPN_24_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-JPN_24 -- cost class 1</t>
-  </si>
-  <si>
     <t>e_won-JPN_24_c4</t>
   </si>
   <si>
@@ -1870,16 +1870,16 @@
     <t>onshore wind resource -- CF class won-JPN_19 -- cost class 3</t>
   </si>
   <si>
+    <t>e_won-JPN_19_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-JPN_19 -- cost class 1</t>
+  </si>
+  <si>
     <t>e_won-JPN_19_c5</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-JPN_19 -- cost class 5</t>
-  </si>
-  <si>
-    <t>e_won-JPN_19_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-JPN_19 -- cost class 1</t>
   </si>
   <si>
     <t>e_won-JPN_19_c4</t>
@@ -8510,7 +8510,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEF2029D-B851-4EA7-B1DC-A3E4CD2B9C63}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01A3603-82E8-4CCB-9837-5DC06401E1AD}">
   <dimension ref="B9:N39"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8589,7 +8589,7 @@
         <v>247</v>
       </c>
       <c r="L11">
-        <v>3.0000000000000001E-3</v>
+        <v>1.0371523245305755E-3</v>
       </c>
       <c r="M11">
         <v>0.2075327378694439</v>
@@ -8627,10 +8627,10 @@
         <v>247</v>
       </c>
       <c r="L12">
-        <v>1.353</v>
+        <v>0.65649015768319074</v>
       </c>
       <c r="M12">
-        <v>0.20713654874866597</v>
+        <v>0.20713654874866602</v>
       </c>
       <c r="N12">
         <v>4</v>
@@ -8665,10 +8665,10 @@
         <v>247</v>
       </c>
       <c r="L13">
-        <v>0.35549999999999998</v>
+        <v>0.21366312079413041</v>
       </c>
       <c r="M13">
-        <v>0.20701828524869773</v>
+        <v>0.20712024183059863</v>
       </c>
       <c r="N13">
         <v>1</v>
@@ -8703,10 +8703,10 @@
         <v>247</v>
       </c>
       <c r="L14">
-        <v>3.2955000000000001</v>
+        <v>1.6963965905775908</v>
       </c>
       <c r="M14">
-        <v>0.20563841338490702</v>
+        <v>0.20567669420839058</v>
       </c>
       <c r="N14">
         <v>2</v>
@@ -8741,7 +8741,7 @@
         <v>247</v>
       </c>
       <c r="L15">
-        <v>0.21525</v>
+        <v>9.7121254953764863E-2</v>
       </c>
       <c r="M15">
         <v>0.2050578284580391</v>
@@ -8779,10 +8779,10 @@
         <v>247</v>
       </c>
       <c r="L16">
-        <v>7.7054999999999998</v>
+        <v>4.2915127571032521</v>
       </c>
       <c r="M16">
-        <v>0.20259461510290533</v>
+        <v>0.20255502580650991</v>
       </c>
       <c r="N16">
         <v>1</v>
@@ -8817,10 +8817,10 @@
         <v>247</v>
       </c>
       <c r="L17">
-        <v>7.5427499999999998</v>
+        <v>4.2106353170092579</v>
       </c>
       <c r="M17">
-        <v>0.20109182165819883</v>
+        <v>0.20107573554270222</v>
       </c>
       <c r="N17">
         <v>2</v>
@@ -8855,10 +8855,10 @@
         <v>247</v>
       </c>
       <c r="L18">
-        <v>10.1835</v>
+        <v>5.8105381027636351</v>
       </c>
       <c r="M18">
-        <v>0.19800682125715702</v>
+        <v>0.19798985691597665</v>
       </c>
       <c r="N18">
         <v>3</v>
@@ -8893,10 +8893,10 @@
         <v>247</v>
       </c>
       <c r="L19">
-        <v>5.5747499999999999</v>
+        <v>3.1617205318018282</v>
       </c>
       <c r="M19">
-        <v>0.1972158580893994</v>
+        <v>0.1971849678557715</v>
       </c>
       <c r="N19">
         <v>4</v>
@@ -8931,10 +8931,10 @@
         <v>247</v>
       </c>
       <c r="L20">
-        <v>5.4262499999999996</v>
+        <v>2.822722424935316</v>
       </c>
       <c r="M20">
-        <v>0.19706749981404917</v>
+        <v>0.19703116612340871</v>
       </c>
       <c r="N20">
         <v>5</v>
@@ -8969,10 +8969,10 @@
         <v>247</v>
       </c>
       <c r="L21">
-        <v>14.555999999999999</v>
+        <v>7.7076377565748819</v>
       </c>
       <c r="M21">
-        <v>0.18968431687229093</v>
+        <v>0.18978107650126499</v>
       </c>
       <c r="N21">
         <v>3</v>
@@ -9007,10 +9007,10 @@
         <v>247</v>
       </c>
       <c r="L22">
-        <v>26.006250000000001</v>
+        <v>13.647951600950009</v>
       </c>
       <c r="M22">
-        <v>0.18952664513807291</v>
+        <v>0.18965938200143581</v>
       </c>
       <c r="N22">
         <v>2</v>
@@ -9045,10 +9045,10 @@
         <v>247</v>
       </c>
       <c r="L23">
-        <v>38.857500000000002</v>
+        <v>21.725398888832906</v>
       </c>
       <c r="M23">
-        <v>0.18840851432021433</v>
+        <v>0.18821064383519293</v>
       </c>
       <c r="N23">
         <v>1</v>
@@ -9083,10 +9083,10 @@
         <v>247</v>
       </c>
       <c r="L24">
-        <v>11.34525</v>
+        <v>5.7973554697050744</v>
       </c>
       <c r="M24">
-        <v>0.18798492578630627</v>
+        <v>0.18804950640538118</v>
       </c>
       <c r="N24">
         <v>5</v>
@@ -9121,10 +9121,10 @@
         <v>247</v>
       </c>
       <c r="L25">
-        <v>10.41375</v>
+        <v>5.4629678944094833</v>
       </c>
       <c r="M25">
-        <v>0.18711996933443356</v>
+        <v>0.18713076676513343</v>
       </c>
       <c r="N25">
         <v>4</v>
@@ -9159,10 +9159,10 @@
         <v>247</v>
       </c>
       <c r="L26">
-        <v>19.518750000000001</v>
+        <v>9.7173451756906104</v>
       </c>
       <c r="M26">
-        <v>0.18073582419998083</v>
+        <v>0.18063454644504431</v>
       </c>
       <c r="N26">
         <v>2</v>
@@ -9197,10 +9197,10 @@
         <v>247</v>
       </c>
       <c r="L27">
-        <v>41.15475</v>
+        <v>22.046035212741312</v>
       </c>
       <c r="M27">
-        <v>0.18004581339474485</v>
+        <v>0.18010227619137506</v>
       </c>
       <c r="N27">
         <v>1</v>
@@ -9235,10 +9235,10 @@
         <v>247</v>
       </c>
       <c r="L28">
-        <v>17.891999999999999</v>
+        <v>8.5183815627027251</v>
       </c>
       <c r="M28">
-        <v>0.17983157225189428</v>
+        <v>0.17976688330242294</v>
       </c>
       <c r="N28">
         <v>3</v>
@@ -9273,10 +9273,10 @@
         <v>247</v>
       </c>
       <c r="L29">
-        <v>12.00375</v>
+        <v>5.3941874445102629</v>
       </c>
       <c r="M29">
-        <v>0.17940353939500725</v>
+        <v>0.17953359496552204</v>
       </c>
       <c r="N29">
         <v>4</v>
@@ -9311,10 +9311,10 @@
         <v>247</v>
       </c>
       <c r="L30">
-        <v>5.6812500000000004</v>
+        <v>2.5255138432215385</v>
       </c>
       <c r="M30">
-        <v>0.17844768756172844</v>
+        <v>0.17869374830970711</v>
       </c>
       <c r="N30">
         <v>5</v>
@@ -9349,10 +9349,10 @@
         <v>247</v>
       </c>
       <c r="L31">
-        <v>33.500250000000001</v>
+        <v>15.119522052011265</v>
       </c>
       <c r="M31">
-        <v>0.17256111201536695</v>
+        <v>0.17257764900941855</v>
       </c>
       <c r="N31">
         <v>1</v>
@@ -9387,10 +9387,10 @@
         <v>247</v>
       </c>
       <c r="L32">
-        <v>18.707249999999998</v>
+        <v>7.746165920142734</v>
       </c>
       <c r="M32">
-        <v>0.17102671420563892</v>
+        <v>0.17095024257417377</v>
       </c>
       <c r="N32">
         <v>3</v>
@@ -9425,10 +9425,10 @@
         <v>247</v>
       </c>
       <c r="L33">
-        <v>26.111249999999998</v>
+        <v>12.04045951409614</v>
       </c>
       <c r="M33">
-        <v>0.16932675338446704</v>
+        <v>0.16929768653575572</v>
       </c>
       <c r="N33">
         <v>2</v>
@@ -9463,10 +9463,10 @@
         <v>247</v>
       </c>
       <c r="L34">
-        <v>11.925750000000001</v>
+        <v>5.2829686285243866</v>
       </c>
       <c r="M34">
-        <v>0.168846568711498</v>
+        <v>0.1690727955762216</v>
       </c>
       <c r="N34">
         <v>4</v>
@@ -9501,10 +9501,10 @@
         <v>247</v>
       </c>
       <c r="L35">
-        <v>7.7077499999999999</v>
+        <v>3.3642832145192507</v>
       </c>
       <c r="M35">
-        <v>0.16853858197872873</v>
+        <v>0.16835607319637591</v>
       </c>
       <c r="N35">
         <v>5</v>
@@ -9539,7 +9539,7 @@
         <v>247</v>
       </c>
       <c r="L36">
-        <v>2.3392499999999998</v>
+        <v>1.0456822276283779</v>
       </c>
       <c r="M36">
         <v>0.16491451479212491</v>
@@ -9577,10 +9577,10 @@
         <v>247</v>
       </c>
       <c r="L37">
-        <v>1.827</v>
+        <v>0.82552886393659175</v>
       </c>
       <c r="M37">
-        <v>0.16455517260928823</v>
+        <v>0.1645551726092882</v>
       </c>
       <c r="N37">
         <v>1</v>
@@ -9615,7 +9615,7 @@
         <v>247</v>
       </c>
       <c r="L38">
-        <v>1.70025</v>
+        <v>0.74213406206392452</v>
       </c>
       <c r="M38">
         <v>0.16390950389206549</v>
@@ -9653,7 +9653,7 @@
         <v>247</v>
       </c>
       <c r="L39">
-        <v>0.89775000000000005</v>
+        <v>0.41945472703062586</v>
       </c>
       <c r="M39">
         <v>0.16366979706904469</v>
@@ -9668,7 +9668,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DD0573D-357A-41FB-AD79-593F1362E8D7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66469083-4509-472A-9E5C-51777F3BA1AD}">
   <dimension ref="B9:AB241"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9789,7 +9789,7 @@
         <v>710</v>
       </c>
       <c r="L11">
-        <v>0.11325</v>
+        <v>0.10961613792773224</v>
       </c>
       <c r="M11">
         <v>0.60943134336451088</v>
@@ -10011,7 +10011,7 @@
         <v>710</v>
       </c>
       <c r="L14">
-        <v>6.8250000000000005E-2</v>
+        <v>5.9024698639353411E-2</v>
       </c>
       <c r="M14">
         <v>0.58748294782093702</v>
@@ -10159,7 +10159,7 @@
         <v>710</v>
       </c>
       <c r="L16">
-        <v>8.9249999999999996E-2</v>
+        <v>8.568010246548606E-2</v>
       </c>
       <c r="M16">
         <v>0.57925651644848553</v>
@@ -10233,7 +10233,7 @@
         <v>710</v>
       </c>
       <c r="L17">
-        <v>1.6635</v>
+        <v>1.4457665016847654</v>
       </c>
       <c r="M17">
         <v>0.57765234546594191</v>
@@ -10307,7 +10307,7 @@
         <v>710</v>
       </c>
       <c r="L18">
-        <v>3.0750000000000002</v>
+        <v>2.8510316761465053</v>
       </c>
       <c r="M18">
         <v>0.57446893665389331</v>
@@ -10381,7 +10381,7 @@
         <v>710</v>
       </c>
       <c r="L19">
-        <v>1.2E-2</v>
+        <v>8.631867246657E-3</v>
       </c>
       <c r="M19">
         <v>0.55617481096337473</v>
@@ -10455,7 +10455,7 @@
         <v>710</v>
       </c>
       <c r="L20">
-        <v>0.63449999999999995</v>
+        <v>0.59443951986827503</v>
       </c>
       <c r="M20">
         <v>0.55122923896985854</v>
@@ -10529,7 +10529,7 @@
         <v>710</v>
       </c>
       <c r="L21">
-        <v>2.2499999999999998E-3</v>
+        <v>1.399952863539948E-3</v>
       </c>
       <c r="M21">
         <v>0.5508583489846447</v>
@@ -10603,7 +10603,7 @@
         <v>710</v>
       </c>
       <c r="L22">
-        <v>0.55200000000000005</v>
+        <v>0.53403699849091946</v>
       </c>
       <c r="M22">
         <v>0.54913697276959383</v>
@@ -10677,10 +10677,10 @@
         <v>710</v>
       </c>
       <c r="L23">
-        <v>4.4999999999999997E-3</v>
+        <v>3.6466097520932521E-3</v>
       </c>
       <c r="M23">
-        <v>0.54844891194147549</v>
+        <v>0.5481562126255598</v>
       </c>
       <c r="N23">
         <v>2</v>
@@ -10751,10 +10751,10 @@
         <v>710</v>
       </c>
       <c r="L24">
-        <v>9.6750000000000003E-2</v>
+        <v>9.5795605252893004E-2</v>
       </c>
       <c r="M24">
-        <v>0.54683847248785233</v>
+        <v>0.54683889639534444</v>
       </c>
       <c r="N24">
         <v>1</v>
@@ -10899,7 +10899,7 @@
         <v>710</v>
       </c>
       <c r="L26">
-        <v>0.29775000000000001</v>
+        <v>0.29512395089723703</v>
       </c>
       <c r="M26">
         <v>0.52676880725479447</v>
@@ -10973,10 +10973,10 @@
         <v>710</v>
       </c>
       <c r="L27">
-        <v>1.1955</v>
+        <v>1.0835865278388652</v>
       </c>
       <c r="M27">
-        <v>0.52196842707780799</v>
+        <v>0.52204391074263623</v>
       </c>
       <c r="N27">
         <v>4</v>
@@ -11047,10 +11047,10 @@
         <v>710</v>
       </c>
       <c r="L28">
-        <v>0.34050000000000002</v>
+        <v>0.26132985914414547</v>
       </c>
       <c r="M28">
-        <v>0.5184325056044754</v>
+        <v>0.51843069331938374</v>
       </c>
       <c r="N28">
         <v>3</v>
@@ -11121,10 +11121,10 @@
         <v>710</v>
       </c>
       <c r="L29">
-        <v>7.5749999999999998E-2</v>
+        <v>7.4826089121588932E-2</v>
       </c>
       <c r="M29">
-        <v>0.51802039853980375</v>
+        <v>0.51802373809858715</v>
       </c>
       <c r="N29">
         <v>2</v>
@@ -11195,10 +11195,10 @@
         <v>710</v>
       </c>
       <c r="L30">
-        <v>3.3000000000000002E-2</v>
+        <v>2.6022369126036119E-2</v>
       </c>
       <c r="M30">
-        <v>0.51722468700843838</v>
+        <v>0.51768204071839008</v>
       </c>
       <c r="N30">
         <v>1</v>
@@ -11269,7 +11269,7 @@
         <v>710</v>
       </c>
       <c r="L31">
-        <v>0.621</v>
+        <v>0.5178308912814702</v>
       </c>
       <c r="M31">
         <v>0.51666398673946423</v>
@@ -11343,10 +11343,10 @@
         <v>710</v>
       </c>
       <c r="L32">
-        <v>6.7500000000000004E-2</v>
+        <v>5.4158290860742669E-2</v>
       </c>
       <c r="M32">
-        <v>0.51430211012453042</v>
+        <v>0.51416291697889893</v>
       </c>
       <c r="N32">
         <v>1</v>
@@ -11565,7 +11565,7 @@
         <v>710</v>
       </c>
       <c r="L35">
-        <v>0.26100000000000001</v>
+        <v>0.19613342981186685</v>
       </c>
       <c r="M35">
         <v>0.50809503989368254</v>
@@ -11639,10 +11639,10 @@
         <v>710</v>
       </c>
       <c r="L36">
-        <v>0.33300000000000002</v>
+        <v>0.22376080183780719</v>
       </c>
       <c r="M36">
-        <v>0.50681955884310492</v>
+        <v>0.50687653797636378</v>
       </c>
       <c r="N36">
         <v>2</v>
@@ -11713,7 +11713,7 @@
         <v>710</v>
       </c>
       <c r="L37">
-        <v>0.69974999999999998</v>
+        <v>0.53138073109704009</v>
       </c>
       <c r="M37">
         <v>0.50308557555399336</v>
@@ -11861,7 +11861,7 @@
         <v>710</v>
       </c>
       <c r="L39">
-        <v>6.9750000000000006E-2</v>
+        <v>4.7514800476474092E-2</v>
       </c>
       <c r="M39">
         <v>0.50164954651910421</v>
@@ -11935,10 +11935,10 @@
         <v>710</v>
       </c>
       <c r="L40">
-        <v>0.88500000000000001</v>
+        <v>0.58261013658929472</v>
       </c>
       <c r="M40">
-        <v>0.49719926895538374</v>
+        <v>0.49721380310189695</v>
       </c>
       <c r="N40">
         <v>1</v>
@@ -12009,10 +12009,10 @@
         <v>710</v>
       </c>
       <c r="L41">
-        <v>1.51725</v>
+        <v>1.4103310412418713</v>
       </c>
       <c r="M41">
-        <v>0.49526117533795883</v>
+        <v>0.49526117533795888</v>
       </c>
       <c r="N41">
         <v>5</v>
@@ -12083,10 +12083,10 @@
         <v>710</v>
       </c>
       <c r="L42">
-        <v>3.4500000000000003E-2</v>
+        <v>3.1777158712621691E-2</v>
       </c>
       <c r="M42">
-        <v>0.49330029433104733</v>
+        <v>0.49333189635635893</v>
       </c>
       <c r="N42">
         <v>1</v>
@@ -12157,10 +12157,10 @@
         <v>710</v>
       </c>
       <c r="L43">
-        <v>0.14924999999999999</v>
+        <v>0.12154105680787904</v>
       </c>
       <c r="M43">
-        <v>0.49035288027653035</v>
+        <v>0.49029857789980918</v>
       </c>
       <c r="N43">
         <v>3</v>
@@ -12231,10 +12231,10 @@
         <v>710</v>
       </c>
       <c r="L44">
-        <v>1.68825</v>
+        <v>1.4769327651259936</v>
       </c>
       <c r="M44">
-        <v>0.49031326880937243</v>
+        <v>0.49029775972664247</v>
       </c>
       <c r="N44">
         <v>4</v>
@@ -12305,7 +12305,7 @@
         <v>710</v>
       </c>
       <c r="L45">
-        <v>0.52725</v>
+        <v>0.42992878047315958</v>
       </c>
       <c r="M45">
         <v>0.48888120851052902</v>
@@ -12379,10 +12379,10 @@
         <v>710</v>
       </c>
       <c r="L46">
-        <v>0.17100000000000001</v>
+        <v>0.15062217513649753</v>
       </c>
       <c r="M46">
-        <v>0.48690606271782633</v>
+        <v>0.48690611103338</v>
       </c>
       <c r="N46">
         <v>2</v>
@@ -12453,10 +12453,10 @@
         <v>710</v>
       </c>
       <c r="L47">
-        <v>0.12</v>
+        <v>0.10495781677073947</v>
       </c>
       <c r="M47">
-        <v>0.48294313676197392</v>
+        <v>0.4829831633515555</v>
       </c>
       <c r="N47">
         <v>2</v>
@@ -12527,10 +12527,10 @@
         <v>710</v>
       </c>
       <c r="L48">
-        <v>0.97875000000000001</v>
+        <v>0.82373844511118677</v>
       </c>
       <c r="M48">
-        <v>0.48055615796371581</v>
+        <v>0.48056005097918353</v>
       </c>
       <c r="N48">
         <v>3</v>
@@ -12601,10 +12601,10 @@
         <v>710</v>
       </c>
       <c r="L49">
-        <v>0.22275</v>
+        <v>0.18531537303337869</v>
       </c>
       <c r="M49">
-        <v>0.48023121509740502</v>
+        <v>0.48014397222581784</v>
       </c>
       <c r="N49">
         <v>1</v>
@@ -12675,10 +12675,10 @@
         <v>710</v>
       </c>
       <c r="L50">
-        <v>1.5907500000000001</v>
+        <v>1.2265045857333658</v>
       </c>
       <c r="M50">
-        <v>0.47689814499555988</v>
+        <v>0.47676858929142607</v>
       </c>
       <c r="N50">
         <v>4</v>
@@ -12749,10 +12749,10 @@
         <v>710</v>
       </c>
       <c r="L51">
-        <v>3.2047500000000002</v>
+        <v>2.4917989176147417</v>
       </c>
       <c r="M51">
-        <v>0.475051868911471</v>
+        <v>0.47505727558780575</v>
       </c>
       <c r="N51">
         <v>5</v>
@@ -12823,10 +12823,10 @@
         <v>710</v>
       </c>
       <c r="L52">
-        <v>0.12675</v>
+        <v>0.11466764859798757</v>
       </c>
       <c r="M52">
-        <v>0.4733830064775828</v>
+        <v>0.47340266072611176</v>
       </c>
       <c r="N52">
         <v>1</v>
@@ -12897,10 +12897,10 @@
         <v>710</v>
       </c>
       <c r="L53">
-        <v>0.63375000000000004</v>
+        <v>0.59454532033715324</v>
       </c>
       <c r="M53">
-        <v>0.47249589518279211</v>
+        <v>0.4725132069329504</v>
       </c>
       <c r="N53">
         <v>2</v>
@@ -12971,10 +12971,10 @@
         <v>710</v>
       </c>
       <c r="L54">
-        <v>1.72725</v>
+        <v>1.6848355888033599</v>
       </c>
       <c r="M54">
-        <v>0.4712515170041468</v>
+        <v>0.47124816167197181</v>
       </c>
       <c r="N54">
         <v>5</v>
@@ -13045,10 +13045,10 @@
         <v>710</v>
       </c>
       <c r="L55">
-        <v>4.8390000000000004</v>
+        <v>3.0995803708688152</v>
       </c>
       <c r="M55">
-        <v>0.46983856881495184</v>
+        <v>0.46989694109562857</v>
       </c>
       <c r="N55">
         <v>3</v>
@@ -13119,10 +13119,10 @@
         <v>710</v>
       </c>
       <c r="L56">
-        <v>1.8262499999999999</v>
+        <v>1.6004943831340317</v>
       </c>
       <c r="M56">
-        <v>0.46951462237253339</v>
+        <v>0.46952098409179838</v>
       </c>
       <c r="N56">
         <v>4</v>
@@ -13193,7 +13193,7 @@
         <v>710</v>
       </c>
       <c r="L57">
-        <v>0.30825000000000002</v>
+        <v>0.29461628629302539</v>
       </c>
       <c r="M57">
         <v>0.46482703081783788</v>
@@ -13267,7 +13267,7 @@
         <v>710</v>
       </c>
       <c r="L58">
-        <v>0.85350000000000004</v>
+        <v>0.8176387997537985</v>
       </c>
       <c r="M58">
         <v>0.4630245219062023</v>
@@ -13341,7 +13341,7 @@
         <v>710</v>
       </c>
       <c r="L59">
-        <v>3.0000000000000001E-3</v>
+        <v>1.9710593733284539E-3</v>
       </c>
       <c r="M59">
         <v>0.46063109886607562</v>
@@ -13415,10 +13415,10 @@
         <v>710</v>
       </c>
       <c r="L60">
-        <v>5.3999999999999999E-2</v>
+        <v>5.2695579272349823E-2</v>
       </c>
       <c r="M60">
-        <v>0.46023937471730875</v>
+        <v>0.46023937471730869</v>
       </c>
       <c r="N60">
         <v>2</v>
@@ -13489,7 +13489,7 @@
         <v>710</v>
       </c>
       <c r="L61">
-        <v>1.11825</v>
+        <v>0.90256809286008455</v>
       </c>
       <c r="M61">
         <v>0.4497869068337233</v>
@@ -13563,7 +13563,7 @@
         <v>710</v>
       </c>
       <c r="L62">
-        <v>0.12075</v>
+        <v>0.11300996309963099</v>
       </c>
       <c r="M62">
         <v>0.4461077590592073</v>
@@ -13637,10 +13637,10 @@
         <v>710</v>
       </c>
       <c r="L63">
-        <v>0.45224999999999999</v>
+        <v>0.36525007446492724</v>
       </c>
       <c r="M63">
-        <v>0.44208309388787315</v>
+        <v>0.44208309388787304</v>
       </c>
       <c r="N63">
         <v>4</v>
@@ -13711,7 +13711,7 @@
         <v>710</v>
       </c>
       <c r="L64">
-        <v>0.90749999999999997</v>
+        <v>0.74459622039583273</v>
       </c>
       <c r="M64">
         <v>0.43915965085013747</v>
@@ -13785,7 +13785,7 @@
         <v>710</v>
       </c>
       <c r="L65">
-        <v>0.57750000000000001</v>
+        <v>0.53303670001957426</v>
       </c>
       <c r="M65">
         <v>0.43847879401799411</v>
@@ -13859,10 +13859,10 @@
         <v>710</v>
       </c>
       <c r="L66">
-        <v>0.2235</v>
+        <v>0.22128008233237467</v>
       </c>
       <c r="M66">
-        <v>0.43578751124735354</v>
+        <v>0.43578751124735349</v>
       </c>
       <c r="N66">
         <v>1</v>
@@ -13933,7 +13933,7 @@
         <v>710</v>
       </c>
       <c r="L67">
-        <v>0.40050000000000002</v>
+        <v>0.28153144564758098</v>
       </c>
       <c r="M67">
         <v>0.43505169839367769</v>
@@ -14007,10 +14007,10 @@
         <v>710</v>
       </c>
       <c r="L68">
-        <v>2.7450000000000001</v>
+        <v>1.8997664463978698</v>
       </c>
       <c r="M68">
-        <v>0.43434322846114382</v>
+        <v>0.43433945366977866</v>
       </c>
       <c r="N68">
         <v>3</v>
@@ -14081,7 +14081,7 @@
         <v>710</v>
       </c>
       <c r="L69">
-        <v>0.28499999999999998</v>
+        <v>0.27653124396368556</v>
       </c>
       <c r="M69">
         <v>0.43371675735497722</v>
@@ -14155,10 +14155,10 @@
         <v>710</v>
       </c>
       <c r="L70">
-        <v>0.18149999999999999</v>
+        <v>0.13142347987018213</v>
       </c>
       <c r="M70">
-        <v>0.43292140194359213</v>
+        <v>0.43291053414887692</v>
       </c>
       <c r="N70">
         <v>1</v>
@@ -14229,10 +14229,10 @@
         <v>710</v>
       </c>
       <c r="L71">
-        <v>1.1467499999999999</v>
+        <v>1.0689782317861916</v>
       </c>
       <c r="M71">
-        <v>0.42948203890265418</v>
+        <v>0.42933129636552692</v>
       </c>
       <c r="N71">
         <v>4</v>
@@ -14303,10 +14303,10 @@
         <v>710</v>
       </c>
       <c r="L72">
-        <v>3.9E-2</v>
+        <v>2.4128965897522905E-2</v>
       </c>
       <c r="M72">
-        <v>0.42802217963468653</v>
+        <v>0.42801731600338161</v>
       </c>
       <c r="N72">
         <v>2</v>
@@ -14377,10 +14377,10 @@
         <v>710</v>
       </c>
       <c r="L73">
-        <v>2.1517499999999998</v>
+        <v>2.0091113564593694</v>
       </c>
       <c r="M73">
-        <v>0.42392145825187699</v>
+        <v>0.42388794346433362</v>
       </c>
       <c r="N73">
         <v>2</v>
@@ -14451,10 +14451,10 @@
         <v>710</v>
       </c>
       <c r="L74">
-        <v>0.87375000000000003</v>
+        <v>0.85180160279356099</v>
       </c>
       <c r="M74">
-        <v>0.42264701090958384</v>
+        <v>0.42264791232416343</v>
       </c>
       <c r="N74">
         <v>3</v>
@@ -14525,10 +14525,10 @@
         <v>710</v>
       </c>
       <c r="L75">
-        <v>0.76200000000000001</v>
+        <v>0.70764985793773971</v>
       </c>
       <c r="M75">
-        <v>0.42155674399515369</v>
+        <v>0.42155992500423922</v>
       </c>
       <c r="N75">
         <v>1</v>
@@ -14599,10 +14599,10 @@
         <v>710</v>
       </c>
       <c r="L76">
-        <v>1.96875</v>
+        <v>1.2435427916038644</v>
       </c>
       <c r="M76">
-        <v>0.41813549499705027</v>
+        <v>0.41847934253087088</v>
       </c>
       <c r="N76">
         <v>4</v>
@@ -14673,10 +14673,10 @@
         <v>710</v>
       </c>
       <c r="L77">
-        <v>3.4514999999999998</v>
+        <v>2.7039872535201912</v>
       </c>
       <c r="M77">
-        <v>0.41649134643603952</v>
+        <v>0.41651685743024153</v>
       </c>
       <c r="N77">
         <v>5</v>
@@ -14747,7 +14747,7 @@
         <v>710</v>
       </c>
       <c r="L78">
-        <v>1.8967499999999999</v>
+        <v>1.7723187021516222</v>
       </c>
       <c r="M78">
         <v>0.41364405387979181</v>
@@ -14821,10 +14821,10 @@
         <v>710</v>
       </c>
       <c r="L79">
-        <v>0.38850000000000001</v>
+        <v>0.37949606932741459</v>
       </c>
       <c r="M79">
-        <v>0.41236474975043008</v>
+        <v>0.41236474975043003</v>
       </c>
       <c r="N79">
         <v>5</v>
@@ -14895,7 +14895,7 @@
         <v>710</v>
       </c>
       <c r="L80">
-        <v>2.1749999999999999E-2</v>
+        <v>2.0621507565169835E-2</v>
       </c>
       <c r="M80">
         <v>0.40971341737243722</v>
@@ -15043,7 +15043,7 @@
         <v>710</v>
       </c>
       <c r="L82">
-        <v>1.11825</v>
+        <v>0.95447583749955289</v>
       </c>
       <c r="M82">
         <v>0.40909045524908572</v>
@@ -15117,7 +15117,7 @@
         <v>710</v>
       </c>
       <c r="L83">
-        <v>0.28425</v>
+        <v>0.24578598659906373</v>
       </c>
       <c r="M83">
         <v>0.40467167364390899</v>
@@ -15191,7 +15191,7 @@
         <v>710</v>
       </c>
       <c r="L84">
-        <v>4.5892499999999998</v>
+        <v>2.9653905432237209</v>
       </c>
       <c r="M84">
         <v>0.40180676346943711</v>
@@ -15265,7 +15265,7 @@
         <v>710</v>
       </c>
       <c r="L85">
-        <v>0.99075000000000002</v>
+        <v>0.90034838117554128</v>
       </c>
       <c r="M85">
         <v>0.39891332798519957</v>
@@ -15339,10 +15339,10 @@
         <v>710</v>
       </c>
       <c r="L86">
-        <v>1.0500000000000001E-2</v>
+        <v>9.8359732433029382E-3</v>
       </c>
       <c r="M86">
-        <v>0.39635365595957772</v>
+        <v>0.39603733138824676</v>
       </c>
       <c r="N86">
         <v>1</v>
@@ -15413,10 +15413,10 @@
         <v>710</v>
       </c>
       <c r="L87">
-        <v>2.952</v>
+        <v>2.4903689906946069</v>
       </c>
       <c r="M87">
-        <v>0.39520385419853771</v>
+        <v>0.39520425094784362</v>
       </c>
       <c r="N87">
         <v>2</v>
@@ -15487,7 +15487,7 @@
         <v>710</v>
       </c>
       <c r="L88">
-        <v>0.23849999999999999</v>
+        <v>0.21399296827931075</v>
       </c>
       <c r="M88">
         <v>0.39352960808118442</v>
@@ -15561,7 +15561,7 @@
         <v>710</v>
       </c>
       <c r="L89">
-        <v>1.9724999999999999</v>
+        <v>1.8845500496508163</v>
       </c>
       <c r="M89">
         <v>0.39201760513407369</v>
@@ -15635,10 +15635,10 @@
         <v>710</v>
       </c>
       <c r="L90">
-        <v>6.2655000000000003</v>
+        <v>4.461216164696074</v>
       </c>
       <c r="M90">
-        <v>0.39173278770665509</v>
+        <v>0.39174634138855119</v>
       </c>
       <c r="N90">
         <v>2</v>
@@ -15709,10 +15709,10 @@
         <v>710</v>
       </c>
       <c r="L91">
-        <v>0.46274999999999999</v>
+        <v>0.44128583926652898</v>
       </c>
       <c r="M91">
-        <v>0.39108593309238393</v>
+        <v>0.39107907603408532</v>
       </c>
       <c r="N91">
         <v>1</v>
@@ -15783,10 +15783,10 @@
         <v>710</v>
       </c>
       <c r="L92">
-        <v>4.7175000000000002</v>
+        <v>4.2483873092081836</v>
       </c>
       <c r="M92">
-        <v>0.39024540464813956</v>
+        <v>0.39019783739591485</v>
       </c>
       <c r="N92">
         <v>3</v>
@@ -15857,7 +15857,7 @@
         <v>710</v>
       </c>
       <c r="L93">
-        <v>2.181</v>
+        <v>1.7650676148849338</v>
       </c>
       <c r="M93">
         <v>0.37741178945933029</v>
@@ -15931,7 +15931,7 @@
         <v>710</v>
       </c>
       <c r="L94">
-        <v>1.1565000000000001</v>
+        <v>1.1256529791632151</v>
       </c>
       <c r="M94">
         <v>0.37396056591114812</v>
@@ -16005,10 +16005,10 @@
         <v>710</v>
       </c>
       <c r="L95">
-        <v>1.50675</v>
+        <v>1.3963773578316945</v>
       </c>
       <c r="M95">
-        <v>0.37272068478616538</v>
+        <v>0.37272068478616532</v>
       </c>
       <c r="N95">
         <v>2</v>
@@ -16079,7 +16079,7 @@
         <v>710</v>
       </c>
       <c r="L96">
-        <v>2.6385000000000001</v>
+        <v>1.524499516573004</v>
       </c>
       <c r="M96">
         <v>0.37116737891681439</v>
@@ -16153,7 +16153,7 @@
         <v>710</v>
       </c>
       <c r="L97">
-        <v>8.1750000000000003E-2</v>
+        <v>4.3449367384098228E-2</v>
       </c>
       <c r="M97">
         <v>0.36359227191351912</v>
@@ -16227,10 +16227,10 @@
         <v>710</v>
       </c>
       <c r="L98">
-        <v>5.4892500000000002</v>
+        <v>3.3621421559339422</v>
       </c>
       <c r="M98">
-        <v>0.36222996690773329</v>
+        <v>0.36190443426986207</v>
       </c>
       <c r="N98">
         <v>1</v>
@@ -16301,7 +16301,7 @@
         <v>710</v>
       </c>
       <c r="L99">
-        <v>3.0202499999999999</v>
+        <v>2.4701877958373588</v>
       </c>
       <c r="M99">
         <v>0.3600782440314329</v>
@@ -16375,7 +16375,7 @@
         <v>710</v>
       </c>
       <c r="L100">
-        <v>2.835</v>
+        <v>2.1785098423168092</v>
       </c>
       <c r="M100">
         <v>0.35832337378710699</v>
@@ -16449,7 +16449,7 @@
         <v>710</v>
       </c>
       <c r="L101">
-        <v>0.82950000000000002</v>
+        <v>0.56335468679468526</v>
       </c>
       <c r="M101">
         <v>0.3561605897266148</v>
@@ -16523,7 +16523,7 @@
         <v>710</v>
       </c>
       <c r="L102">
-        <v>0.69599999999999995</v>
+        <v>0.50502757057188818</v>
       </c>
       <c r="M102">
         <v>0.3528594272743385</v>
@@ -16597,7 +16597,7 @@
         <v>710</v>
       </c>
       <c r="L103">
-        <v>0.77175000000000005</v>
+        <v>0.73178766612719792</v>
       </c>
       <c r="M103">
         <v>0.35238892107842351</v>
@@ -16671,7 +16671,7 @@
         <v>710</v>
       </c>
       <c r="L104">
-        <v>0.67274999999999996</v>
+        <v>0.46035808007998508</v>
       </c>
       <c r="M104">
         <v>0.35144960385110119</v>
@@ -16745,10 +16745,10 @@
         <v>710</v>
       </c>
       <c r="L105">
-        <v>0.69750000000000001</v>
+        <v>0.49768682212704912</v>
       </c>
       <c r="M105">
-        <v>0.35078965987541683</v>
+        <v>0.35073727150259759</v>
       </c>
       <c r="N105">
         <v>1</v>
@@ -16819,10 +16819,10 @@
         <v>710</v>
       </c>
       <c r="L106">
-        <v>1.16025</v>
+        <v>0.68281567437193502</v>
       </c>
       <c r="M106">
-        <v>0.34964311368598805</v>
+        <v>0.34986851542082925</v>
       </c>
       <c r="N106">
         <v>2</v>
@@ -16893,7 +16893,7 @@
         <v>710</v>
       </c>
       <c r="L107">
-        <v>3.9097499999999998</v>
+        <v>2.6358605361198815</v>
       </c>
       <c r="M107">
         <v>0.34453191309095799</v>
@@ -16967,7 +16967,7 @@
         <v>710</v>
       </c>
       <c r="L108">
-        <v>1.8082499999999999</v>
+        <v>1.082021228437626</v>
       </c>
       <c r="M108">
         <v>0.3435774552745246</v>
@@ -17041,7 +17041,7 @@
         <v>710</v>
       </c>
       <c r="L109">
-        <v>1.3687499999999999</v>
+        <v>1.1916317680459974</v>
       </c>
       <c r="M109">
         <v>0.33909339165080932</v>
@@ -17115,7 +17115,7 @@
         <v>710</v>
       </c>
       <c r="L110">
-        <v>0.10349999999999999</v>
+        <v>8.0749243920253205E-2</v>
       </c>
       <c r="M110">
         <v>0.33583868224971108</v>
@@ -17189,7 +17189,7 @@
         <v>710</v>
       </c>
       <c r="L111">
-        <v>4.266</v>
+        <v>3.9567729542332599</v>
       </c>
       <c r="M111">
         <v>0.33570005222980392</v>
@@ -17263,10 +17263,10 @@
         <v>710</v>
       </c>
       <c r="L112">
-        <v>3.7605</v>
+        <v>2.5871512527835279</v>
       </c>
       <c r="M112">
-        <v>0.332146144945763</v>
+        <v>0.33220245354937217</v>
       </c>
       <c r="N112">
         <v>2</v>
@@ -17337,10 +17337,10 @@
         <v>710</v>
       </c>
       <c r="L113">
-        <v>5.1517499999999998</v>
+        <v>4.119883941947327</v>
       </c>
       <c r="M113">
-        <v>0.3313158969268476</v>
+        <v>0.33121075513174725</v>
       </c>
       <c r="N113">
         <v>3</v>
@@ -17411,10 +17411,10 @@
         <v>710</v>
       </c>
       <c r="L114">
-        <v>7.31175</v>
+        <v>5.9616437511257114</v>
       </c>
       <c r="M114">
-        <v>0.3283370694284134</v>
+        <v>0.32841498955297116</v>
       </c>
       <c r="N114">
         <v>1</v>
@@ -17485,13 +17485,13 @@
         <v>710</v>
       </c>
       <c r="L115">
-        <v>6.1515000000000004</v>
+        <v>0.5701796104853627</v>
       </c>
       <c r="M115">
-        <v>0.32822734213725974</v>
+        <v>0.32800522313494851</v>
       </c>
       <c r="N115">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P115" t="s">
         <v>182</v>
@@ -17559,13 +17559,13 @@
         <v>710</v>
       </c>
       <c r="L116">
-        <v>0.60675000000000001</v>
+        <v>5.0778765825359748</v>
       </c>
       <c r="M116">
-        <v>0.32800522313494851</v>
+        <v>0.32783524946143322</v>
       </c>
       <c r="N116">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P116" t="s">
         <v>182</v>
@@ -17633,7 +17633,7 @@
         <v>710</v>
       </c>
       <c r="L117">
-        <v>2.6587499999999999</v>
+        <v>1.930026452811612</v>
       </c>
       <c r="M117">
         <v>0.32326834091886941</v>
@@ -17707,7 +17707,7 @@
         <v>710</v>
       </c>
       <c r="L118">
-        <v>0.23849999999999999</v>
+        <v>0.12655475198691574</v>
       </c>
       <c r="M118">
         <v>0.32325845475265869</v>
@@ -17781,10 +17781,10 @@
         <v>710</v>
       </c>
       <c r="L119">
-        <v>3.9412500000000001</v>
+        <v>2.6988006975839571</v>
       </c>
       <c r="M119">
-        <v>0.32120220457184789</v>
+        <v>0.32139424439932041</v>
       </c>
       <c r="N119">
         <v>1</v>
@@ -17855,7 +17855,7 @@
         <v>710</v>
       </c>
       <c r="L120">
-        <v>4.1212499999999999</v>
+        <v>2.9591079046712392</v>
       </c>
       <c r="M120">
         <v>0.31680968880793048</v>
@@ -17929,7 +17929,7 @@
         <v>710</v>
       </c>
       <c r="L121">
-        <v>2.04</v>
+        <v>1.7085874251497006</v>
       </c>
       <c r="M121">
         <v>0.31593895307014741</v>
@@ -18003,13 +18003,13 @@
         <v>710</v>
       </c>
       <c r="L122">
-        <v>8.7832500000000007</v>
+        <v>2.7805279496200139</v>
       </c>
       <c r="M122">
-        <v>0.31256181663672555</v>
+        <v>0.31284042189855682</v>
       </c>
       <c r="N122">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P122" t="s">
         <v>182</v>
@@ -18077,13 +18077,13 @@
         <v>710</v>
       </c>
       <c r="L123">
-        <v>3.57525</v>
+        <v>7.4794605676373838</v>
       </c>
       <c r="M123">
-        <v>0.31246613081895436</v>
+        <v>0.31259262208011729</v>
       </c>
       <c r="N123">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P123" t="s">
         <v>182</v>
@@ -18151,10 +18151,10 @@
         <v>710</v>
       </c>
       <c r="L124">
-        <v>2.883</v>
+        <v>2.3327571098192692</v>
       </c>
       <c r="M124">
-        <v>0.3112373476154377</v>
+        <v>0.31100787093112386</v>
       </c>
       <c r="N124">
         <v>3</v>
@@ -18225,10 +18225,10 @@
         <v>710</v>
       </c>
       <c r="L125">
-        <v>11.2905</v>
+        <v>8.9899915474857703</v>
       </c>
       <c r="M125">
-        <v>0.31053145279200772</v>
+        <v>0.31034085738927747</v>
       </c>
       <c r="N125">
         <v>1</v>
@@ -18299,10 +18299,10 @@
         <v>710</v>
       </c>
       <c r="L126">
-        <v>4.0994999999999999</v>
+        <v>3.6231690229201132</v>
       </c>
       <c r="M126">
-        <v>0.30787361342613517</v>
+        <v>0.30786894951753696</v>
       </c>
       <c r="N126">
         <v>5</v>
@@ -18373,7 +18373,7 @@
         <v>710</v>
       </c>
       <c r="L127">
-        <v>4.8937499999999998</v>
+        <v>3.8954162920336874</v>
       </c>
       <c r="M127">
         <v>0.30404009189792658</v>
@@ -18447,7 +18447,7 @@
         <v>710</v>
       </c>
       <c r="L128">
-        <v>4.056</v>
+        <v>3.5767080790118708</v>
       </c>
       <c r="M128">
         <v>0.30247130311977388</v>
@@ -18521,7 +18521,7 @@
         <v>710</v>
       </c>
       <c r="L129">
-        <v>3.2130000000000001</v>
+        <v>2.2565906747040452</v>
       </c>
       <c r="M129">
         <v>0.3008540584096499</v>
@@ -18595,7 +18595,7 @@
         <v>710</v>
       </c>
       <c r="L130">
-        <v>6.1252500000000003</v>
+        <v>3.4518234842133215</v>
       </c>
       <c r="M130">
         <v>0.29597343440273338</v>
@@ -18669,7 +18669,7 @@
         <v>710</v>
       </c>
       <c r="L131">
-        <v>1.30725</v>
+        <v>1.1062575258439435</v>
       </c>
       <c r="M131">
         <v>0.29568926542758428</v>
@@ -18743,7 +18743,7 @@
         <v>710</v>
       </c>
       <c r="L132">
-        <v>5.03925</v>
+        <v>4.437106180443541</v>
       </c>
       <c r="M132">
         <v>0.29369009043473132</v>
@@ -18817,7 +18817,7 @@
         <v>710</v>
       </c>
       <c r="L133">
-        <v>1.00125</v>
+        <v>0.93355957980274695</v>
       </c>
       <c r="M133">
         <v>0.29348791386184808</v>
@@ -18891,7 +18891,7 @@
         <v>710</v>
       </c>
       <c r="L134">
-        <v>5.2515000000000001</v>
+        <v>2.7631101955952566</v>
       </c>
       <c r="M134">
         <v>0.29159868375129949</v>
@@ -18965,7 +18965,7 @@
         <v>710</v>
       </c>
       <c r="L135">
-        <v>4.2990000000000004</v>
+        <v>2.9776716498520166</v>
       </c>
       <c r="M135">
         <v>0.28994650655547199</v>
@@ -19039,7 +19039,7 @@
         <v>710</v>
       </c>
       <c r="L136">
-        <v>2.2522500000000001</v>
+        <v>2.0870442206855278</v>
       </c>
       <c r="M136">
         <v>0.28590023740774501</v>
@@ -19113,10 +19113,10 @@
         <v>710</v>
       </c>
       <c r="L137">
-        <v>7.52475</v>
+        <v>5.722897504749815</v>
       </c>
       <c r="M137">
-        <v>0.28348964093151974</v>
+        <v>0.28341917230727609</v>
       </c>
       <c r="N137">
         <v>5</v>
@@ -19187,10 +19187,10 @@
         <v>710</v>
       </c>
       <c r="L138">
-        <v>5.5439999999999996</v>
+        <v>4.5833316817825649</v>
       </c>
       <c r="M138">
-        <v>0.28209679149581118</v>
+        <v>0.28208366265702323</v>
       </c>
       <c r="N138">
         <v>2</v>
@@ -19261,10 +19261,10 @@
         <v>710</v>
       </c>
       <c r="L139">
-        <v>14.077500000000001</v>
+        <v>10.630714018160289</v>
       </c>
       <c r="M139">
-        <v>0.2786574258921925</v>
+        <v>0.27867653356769356</v>
       </c>
       <c r="N139">
         <v>1</v>
@@ -19335,10 +19335,10 @@
         <v>710</v>
       </c>
       <c r="L140">
-        <v>5.625</v>
+        <v>3.6734431712540059</v>
       </c>
       <c r="M140">
-        <v>0.27820569902450454</v>
+        <v>0.27734536748646399</v>
       </c>
       <c r="N140">
         <v>4</v>
@@ -19409,10 +19409,10 @@
         <v>710</v>
       </c>
       <c r="L141">
-        <v>7.2067500000000004</v>
+        <v>5.5733807879342114</v>
       </c>
       <c r="M141">
-        <v>0.2759716501107044</v>
+        <v>0.27594812737375835</v>
       </c>
       <c r="N141">
         <v>3</v>
@@ -19483,7 +19483,7 @@
         <v>710</v>
       </c>
       <c r="L142">
-        <v>3.8227500000000001</v>
+        <v>2.8457638428070613</v>
       </c>
       <c r="M142">
         <v>0.27470069827435017</v>
@@ -19557,7 +19557,7 @@
         <v>710</v>
       </c>
       <c r="L143">
-        <v>0.96375</v>
+        <v>0.90122894461234171</v>
       </c>
       <c r="M143">
         <v>0.27153669155949578</v>
@@ -19631,10 +19631,10 @@
         <v>710</v>
       </c>
       <c r="L144">
-        <v>5.4037499999999996</v>
+        <v>4.3569049883085933</v>
       </c>
       <c r="M144">
-        <v>0.26289718836314824</v>
+        <v>0.26305990459512235</v>
       </c>
       <c r="N144">
         <v>4</v>
@@ -19705,10 +19705,10 @@
         <v>710</v>
       </c>
       <c r="L145">
-        <v>3.51525</v>
+        <v>3.3075384822560077</v>
       </c>
       <c r="M145">
-        <v>0.2594927189402193</v>
+        <v>0.25947817077488761</v>
       </c>
       <c r="N145">
         <v>5</v>
@@ -19779,10 +19779,10 @@
         <v>710</v>
       </c>
       <c r="L146">
-        <v>9.7859999999999996</v>
+        <v>9.6271409913150343</v>
       </c>
       <c r="M146">
-        <v>0.25862841050493723</v>
+        <v>0.25863236619737145</v>
       </c>
       <c r="N146">
         <v>1</v>
@@ -19853,10 +19853,10 @@
         <v>710</v>
       </c>
       <c r="L147">
-        <v>9.9975000000000005</v>
+        <v>8.2601013176025404</v>
       </c>
       <c r="M147">
-        <v>0.25808274599385755</v>
+        <v>0.25814559964518058</v>
       </c>
       <c r="N147">
         <v>2</v>
@@ -19927,10 +19927,10 @@
         <v>710</v>
       </c>
       <c r="L148">
-        <v>9.0097500000000004</v>
+        <v>7.1824859810313901</v>
       </c>
       <c r="M148">
-        <v>0.25726721247264178</v>
+        <v>0.25722598545515429</v>
       </c>
       <c r="N148">
         <v>3</v>
@@ -20001,7 +20001,7 @@
         <v>710</v>
       </c>
       <c r="L149">
-        <v>5.5132500000000002</v>
+        <v>4.9585909575093545</v>
       </c>
       <c r="M149">
         <v>0.25423997315365521</v>
@@ -20075,7 +20075,7 @@
         <v>710</v>
       </c>
       <c r="L150">
-        <v>5.62575</v>
+        <v>4.985714889357741</v>
       </c>
       <c r="M150">
         <v>0.25207161957122692</v>
@@ -20149,7 +20149,7 @@
         <v>710</v>
       </c>
       <c r="L151">
-        <v>3.9592499999999999</v>
+        <v>3.7861485725941537</v>
       </c>
       <c r="M151">
         <v>0.247501930426336</v>
@@ -20223,10 +20223,10 @@
         <v>710</v>
       </c>
       <c r="L152">
-        <v>9.6277500000000007</v>
+        <v>8.0612876583840354</v>
       </c>
       <c r="M152">
-        <v>0.24249561259684635</v>
+        <v>0.242540680747937</v>
       </c>
       <c r="N152">
         <v>2</v>
@@ -20297,10 +20297,10 @@
         <v>710</v>
       </c>
       <c r="L153">
-        <v>4.4077500000000001</v>
+        <v>3.2878265610237882</v>
       </c>
       <c r="M153">
-        <v>0.24179220428159895</v>
+        <v>0.24151290534391567</v>
       </c>
       <c r="N153">
         <v>5</v>
@@ -20371,13 +20371,13 @@
         <v>710</v>
       </c>
       <c r="L154">
-        <v>3.8302499999999999</v>
+        <v>10.077370647160729</v>
       </c>
       <c r="M154">
-        <v>0.23809961497772572</v>
+        <v>0.23818515310754351</v>
       </c>
       <c r="N154">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P154" t="s">
         <v>182</v>
@@ -20445,13 +20445,13 @@
         <v>710</v>
       </c>
       <c r="L155">
-        <v>12.248250000000001</v>
+        <v>3.1126561605319103</v>
       </c>
       <c r="M155">
-        <v>0.23805224574762282</v>
+        <v>0.23812978056304623</v>
       </c>
       <c r="N155">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P155" t="s">
         <v>182</v>
@@ -20519,10 +20519,10 @@
         <v>710</v>
       </c>
       <c r="L156">
-        <v>3.1957499999999999</v>
+        <v>2.2587529068002055</v>
       </c>
       <c r="M156">
-        <v>0.23510112794372742</v>
+        <v>0.2350989057003342</v>
       </c>
       <c r="N156">
         <v>4</v>
@@ -20593,7 +20593,7 @@
         <v>710</v>
       </c>
       <c r="L157">
-        <v>6.0382499999999997</v>
+        <v>4.224073117148845</v>
       </c>
       <c r="M157">
         <v>0.23335159644867851</v>
@@ -20667,10 +20667,10 @@
         <v>710</v>
       </c>
       <c r="L158">
-        <v>3.44475</v>
+        <v>2.1161785771130592</v>
       </c>
       <c r="M158">
-        <v>0.22955991431958622</v>
+        <v>0.22955991431958619</v>
       </c>
       <c r="N158">
         <v>5</v>
@@ -20741,7 +20741,7 @@
         <v>710</v>
       </c>
       <c r="L159">
-        <v>3.6960000000000002</v>
+        <v>3.1387112373653965</v>
       </c>
       <c r="M159">
         <v>0.22908245738783839</v>
@@ -20815,7 +20815,7 @@
         <v>710</v>
       </c>
       <c r="L160">
-        <v>5.9474999999999998</v>
+        <v>3.477658910741301</v>
       </c>
       <c r="M160">
         <v>0.2277579635590582</v>
@@ -20889,10 +20889,10 @@
         <v>710</v>
       </c>
       <c r="L161">
-        <v>3.1492499999999999</v>
+        <v>2.1208173359511084</v>
       </c>
       <c r="M161">
-        <v>0.22651613048957134</v>
+        <v>0.22651613048957131</v>
       </c>
       <c r="N161">
         <v>3</v>
@@ -20963,7 +20963,7 @@
         <v>710</v>
       </c>
       <c r="L162">
-        <v>4.0650000000000004</v>
+        <v>3.5532255555321965</v>
       </c>
       <c r="M162">
         <v>0.2229381655813526</v>
@@ -21037,10 +21037,10 @@
         <v>710</v>
       </c>
       <c r="L163">
-        <v>11.223000000000001</v>
+        <v>9.7340080572413132</v>
       </c>
       <c r="M163">
-        <v>0.22103012541439568</v>
+        <v>0.22102121186859752</v>
       </c>
       <c r="N163">
         <v>1</v>
@@ -21111,10 +21111,10 @@
         <v>710</v>
       </c>
       <c r="L164">
-        <v>2.10975</v>
+        <v>1.7245071966171635</v>
       </c>
       <c r="M164">
-        <v>0.21979221356497117</v>
+        <v>0.22001393540959741</v>
       </c>
       <c r="N164">
         <v>2</v>
@@ -21185,7 +21185,7 @@
         <v>710</v>
       </c>
       <c r="L165">
-        <v>4.0057499999999999</v>
+        <v>2.8901556673866517</v>
       </c>
       <c r="M165">
         <v>0.21716418578518851</v>
@@ -21259,10 +21259,10 @@
         <v>710</v>
       </c>
       <c r="L166">
-        <v>9.7995000000000001</v>
+        <v>9.0870978275099734</v>
       </c>
       <c r="M166">
-        <v>0.21629232082687486</v>
+        <v>0.21627570040274063</v>
       </c>
       <c r="N166">
         <v>3</v>
@@ -21333,10 +21333,10 @@
         <v>710</v>
       </c>
       <c r="L167">
-        <v>7.4474999999999998</v>
+        <v>7.2584667467183186</v>
       </c>
       <c r="M167">
-        <v>0.21136790648790549</v>
+        <v>0.21137914563506557</v>
       </c>
       <c r="N167">
         <v>2</v>
@@ -21407,10 +21407,10 @@
         <v>710</v>
       </c>
       <c r="L168">
-        <v>11.0685</v>
+        <v>7.4979945197514937</v>
       </c>
       <c r="M168">
-        <v>0.210602509743257</v>
+        <v>0.21111769489021798</v>
       </c>
       <c r="N168">
         <v>5</v>
@@ -21481,10 +21481,10 @@
         <v>710</v>
       </c>
       <c r="L169">
-        <v>17.43</v>
+        <v>14.03247459712129</v>
       </c>
       <c r="M169">
-        <v>0.21035226782058111</v>
+        <v>0.21048989813022959</v>
       </c>
       <c r="N169">
         <v>1</v>
@@ -21555,10 +21555,10 @@
         <v>710</v>
       </c>
       <c r="L170">
-        <v>10.39725</v>
+        <v>7.8760900973950845</v>
       </c>
       <c r="M170">
-        <v>0.21017199772355993</v>
+        <v>0.21012809909906782</v>
       </c>
       <c r="N170">
         <v>4</v>
@@ -21629,10 +21629,10 @@
         <v>710</v>
       </c>
       <c r="L171">
-        <v>9.1297499999999996</v>
+        <v>6.3935145495631582</v>
       </c>
       <c r="M171">
-        <v>0.21013589545421191</v>
+        <v>0.20938731211989858</v>
       </c>
       <c r="N171">
         <v>3</v>
@@ -21703,7 +21703,7 @@
         <v>710</v>
       </c>
       <c r="L172">
-        <v>6.0952500000000001</v>
+        <v>5.2687756283486227</v>
       </c>
       <c r="M172">
         <v>0.20184708427786169</v>
@@ -21777,7 +21777,7 @@
         <v>710</v>
       </c>
       <c r="L173">
-        <v>3.7934999999999999</v>
+        <v>2.5288703397139125</v>
       </c>
       <c r="M173">
         <v>0.2011788731561634</v>
@@ -21851,7 +21851,7 @@
         <v>710</v>
       </c>
       <c r="L174">
-        <v>4.1459999999999999</v>
+        <v>2.9083431654821106</v>
       </c>
       <c r="M174">
         <v>0.19750062325734599</v>
@@ -21925,10 +21925,10 @@
         <v>710</v>
       </c>
       <c r="L175">
-        <v>9.28125</v>
+        <v>7.4334898806643936</v>
       </c>
       <c r="M175">
-        <v>0.19270214987126122</v>
+        <v>0.19298667137883921</v>
       </c>
       <c r="N175">
         <v>2</v>
@@ -21999,10 +21999,10 @@
         <v>710</v>
       </c>
       <c r="L176">
-        <v>8.3309999999999995</v>
+        <v>7.38820347927442</v>
       </c>
       <c r="M176">
-        <v>0.19060205213714995</v>
+        <v>0.19055000349569082</v>
       </c>
       <c r="N176">
         <v>3</v>
@@ -22073,13 +22073,13 @@
         <v>710</v>
       </c>
       <c r="L177">
-        <v>3.6877499999999999</v>
+        <v>9.0953449583385275</v>
       </c>
       <c r="M177">
-        <v>0.18807905497550029</v>
+        <v>0.18808796706401421</v>
       </c>
       <c r="N177">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P177" t="s">
         <v>182</v>
@@ -22147,13 +22147,13 @@
         <v>710</v>
       </c>
       <c r="L178">
-        <v>11.177250000000001</v>
+        <v>3.0133100897090981</v>
       </c>
       <c r="M178">
-        <v>0.18799180071236588</v>
+        <v>0.18807905497550029</v>
       </c>
       <c r="N178">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P178" t="s">
         <v>182</v>
@@ -22221,7 +22221,7 @@
         <v>710</v>
       </c>
       <c r="L179">
-        <v>4.4197499999999996</v>
+        <v>1.8394835454375038</v>
       </c>
       <c r="M179">
         <v>0.18775731703101031</v>
@@ -22295,10 +22295,10 @@
         <v>710</v>
       </c>
       <c r="L180">
-        <v>6.27</v>
+        <v>4.3797343042366403</v>
       </c>
       <c r="M180">
-        <v>0.18362445041578712</v>
+        <v>0.18356191776011779</v>
       </c>
       <c r="N180">
         <v>4</v>
@@ -22369,10 +22369,10 @@
         <v>710</v>
       </c>
       <c r="L181">
-        <v>11.24175</v>
+        <v>9.7247067679084545</v>
       </c>
       <c r="M181">
-        <v>0.18314682284920505</v>
+        <v>0.18310503630514924</v>
       </c>
       <c r="N181">
         <v>2</v>
@@ -22443,10 +22443,10 @@
         <v>710</v>
       </c>
       <c r="L182">
-        <v>11.705249999999999</v>
+        <v>9.2573382238903612</v>
       </c>
       <c r="M182">
-        <v>0.18197331468163983</v>
+        <v>0.1819866611074511</v>
       </c>
       <c r="N182">
         <v>3</v>
@@ -22517,10 +22517,10 @@
         <v>710</v>
       </c>
       <c r="L183">
-        <v>15.94875</v>
+        <v>14.215571935999174</v>
       </c>
       <c r="M183">
-        <v>0.1807365520487802</v>
+        <v>0.18088342691258424</v>
       </c>
       <c r="N183">
         <v>1</v>
@@ -22591,10 +22591,10 @@
         <v>710</v>
       </c>
       <c r="L184">
-        <v>8.2342499999999994</v>
+        <v>6.40454709471235</v>
       </c>
       <c r="M184">
-        <v>0.17611091629149411</v>
+        <v>0.17602640815974313</v>
       </c>
       <c r="N184">
         <v>5</v>
@@ -22665,10 +22665,10 @@
         <v>710</v>
       </c>
       <c r="L185">
-        <v>10.96125</v>
+        <v>8.437042784777594</v>
       </c>
       <c r="M185">
-        <v>0.1710235945513317</v>
+        <v>0.17099210028629605</v>
       </c>
       <c r="N185">
         <v>3</v>
@@ -22739,10 +22739,10 @@
         <v>710</v>
       </c>
       <c r="L186">
-        <v>13.4535</v>
+        <v>11.716284931407461</v>
       </c>
       <c r="M186">
-        <v>0.17082411669799435</v>
+        <v>0.1706666839302006</v>
       </c>
       <c r="N186">
         <v>2</v>
@@ -22813,10 +22813,10 @@
         <v>710</v>
       </c>
       <c r="L187">
-        <v>16.001249999999999</v>
+        <v>14.042520418871376</v>
       </c>
       <c r="M187">
-        <v>0.16770565695964496</v>
+        <v>0.16757077121653138</v>
       </c>
       <c r="N187">
         <v>1</v>
@@ -22887,10 +22887,10 @@
         <v>710</v>
       </c>
       <c r="L188">
-        <v>5.3497500000000002</v>
+        <v>4.0647545329371013</v>
       </c>
       <c r="M188">
-        <v>0.16723970212772341</v>
+        <v>0.16726844834868984</v>
       </c>
       <c r="N188">
         <v>4</v>
@@ -22961,10 +22961,10 @@
         <v>710</v>
       </c>
       <c r="L189">
-        <v>8.5372500000000002</v>
+        <v>5.9628185385678627</v>
       </c>
       <c r="M189">
-        <v>0.16692376360911659</v>
+        <v>0.16687026264243102</v>
       </c>
       <c r="N189">
         <v>5</v>
@@ -23035,10 +23035,10 @@
         <v>710</v>
       </c>
       <c r="L190">
-        <v>10.901999999999999</v>
+        <v>8.7820508906037897</v>
       </c>
       <c r="M190">
-        <v>0.16238271383192598</v>
+        <v>0.16232899105347312</v>
       </c>
       <c r="N190">
         <v>2</v>
@@ -23109,10 +23109,10 @@
         <v>710</v>
       </c>
       <c r="L191">
-        <v>14.5245</v>
+        <v>13.116983201971063</v>
       </c>
       <c r="M191">
-        <v>0.16212376344886312</v>
+        <v>0.16227401013607615</v>
       </c>
       <c r="N191">
         <v>1</v>
@@ -23183,10 +23183,10 @@
         <v>710</v>
       </c>
       <c r="L192">
-        <v>5.931</v>
+        <v>5.3975986705205488</v>
       </c>
       <c r="M192">
-        <v>0.1611261542525429</v>
+        <v>0.16112406428027273</v>
       </c>
       <c r="N192">
         <v>4</v>
@@ -23257,10 +23257,10 @@
         <v>710</v>
       </c>
       <c r="L193">
-        <v>10.1355</v>
+        <v>8.2115626900617382</v>
       </c>
       <c r="M193">
-        <v>0.16042394793031092</v>
+        <v>0.16046915696737057</v>
       </c>
       <c r="N193">
         <v>5</v>
@@ -23331,10 +23331,10 @@
         <v>710</v>
       </c>
       <c r="L194">
-        <v>8.3535000000000004</v>
+        <v>6.8049371627198321</v>
       </c>
       <c r="M194">
-        <v>0.15699174131130694</v>
+        <v>0.15698634661161906</v>
       </c>
       <c r="N194">
         <v>3</v>
@@ -23405,7 +23405,7 @@
         <v>710</v>
       </c>
       <c r="L195">
-        <v>0.53700000000000003</v>
+        <v>0.2188492248454757</v>
       </c>
       <c r="M195">
         <v>0.154640745389552</v>
@@ -23479,7 +23479,7 @@
         <v>710</v>
       </c>
       <c r="L196">
-        <v>5.7607499999999998</v>
+        <v>3.8894694256571345</v>
       </c>
       <c r="M196">
         <v>0.1496883689011215</v>
@@ -23553,7 +23553,7 @@
         <v>710</v>
       </c>
       <c r="L197">
-        <v>3.6127500000000001</v>
+        <v>2.365020148547377</v>
       </c>
       <c r="M197">
         <v>0.14829316337006501</v>
@@ -23627,7 +23627,7 @@
         <v>710</v>
       </c>
       <c r="L198">
-        <v>3.66825</v>
+        <v>1.6172661409762021</v>
       </c>
       <c r="M198">
         <v>0.1478386784688889</v>
@@ -23701,10 +23701,10 @@
         <v>710</v>
       </c>
       <c r="L199">
-        <v>8.7877500000000008</v>
+        <v>7.926161667413294</v>
       </c>
       <c r="M199">
-        <v>0.14691894753301254</v>
+        <v>0.14688743091115503</v>
       </c>
       <c r="N199">
         <v>1</v>
@@ -23775,7 +23775,7 @@
         <v>710</v>
       </c>
       <c r="L200">
-        <v>2.8972500000000001</v>
+        <v>2.0980900568860168</v>
       </c>
       <c r="M200">
         <v>0.14462996363330979</v>
@@ -23849,7 +23849,7 @@
         <v>710</v>
       </c>
       <c r="L201">
-        <v>2.48475</v>
+        <v>1.9315919928791523</v>
       </c>
       <c r="M201">
         <v>0.1425119031285286</v>
@@ -23923,7 +23923,7 @@
         <v>710</v>
       </c>
       <c r="L202">
-        <v>5.9504999999999999</v>
+        <v>2.48933283553635</v>
       </c>
       <c r="M202">
         <v>0.1422219482184012</v>
@@ -23997,7 +23997,7 @@
         <v>710</v>
       </c>
       <c r="L203">
-        <v>3.45</v>
+        <v>2.9043127741779688</v>
       </c>
       <c r="M203">
         <v>0.1421912359397606</v>
@@ -24071,10 +24071,10 @@
         <v>710</v>
       </c>
       <c r="L204">
-        <v>6.2917500000000004</v>
+        <v>3.3187541118640951</v>
       </c>
       <c r="M204">
-        <v>0.14204952172905705</v>
+        <v>0.14152862910693076</v>
       </c>
       <c r="N204">
         <v>1</v>
@@ -24145,7 +24145,7 @@
         <v>710</v>
       </c>
       <c r="L205">
-        <v>5.1652500000000003</v>
+        <v>4.1744072681478483</v>
       </c>
       <c r="M205">
         <v>0.13326236655501239</v>
@@ -24219,10 +24219,10 @@
         <v>710</v>
       </c>
       <c r="L206">
-        <v>7.0229999999999997</v>
+        <v>6.7085627728515904</v>
       </c>
       <c r="M206">
-        <v>0.13185307277831423</v>
+        <v>0.13184812464182616</v>
       </c>
       <c r="N206">
         <v>1</v>
@@ -24293,7 +24293,7 @@
         <v>710</v>
       </c>
       <c r="L207">
-        <v>1.58775</v>
+        <v>1.3517369156998773</v>
       </c>
       <c r="M207">
         <v>0.13127532601331501</v>
@@ -24367,7 +24367,7 @@
         <v>710</v>
       </c>
       <c r="L208">
-        <v>5.93025</v>
+        <v>3.2678269060174125</v>
       </c>
       <c r="M208">
         <v>0.12954530430657329</v>
@@ -24441,7 +24441,7 @@
         <v>710</v>
       </c>
       <c r="L209">
-        <v>4.2052500000000004</v>
+        <v>3.6845292109056347</v>
       </c>
       <c r="M209">
         <v>0.12837789971369901</v>
@@ -24515,10 +24515,10 @@
         <v>710</v>
       </c>
       <c r="L210">
-        <v>2.4510000000000001</v>
+        <v>2.0859673682178026</v>
       </c>
       <c r="M210">
-        <v>0.12212314723937491</v>
+        <v>0.1221231472393749</v>
       </c>
       <c r="N210">
         <v>3</v>
@@ -24589,10 +24589,10 @@
         <v>710</v>
       </c>
       <c r="L211">
-        <v>5.2649999999999997</v>
+        <v>4.5571326565726089</v>
       </c>
       <c r="M211">
-        <v>0.1187798028849209</v>
+        <v>0.11877980288492092</v>
       </c>
       <c r="N211">
         <v>1</v>
@@ -24663,10 +24663,10 @@
         <v>710</v>
       </c>
       <c r="L212">
-        <v>4.8360000000000003</v>
+        <v>3.8642344750765805</v>
       </c>
       <c r="M212">
-        <v>0.11582201128351101</v>
+        <v>0.11582201128351099</v>
       </c>
       <c r="N212">
         <v>2</v>
@@ -24737,7 +24737,7 @@
         <v>710</v>
       </c>
       <c r="L213">
-        <v>4.2787499999999996</v>
+        <v>3.0356801491000578</v>
       </c>
       <c r="M213">
         <v>0.1151728163575572</v>
@@ -24811,10 +24811,10 @@
         <v>710</v>
       </c>
       <c r="L214">
-        <v>4.3769999999999998</v>
+        <v>3.3673008750082656</v>
       </c>
       <c r="M214">
-        <v>0.1140717835648902</v>
+        <v>0.11407178356489019</v>
       </c>
       <c r="N214">
         <v>2</v>
@@ -24885,7 +24885,7 @@
         <v>710</v>
       </c>
       <c r="L215">
-        <v>2.9797500000000001</v>
+        <v>2.9166326780077103</v>
       </c>
       <c r="M215">
         <v>0.1139454350974745</v>
@@ -24959,7 +24959,7 @@
         <v>710</v>
       </c>
       <c r="L216">
-        <v>0.75749999999999995</v>
+        <v>0.50100266242633718</v>
       </c>
       <c r="M216">
         <v>0.1123423603571337</v>
@@ -25033,10 +25033,10 @@
         <v>710</v>
       </c>
       <c r="L217">
-        <v>2.3107500000000001</v>
+        <v>1.6818505919224802</v>
       </c>
       <c r="M217">
-        <v>0.1055200573624115</v>
+        <v>0.10552005736241149</v>
       </c>
       <c r="N217">
         <v>3</v>
@@ -25107,10 +25107,10 @@
         <v>710</v>
       </c>
       <c r="L218">
-        <v>4.6589999999999998</v>
+        <v>3.5085398458748869</v>
       </c>
       <c r="M218">
-        <v>9.9770752656015496E-2</v>
+        <v>9.977075265601551E-2</v>
       </c>
       <c r="N218">
         <v>1</v>
@@ -25181,7 +25181,7 @@
         <v>710</v>
       </c>
       <c r="L219">
-        <v>1.7925</v>
+        <v>1.6801471785973865</v>
       </c>
       <c r="M219">
         <v>9.7177892981614306E-2</v>
@@ -25255,10 +25255,10 @@
         <v>710</v>
       </c>
       <c r="L220">
-        <v>2.3460000000000001</v>
+        <v>1.7305667994244844</v>
       </c>
       <c r="M220">
-        <v>9.6049687486761195E-2</v>
+        <v>9.6049687486761182E-2</v>
       </c>
       <c r="N220">
         <v>3</v>
@@ -25329,7 +25329,7 @@
         <v>710</v>
       </c>
       <c r="L221">
-        <v>2.298</v>
+        <v>2.2537596268317497</v>
       </c>
       <c r="M221">
         <v>9.1361324752340503E-2</v>
@@ -25403,7 +25403,7 @@
         <v>710</v>
       </c>
       <c r="L222">
-        <v>2.5590000000000002</v>
+        <v>1.3332290746268656</v>
       </c>
       <c r="M222">
         <v>8.8882280926081095E-2</v>
@@ -25477,7 +25477,7 @@
         <v>710</v>
       </c>
       <c r="L223">
-        <v>0.82499999999999996</v>
+        <v>0.79363369364395076</v>
       </c>
       <c r="M223">
         <v>8.8071294439464196E-2</v>
@@ -25551,7 +25551,7 @@
         <v>710</v>
       </c>
       <c r="L224">
-        <v>3.02325</v>
+        <v>1.8703447531124959</v>
       </c>
       <c r="M224">
         <v>8.7058544346671402E-2</v>
@@ -25625,7 +25625,7 @@
         <v>710</v>
       </c>
       <c r="L225">
-        <v>2.4172500000000001</v>
+        <v>2.136429828455233</v>
       </c>
       <c r="M225">
         <v>8.5476919420985703E-2</v>
@@ -25699,7 +25699,7 @@
         <v>710</v>
       </c>
       <c r="L226">
-        <v>3.093</v>
+        <v>2.9902228837744058</v>
       </c>
       <c r="M226">
         <v>8.2759689059080099E-2</v>
@@ -25773,7 +25773,7 @@
         <v>710</v>
       </c>
       <c r="L227">
-        <v>2.0767500000000001</v>
+        <v>0.81976113101330594</v>
       </c>
       <c r="M227">
         <v>8.1686744709339995E-2</v>
@@ -25847,7 +25847,7 @@
         <v>710</v>
       </c>
       <c r="L228">
-        <v>4.3912500000000003</v>
+        <v>2.0178097216940154</v>
       </c>
       <c r="M228">
         <v>8.0117635936464607E-2</v>
@@ -25921,7 +25921,7 @@
         <v>710</v>
       </c>
       <c r="L229">
-        <v>2.6902499999999998</v>
+        <v>2.4006628901403739</v>
       </c>
       <c r="M229">
         <v>7.9178762972175298E-2</v>
@@ -25995,7 +25995,7 @@
         <v>710</v>
       </c>
       <c r="L230">
-        <v>3.5722499999999999</v>
+        <v>2.9586862317386178</v>
       </c>
       <c r="M230">
         <v>7.8224179356388798E-2</v>
@@ -26033,7 +26033,7 @@
         <v>710</v>
       </c>
       <c r="L231">
-        <v>3.6382500000000002</v>
+        <v>3.0073033200293811</v>
       </c>
       <c r="M231">
         <v>7.4899694895753197E-2</v>
@@ -26071,7 +26071,7 @@
         <v>710</v>
       </c>
       <c r="L232">
-        <v>2.4817499999999999</v>
+        <v>2.3363667253637517</v>
       </c>
       <c r="M232">
         <v>6.5620411654016206E-2</v>
@@ -26109,7 +26109,7 @@
         <v>710</v>
       </c>
       <c r="L233">
-        <v>2.9235000000000002</v>
+        <v>2.5392002018051336</v>
       </c>
       <c r="M233">
         <v>6.1234415640421203E-2</v>
@@ -26147,10 +26147,10 @@
         <v>710</v>
       </c>
       <c r="L234">
-        <v>2.7690000000000001</v>
+        <v>2.3152872522458292</v>
       </c>
       <c r="M234">
-        <v>5.3768224457835793E-2</v>
+        <v>5.37682244578358E-2</v>
       </c>
       <c r="N234">
         <v>1</v>
@@ -26185,7 +26185,7 @@
         <v>710</v>
       </c>
       <c r="L235">
-        <v>0.93825000000000003</v>
+        <v>0.79573817914735678</v>
       </c>
       <c r="M235">
         <v>5.09076469351342E-2</v>
@@ -26223,7 +26223,7 @@
         <v>710</v>
       </c>
       <c r="L236">
-        <v>2.0902500000000002</v>
+        <v>1.8421426864619588</v>
       </c>
       <c r="M236">
         <v>4.8040996790013502E-2</v>
@@ -26261,7 +26261,7 @@
         <v>710</v>
       </c>
       <c r="L237">
-        <v>2.5282499999999999</v>
+        <v>2.1641244827395534</v>
       </c>
       <c r="M237">
         <v>4.7313566954455197E-2</v>
@@ -26299,7 +26299,7 @@
         <v>710</v>
       </c>
       <c r="L238">
-        <v>4.4085000000000001</v>
+        <v>3.9866858008604655</v>
       </c>
       <c r="M238">
         <v>4.4214949296898599E-2</v>
@@ -26337,7 +26337,7 @@
         <v>710</v>
       </c>
       <c r="L239">
-        <v>3.69</v>
+        <v>3.1452066630552546</v>
       </c>
       <c r="M239">
         <v>4.3180538556199001E-2</v>
@@ -26375,7 +26375,7 @@
         <v>710</v>
       </c>
       <c r="L240">
-        <v>1.7617499999999999</v>
+        <v>1.5599962381547079</v>
       </c>
       <c r="M240">
         <v>3.5959791363848297E-2</v>
@@ -26413,7 +26413,7 @@
         <v>710</v>
       </c>
       <c r="L241">
-        <v>1.4715</v>
+        <v>0.9558854555580093</v>
       </c>
       <c r="M241">
         <v>3.4381811557280102E-2</v>
@@ -26428,7 +26428,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAF02795-4EAC-4852-9FB4-92C827F616FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6738AAB2-9210-451B-B7AA-CB6AB124E09F}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61A75C8A-ED05-43FE-8EED-46AD54C89BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0333D973-3AD1-4C5E-862A-EE6AB0BEEB7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8510,7 +8510,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01A3603-82E8-4CCB-9837-5DC06401E1AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BB6B63-9FE2-4C14-AEDA-10280AF0B279}">
   <dimension ref="B9:N39"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9668,7 +9668,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66469083-4509-472A-9E5C-51777F3BA1AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1806B6C8-318D-4722-9539-20DEE482BFD9}">
   <dimension ref="B9:AB241"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -26428,7 +26428,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6738AAB2-9210-451B-B7AA-CB6AB124E09F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B31C9C49-846F-4E7E-A032-7B908616A2F4}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0333D973-3AD1-4C5E-862A-EE6AB0BEEB7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F0E7737-7FAA-4CA1-B261-EA00A9EEDBBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8510,7 +8510,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BB6B63-9FE2-4C14-AEDA-10280AF0B279}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5802F4D-0230-43F1-8FB1-6369D1D7D6E7}">
   <dimension ref="B9:N39"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9668,7 +9668,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1806B6C8-318D-4722-9539-20DEE482BFD9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AF68027-24AC-4069-A67D-86189CAAA42E}">
   <dimension ref="B9:AB241"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -26428,7 +26428,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B31C9C49-846F-4E7E-A032-7B908616A2F4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05661A8E-2B62-49A2-AFE4-9CD86DE300CD}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F0E7737-7FAA-4CA1-B261-EA00A9EEDBBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{190C0929-BA9E-47C0-BE7E-9F6E2683EB30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8510,7 +8510,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5802F4D-0230-43F1-8FB1-6369D1D7D6E7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F548C79-E837-477B-8006-A39A537A76B9}">
   <dimension ref="B9:N39"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8782,7 +8782,7 @@
         <v>4.2915127571032521</v>
       </c>
       <c r="M16">
-        <v>0.20255502580650991</v>
+        <v>0.20255502580650994</v>
       </c>
       <c r="N16">
         <v>1</v>
@@ -9200,7 +9200,7 @@
         <v>22.046035212741312</v>
       </c>
       <c r="M27">
-        <v>0.18010227619137506</v>
+        <v>0.18010227619137509</v>
       </c>
       <c r="N27">
         <v>1</v>
@@ -9390,7 +9390,7 @@
         <v>7.746165920142734</v>
       </c>
       <c r="M32">
-        <v>0.17095024257417377</v>
+        <v>0.17095024257417379</v>
       </c>
       <c r="N32">
         <v>3</v>
@@ -9466,7 +9466,7 @@
         <v>5.2829686285243866</v>
       </c>
       <c r="M34">
-        <v>0.1690727955762216</v>
+        <v>0.16907279557622168</v>
       </c>
       <c r="N34">
         <v>4</v>
@@ -9580,7 +9580,7 @@
         <v>0.82552886393659175</v>
       </c>
       <c r="M37">
-        <v>0.1645551726092882</v>
+        <v>0.16455517260928829</v>
       </c>
       <c r="N37">
         <v>1</v>
@@ -9668,7 +9668,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AF68027-24AC-4069-A67D-86189CAAA42E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BC51EC8-3E25-49C1-858E-3BF1C946923B}">
   <dimension ref="B9:AB241"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9792,7 +9792,7 @@
         <v>0.10961613792773224</v>
       </c>
       <c r="M11">
-        <v>0.60943134336451088</v>
+        <v>0.60943134184577885</v>
       </c>
       <c r="N11">
         <v>2</v>
@@ -9866,7 +9866,7 @@
         <v>6.7499999999999999E-3</v>
       </c>
       <c r="M12">
-        <v>0.60502917932075517</v>
+        <v>0.60502917795414135</v>
       </c>
       <c r="N12">
         <v>1</v>
@@ -9940,7 +9940,7 @@
         <v>3.7499999999999999E-3</v>
       </c>
       <c r="M13">
-        <v>0.59130060240154225</v>
+        <v>0.59130060022282682</v>
       </c>
       <c r="N13">
         <v>1</v>
@@ -10014,7 +10014,7 @@
         <v>5.9024698639353411E-2</v>
       </c>
       <c r="M14">
-        <v>0.58748294782093702</v>
+        <v>0.5874829460365818</v>
       </c>
       <c r="N14">
         <v>2</v>
@@ -10088,7 +10088,7 @@
         <v>8.1000000000000003E-2</v>
       </c>
       <c r="M15">
-        <v>0.58154191740178784</v>
+        <v>0.58154191570172487</v>
       </c>
       <c r="N15">
         <v>1</v>
@@ -10162,7 +10162,7 @@
         <v>8.568010246548606E-2</v>
       </c>
       <c r="M16">
-        <v>0.57925651644848553</v>
+        <v>0.57925651407778767</v>
       </c>
       <c r="N16">
         <v>2</v>
@@ -10236,7 +10236,7 @@
         <v>1.4457665016847654</v>
       </c>
       <c r="M17">
-        <v>0.57765234546594191</v>
+        <v>0.57765234323057713</v>
       </c>
       <c r="N17">
         <v>3</v>
@@ -10310,7 +10310,7 @@
         <v>2.8510316761465053</v>
       </c>
       <c r="M18">
-        <v>0.57446893665389331</v>
+        <v>0.57446893496322238</v>
       </c>
       <c r="N18">
         <v>1</v>
@@ -10384,7 +10384,7 @@
         <v>8.631867246657E-3</v>
       </c>
       <c r="M19">
-        <v>0.55617481096337473</v>
+        <v>0.55617480874343816</v>
       </c>
       <c r="N19">
         <v>1</v>
@@ -10458,7 +10458,7 @@
         <v>0.59443951986827503</v>
       </c>
       <c r="M20">
-        <v>0.55122923896985854</v>
+        <v>0.55122923728874829</v>
       </c>
       <c r="N20">
         <v>5</v>
@@ -10532,7 +10532,7 @@
         <v>1.399952863539948E-3</v>
       </c>
       <c r="M21">
-        <v>0.5508583489846447</v>
+        <v>0.55085834727188376</v>
       </c>
       <c r="N21">
         <v>4</v>
@@ -10606,7 +10606,7 @@
         <v>0.53403699849091946</v>
       </c>
       <c r="M22">
-        <v>0.54913697276959383</v>
+        <v>0.54913697116357829</v>
       </c>
       <c r="N22">
         <v>3</v>
@@ -10680,7 +10680,7 @@
         <v>3.6466097520932521E-3</v>
       </c>
       <c r="M23">
-        <v>0.5481562126255598</v>
+        <v>0.5481562105411073</v>
       </c>
       <c r="N23">
         <v>2</v>
@@ -10754,7 +10754,7 @@
         <v>9.5795605252893004E-2</v>
       </c>
       <c r="M24">
-        <v>0.54683889639534444</v>
+        <v>0.54683889516558604</v>
       </c>
       <c r="N24">
         <v>1</v>
@@ -10828,7 +10828,7 @@
         <v>7.5000000000000002E-4</v>
       </c>
       <c r="M25">
-        <v>0.54395460724532174</v>
+        <v>0.54395460514461624</v>
       </c>
       <c r="N25">
         <v>1</v>
@@ -10902,7 +10902,7 @@
         <v>0.29512395089723703</v>
       </c>
       <c r="M26">
-        <v>0.52676880725479447</v>
+        <v>0.52676880567442852</v>
       </c>
       <c r="N26">
         <v>1</v>
@@ -10976,7 +10976,7 @@
         <v>1.0835865278388652</v>
       </c>
       <c r="M27">
-        <v>0.52204391074263623</v>
+        <v>0.52204390847224891</v>
       </c>
       <c r="N27">
         <v>4</v>
@@ -11050,7 +11050,7 @@
         <v>0.26132985914414547</v>
       </c>
       <c r="M28">
-        <v>0.51843069331938374</v>
+        <v>0.51843069076688508</v>
       </c>
       <c r="N28">
         <v>3</v>
@@ -11086,7 +11086,7 @@
         <v>6.4477500000000001</v>
       </c>
       <c r="AA28">
-        <v>0.5196422030992397</v>
+        <v>0.51964220309923981</v>
       </c>
       <c r="AB28">
         <v>1</v>
@@ -11124,7 +11124,7 @@
         <v>7.4826089121588932E-2</v>
       </c>
       <c r="M29">
-        <v>0.51802373809858715</v>
+        <v>0.51802373631556919</v>
       </c>
       <c r="N29">
         <v>2</v>
@@ -11198,7 +11198,7 @@
         <v>2.6022369126036119E-2</v>
       </c>
       <c r="M30">
-        <v>0.51768204071839008</v>
+        <v>0.51768203875658458</v>
       </c>
       <c r="N30">
         <v>1</v>
@@ -11272,7 +11272,7 @@
         <v>0.5178308912814702</v>
       </c>
       <c r="M31">
-        <v>0.51666398673946423</v>
+        <v>0.51666398501178112</v>
       </c>
       <c r="N31">
         <v>5</v>
@@ -11346,7 +11346,7 @@
         <v>5.4158290860742669E-2</v>
       </c>
       <c r="M32">
-        <v>0.51416291697889893</v>
+        <v>0.51416291508588241</v>
       </c>
       <c r="N32">
         <v>1</v>
@@ -11382,7 +11382,7 @@
         <v>1.75275</v>
       </c>
       <c r="AA32">
-        <v>0.50951046620072848</v>
+        <v>0.5095104662007286</v>
       </c>
       <c r="AB32">
         <v>4</v>
@@ -11420,7 +11420,7 @@
         <v>4.4999999999999997E-3</v>
       </c>
       <c r="M33">
-        <v>0.5122967179425304</v>
+        <v>0.51229671627177376</v>
       </c>
       <c r="N33">
         <v>3</v>
@@ -11494,7 +11494,7 @@
         <v>2.2499999999999998E-3</v>
       </c>
       <c r="M34">
-        <v>0.50839900822417505</v>
+        <v>0.50839900658157799</v>
       </c>
       <c r="N34">
         <v>4</v>
@@ -11568,7 +11568,7 @@
         <v>0.19613342981186685</v>
       </c>
       <c r="M35">
-        <v>0.50809503989368254</v>
+        <v>0.50809503814926271</v>
       </c>
       <c r="N35">
         <v>5</v>
@@ -11642,7 +11642,7 @@
         <v>0.22376080183780719</v>
       </c>
       <c r="M36">
-        <v>0.50687653797636378</v>
+        <v>0.50687653550277167</v>
       </c>
       <c r="N36">
         <v>2</v>
@@ -11716,7 +11716,7 @@
         <v>0.53138073109704009</v>
       </c>
       <c r="M37">
-        <v>0.50308557555399336</v>
+        <v>0.50308557379360763</v>
       </c>
       <c r="N37">
         <v>3</v>
@@ -11790,7 +11790,7 @@
         <v>3.15E-2</v>
       </c>
       <c r="M38">
-        <v>0.50263063638510508</v>
+        <v>0.50263063460003476</v>
       </c>
       <c r="N38">
         <v>2</v>
@@ -11864,7 +11864,7 @@
         <v>4.7514800476474092E-2</v>
       </c>
       <c r="M39">
-        <v>0.50164954651910421</v>
+        <v>0.50164954457935995</v>
       </c>
       <c r="N39">
         <v>4</v>
@@ -11938,7 +11938,7 @@
         <v>0.58261013658929472</v>
       </c>
       <c r="M40">
-        <v>0.49721380310189695</v>
+        <v>0.49721380158743478</v>
       </c>
       <c r="N40">
         <v>1</v>
@@ -11974,7 +11974,7 @@
         <v>7.3994999999999997</v>
       </c>
       <c r="AA40">
-        <v>0.49854799457889354</v>
+        <v>0.49854799457889365</v>
       </c>
       <c r="AB40">
         <v>5</v>
@@ -12012,7 +12012,7 @@
         <v>1.4103310412418713</v>
       </c>
       <c r="M41">
-        <v>0.49526117533795888</v>
+        <v>0.49526117316867674</v>
       </c>
       <c r="N41">
         <v>5</v>
@@ -12086,7 +12086,7 @@
         <v>3.1777158712621691E-2</v>
       </c>
       <c r="M42">
-        <v>0.49333189635635893</v>
+        <v>0.49333189480777589</v>
       </c>
       <c r="N42">
         <v>1</v>
@@ -12122,7 +12122,7 @@
         <v>10.572749999999999</v>
       </c>
       <c r="AA42">
-        <v>0.49328389891595797</v>
+        <v>0.49328389891595809</v>
       </c>
       <c r="AB42">
         <v>2</v>
@@ -12160,7 +12160,7 @@
         <v>0.12154105680787904</v>
       </c>
       <c r="M43">
-        <v>0.49029857789980918</v>
+        <v>0.49029857584394348</v>
       </c>
       <c r="N43">
         <v>3</v>
@@ -12196,7 +12196,7 @@
         <v>5.3895</v>
       </c>
       <c r="AA43">
-        <v>0.49192590990459817</v>
+        <v>0.49192590990459828</v>
       </c>
       <c r="AB43">
         <v>4</v>
@@ -12234,7 +12234,7 @@
         <v>1.4769327651259936</v>
       </c>
       <c r="M44">
-        <v>0.49029775972664247</v>
+        <v>0.49029775783932267</v>
       </c>
       <c r="N44">
         <v>4</v>
@@ -12308,7 +12308,7 @@
         <v>0.42992878047315958</v>
       </c>
       <c r="M45">
-        <v>0.48888120851052902</v>
+        <v>0.4888812060555327</v>
       </c>
       <c r="N45">
         <v>5</v>
@@ -12344,7 +12344,7 @@
         <v>13.419750000000001</v>
       </c>
       <c r="AA45">
-        <v>0.49030984534725242</v>
+        <v>0.49030984534725253</v>
       </c>
       <c r="AB45">
         <v>1</v>
@@ -12382,7 +12382,7 @@
         <v>0.15062217513649753</v>
       </c>
       <c r="M46">
-        <v>0.48690611103338</v>
+        <v>0.48690610947059254</v>
       </c>
       <c r="N46">
         <v>2</v>
@@ -12456,7 +12456,7 @@
         <v>0.10495781677073947</v>
       </c>
       <c r="M47">
-        <v>0.4829831633515555</v>
+        <v>0.48298316145690012</v>
       </c>
       <c r="N47">
         <v>2</v>
@@ -12530,7 +12530,7 @@
         <v>0.82373844511118677</v>
       </c>
       <c r="M48">
-        <v>0.48056005097918353</v>
+        <v>0.48056004865778706</v>
       </c>
       <c r="N48">
         <v>3</v>
@@ -12604,7 +12604,7 @@
         <v>0.18531537303337869</v>
       </c>
       <c r="M49">
-        <v>0.48014397222581784</v>
+        <v>0.4801439701427177</v>
       </c>
       <c r="N49">
         <v>1</v>
@@ -12678,7 +12678,7 @@
         <v>1.2265045857333658</v>
       </c>
       <c r="M50">
-        <v>0.47676858929142607</v>
+        <v>0.47676858733866129</v>
       </c>
       <c r="N50">
         <v>4</v>
@@ -12752,7 +12752,7 @@
         <v>2.4917989176147417</v>
       </c>
       <c r="M51">
-        <v>0.47505727558780575</v>
+        <v>0.47505727372447054</v>
       </c>
       <c r="N51">
         <v>5</v>
@@ -12826,7 +12826,7 @@
         <v>0.11466764859798757</v>
       </c>
       <c r="M52">
-        <v>0.47340266072611176</v>
+        <v>0.4734026586489532</v>
       </c>
       <c r="N52">
         <v>1</v>
@@ -12900,7 +12900,7 @@
         <v>0.59454532033715324</v>
       </c>
       <c r="M53">
-        <v>0.4725132069329504</v>
+        <v>0.47251320550585951</v>
       </c>
       <c r="N53">
         <v>2</v>
@@ -12974,7 +12974,7 @@
         <v>1.6848355888033599</v>
       </c>
       <c r="M54">
-        <v>0.47124816167197181</v>
+        <v>0.47124815963791317</v>
       </c>
       <c r="N54">
         <v>5</v>
@@ -13048,7 +13048,7 @@
         <v>3.0995803708688152</v>
       </c>
       <c r="M55">
-        <v>0.46989694109562857</v>
+        <v>0.46989693713652458</v>
       </c>
       <c r="N55">
         <v>3</v>
@@ -13122,7 +13122,7 @@
         <v>1.6004943831340317</v>
       </c>
       <c r="M56">
-        <v>0.46952098409179838</v>
+        <v>0.4695209825618939</v>
       </c>
       <c r="N56">
         <v>4</v>
@@ -13196,7 +13196,7 @@
         <v>0.29461628629302539</v>
       </c>
       <c r="M57">
-        <v>0.46482703081783788</v>
+        <v>0.4648270288621571</v>
       </c>
       <c r="N57">
         <v>4</v>
@@ -13270,7 +13270,7 @@
         <v>0.8176387997537985</v>
       </c>
       <c r="M58">
-        <v>0.4630245219062023</v>
+        <v>0.46302452073426698</v>
       </c>
       <c r="N58">
         <v>3</v>
@@ -13306,7 +13306,7 @@
         <v>33.202500000000001</v>
       </c>
       <c r="AA58">
-        <v>0.45931852213053248</v>
+        <v>0.45931852213053254</v>
       </c>
       <c r="AB58">
         <v>1</v>
@@ -13344,7 +13344,7 @@
         <v>1.9710593733284539E-3</v>
       </c>
       <c r="M59">
-        <v>0.46063109886607562</v>
+        <v>0.46063109716214851</v>
       </c>
       <c r="N59">
         <v>1</v>
@@ -13418,7 +13418,7 @@
         <v>5.2695579272349823E-2</v>
       </c>
       <c r="M60">
-        <v>0.46023937471730869</v>
+        <v>0.4602393738252113</v>
       </c>
       <c r="N60">
         <v>2</v>
@@ -13492,7 +13492,7 @@
         <v>0.90256809286008455</v>
       </c>
       <c r="M61">
-        <v>0.4497869068337233</v>
+        <v>0.44978690417335143</v>
       </c>
       <c r="N61">
         <v>1</v>
@@ -13566,7 +13566,7 @@
         <v>0.11300996309963099</v>
       </c>
       <c r="M62">
-        <v>0.4461077590592073</v>
+        <v>0.44610775744460968</v>
       </c>
       <c r="N62">
         <v>2</v>
@@ -13640,7 +13640,7 @@
         <v>0.36525007446492724</v>
       </c>
       <c r="M63">
-        <v>0.44208309388787304</v>
+        <v>0.4420830921266683</v>
       </c>
       <c r="N63">
         <v>4</v>
@@ -13676,7 +13676,7 @@
         <v>15.98325</v>
       </c>
       <c r="AA63">
-        <v>0.44872020993744899</v>
+        <v>0.44872020993744904</v>
       </c>
       <c r="AB63">
         <v>1</v>
@@ -13714,7 +13714,7 @@
         <v>0.74459622039583273</v>
       </c>
       <c r="M64">
-        <v>0.43915965085013747</v>
+        <v>0.43915964917317218</v>
       </c>
       <c r="N64">
         <v>5</v>
@@ -13750,7 +13750,7 @@
         <v>23.565000000000001</v>
       </c>
       <c r="AA64">
-        <v>0.44871312657382378</v>
+        <v>0.44871312657382384</v>
       </c>
       <c r="AB64">
         <v>3</v>
@@ -13788,7 +13788,7 @@
         <v>0.53303670001957426</v>
       </c>
       <c r="M65">
-        <v>0.43847879401799411</v>
+        <v>0.438478792247192</v>
       </c>
       <c r="N65">
         <v>3</v>
@@ -13862,7 +13862,7 @@
         <v>0.22128008233237467</v>
       </c>
       <c r="M66">
-        <v>0.43578751124735349</v>
+        <v>0.43578750933175442</v>
       </c>
       <c r="N66">
         <v>1</v>
@@ -13936,7 +13936,7 @@
         <v>0.28153144564758098</v>
       </c>
       <c r="M67">
-        <v>0.43505169839367769</v>
+        <v>0.43505169655694698</v>
       </c>
       <c r="N67">
         <v>2</v>
@@ -14010,7 +14010,7 @@
         <v>1.8997664463978698</v>
       </c>
       <c r="M68">
-        <v>0.43433945366977866</v>
+        <v>0.43433945100479587</v>
       </c>
       <c r="N68">
         <v>3</v>
@@ -14084,7 +14084,7 @@
         <v>0.27653124396368556</v>
       </c>
       <c r="M69">
-        <v>0.43371675735497722</v>
+        <v>0.43371675562047302</v>
       </c>
       <c r="N69">
         <v>5</v>
@@ -14158,7 +14158,7 @@
         <v>0.13142347987018213</v>
       </c>
       <c r="M70">
-        <v>0.43291053414887692</v>
+        <v>0.43291053250140632</v>
       </c>
       <c r="N70">
         <v>1</v>
@@ -14232,7 +14232,7 @@
         <v>1.0689782317861916</v>
       </c>
       <c r="M71">
-        <v>0.42933129636552692</v>
+        <v>0.42933129492650407</v>
       </c>
       <c r="N71">
         <v>4</v>
@@ -14306,7 +14306,7 @@
         <v>2.4128965897522905E-2</v>
       </c>
       <c r="M72">
-        <v>0.42801731600338161</v>
+        <v>0.42801731398789794</v>
       </c>
       <c r="N72">
         <v>2</v>
@@ -14380,7 +14380,7 @@
         <v>2.0091113564593694</v>
       </c>
       <c r="M73">
-        <v>0.42388794346433362</v>
+        <v>0.42388793819588405</v>
       </c>
       <c r="N73">
         <v>2</v>
@@ -14454,7 +14454,7 @@
         <v>0.85180160279356099</v>
       </c>
       <c r="M74">
-        <v>0.42264791232416343</v>
+        <v>0.42264791052742917</v>
       </c>
       <c r="N74">
         <v>3</v>
@@ -14490,7 +14490,7 @@
         <v>27.7395</v>
       </c>
       <c r="AA74">
-        <v>0.42917983834286771</v>
+        <v>0.42917983834286777</v>
       </c>
       <c r="AB74">
         <v>1</v>
@@ -14528,7 +14528,7 @@
         <v>0.70764985793773971</v>
       </c>
       <c r="M75">
-        <v>0.42155992500423922</v>
+        <v>0.42155992340498916</v>
       </c>
       <c r="N75">
         <v>1</v>
@@ -14564,7 +14564,7 @@
         <v>12.3375</v>
       </c>
       <c r="AA75">
-        <v>0.42887881886214896</v>
+        <v>0.42887881886214901</v>
       </c>
       <c r="AB75">
         <v>5</v>
@@ -14602,7 +14602,7 @@
         <v>1.2435427916038644</v>
       </c>
       <c r="M76">
-        <v>0.41847934253087088</v>
+        <v>0.41847934132225179</v>
       </c>
       <c r="N76">
         <v>4</v>
@@ -14676,7 +14676,7 @@
         <v>2.7039872535201912</v>
       </c>
       <c r="M77">
-        <v>0.41651685743024153</v>
+        <v>0.41651685583599279</v>
       </c>
       <c r="N77">
         <v>5</v>
@@ -14750,7 +14750,7 @@
         <v>1.7723187021516222</v>
       </c>
       <c r="M78">
-        <v>0.41364405387979181</v>
+        <v>0.41364405211883598</v>
       </c>
       <c r="N78">
         <v>3</v>
@@ -14824,7 +14824,7 @@
         <v>0.37949606932741459</v>
       </c>
       <c r="M79">
-        <v>0.41236474975043003</v>
+        <v>0.41236474796330491</v>
       </c>
       <c r="N79">
         <v>5</v>
@@ -14898,7 +14898,7 @@
         <v>2.0621507565169835E-2</v>
       </c>
       <c r="M80">
-        <v>0.40971341737243722</v>
+        <v>0.40971341560996466</v>
       </c>
       <c r="N80">
         <v>1</v>
@@ -14972,7 +14972,7 @@
         <v>1.35E-2</v>
       </c>
       <c r="M81">
-        <v>0.40921358702712241</v>
+        <v>0.40921358491542165</v>
       </c>
       <c r="N81">
         <v>2</v>
@@ -15046,7 +15046,7 @@
         <v>0.95447583749955289</v>
       </c>
       <c r="M82">
-        <v>0.40909045524908572</v>
+        <v>0.40909045266366428</v>
       </c>
       <c r="N82">
         <v>4</v>
@@ -15082,7 +15082,7 @@
         <v>23.5365</v>
       </c>
       <c r="AA82">
-        <v>0.41242577093734001</v>
+        <v>0.41242577093734006</v>
       </c>
       <c r="AB82">
         <v>4</v>
@@ -15120,7 +15120,7 @@
         <v>0.24578598659906373</v>
       </c>
       <c r="M83">
-        <v>0.40467167364390899</v>
+        <v>0.4046716720250596</v>
       </c>
       <c r="N83">
         <v>3</v>
@@ -15194,7 +15194,7 @@
         <v>2.9653905432237209</v>
       </c>
       <c r="M84">
-        <v>0.40180676346943711</v>
+        <v>0.40180676163006768</v>
       </c>
       <c r="N84">
         <v>4</v>
@@ -15268,7 +15268,7 @@
         <v>0.90034838117554128</v>
       </c>
       <c r="M85">
-        <v>0.39891332798519957</v>
+        <v>0.398913326703215</v>
       </c>
       <c r="N85">
         <v>5</v>
@@ -15342,7 +15342,7 @@
         <v>9.8359732433029382E-3</v>
       </c>
       <c r="M86">
-        <v>0.39603733138824676</v>
+        <v>0.39603732915294398</v>
       </c>
       <c r="N86">
         <v>1</v>
@@ -15416,7 +15416,7 @@
         <v>2.4903689906946069</v>
       </c>
       <c r="M87">
-        <v>0.39520425094784362</v>
+        <v>0.39520424811094879</v>
       </c>
       <c r="N87">
         <v>2</v>
@@ -15490,7 +15490,7 @@
         <v>0.21399296827931075</v>
       </c>
       <c r="M88">
-        <v>0.39352960808118442</v>
+        <v>0.39352960622992877</v>
       </c>
       <c r="N88">
         <v>5</v>
@@ -15526,7 +15526,7 @@
         <v>6.2175000000000002</v>
       </c>
       <c r="AA88">
-        <v>0.40006361029924836</v>
+        <v>0.40006361029924853</v>
       </c>
       <c r="AB88">
         <v>5</v>
@@ -15564,7 +15564,7 @@
         <v>1.8845500496508163</v>
       </c>
       <c r="M89">
-        <v>0.39201760513407369</v>
+        <v>0.39201760386005902</v>
       </c>
       <c r="N89">
         <v>4</v>
@@ -15600,7 +15600,7 @@
         <v>19.062000000000001</v>
       </c>
       <c r="AA89">
-        <v>0.39988477686082979</v>
+        <v>0.39988477686082985</v>
       </c>
       <c r="AB89">
         <v>3</v>
@@ -15638,7 +15638,7 @@
         <v>4.461216164696074</v>
       </c>
       <c r="M90">
-        <v>0.39174634138855119</v>
+        <v>0.39174633485623905</v>
       </c>
       <c r="N90">
         <v>2</v>
@@ -15712,7 +15712,7 @@
         <v>0.44128583926652898</v>
       </c>
       <c r="M91">
-        <v>0.39107907603408532</v>
+        <v>0.39107907456827129</v>
       </c>
       <c r="N91">
         <v>1</v>
@@ -15748,7 +15748,7 @@
         <v>8.6932500000000008</v>
       </c>
       <c r="AA91">
-        <v>0.39344675224306835</v>
+        <v>0.39344675224306841</v>
       </c>
       <c r="AB91">
         <v>2</v>
@@ -15786,7 +15786,7 @@
         <v>4.2483873092081836</v>
       </c>
       <c r="M92">
-        <v>0.39019783739591485</v>
+        <v>0.39019783424238574</v>
       </c>
       <c r="N92">
         <v>3</v>
@@ -15860,7 +15860,7 @@
         <v>1.7650676148849338</v>
       </c>
       <c r="M93">
-        <v>0.37741178945933029</v>
+        <v>0.37741178771454048</v>
       </c>
       <c r="N93">
         <v>1</v>
@@ -15934,7 +15934,7 @@
         <v>1.1256529791632151</v>
       </c>
       <c r="M94">
-        <v>0.37396056591114812</v>
+        <v>0.37396056487023421</v>
       </c>
       <c r="N94">
         <v>3</v>
@@ -16008,7 +16008,7 @@
         <v>1.3963773578316945</v>
       </c>
       <c r="M95">
-        <v>0.37272068478616532</v>
+        <v>0.37272068086972127</v>
       </c>
       <c r="N95">
         <v>2</v>
@@ -16082,7 +16082,7 @@
         <v>1.524499516573004</v>
       </c>
       <c r="M96">
-        <v>0.37116737891681439</v>
+        <v>0.37116737760427537</v>
       </c>
       <c r="N96">
         <v>1</v>
@@ -16156,7 +16156,7 @@
         <v>4.3449367384098228E-2</v>
       </c>
       <c r="M97">
-        <v>0.36359227191351912</v>
+        <v>0.3635922706372916</v>
       </c>
       <c r="N97">
         <v>4</v>
@@ -16230,7 +16230,7 @@
         <v>3.3621421559339422</v>
       </c>
       <c r="M98">
-        <v>0.36190443426986207</v>
+        <v>0.36190443196342476</v>
       </c>
       <c r="N98">
         <v>1</v>
@@ -16266,7 +16266,7 @@
         <v>12.579750000000001</v>
       </c>
       <c r="AA98">
-        <v>0.37975983977368127</v>
+        <v>0.37975983977368133</v>
       </c>
       <c r="AB98">
         <v>3</v>
@@ -16304,7 +16304,7 @@
         <v>2.4701877958373588</v>
       </c>
       <c r="M99">
-        <v>0.3600782440314329</v>
+        <v>0.3600782433118877</v>
       </c>
       <c r="N99">
         <v>2</v>
@@ -16378,7 +16378,7 @@
         <v>2.1785098423168092</v>
       </c>
       <c r="M100">
-        <v>0.35832337378710699</v>
+        <v>0.35832337216720572</v>
       </c>
       <c r="N100">
         <v>3</v>
@@ -16452,7 +16452,7 @@
         <v>0.56335468679468526</v>
       </c>
       <c r="M101">
-        <v>0.3561605897266148</v>
+        <v>0.3561605879600041</v>
       </c>
       <c r="N101">
         <v>5</v>
@@ -16526,7 +16526,7 @@
         <v>0.50502757057188818</v>
       </c>
       <c r="M102">
-        <v>0.3528594272743385</v>
+        <v>0.352859425364908</v>
       </c>
       <c r="N102">
         <v>3</v>
@@ -16600,7 +16600,7 @@
         <v>0.73178766612719792</v>
       </c>
       <c r="M103">
-        <v>0.35238892107842351</v>
+        <v>0.35238891977962761</v>
       </c>
       <c r="N103">
         <v>5</v>
@@ -16674,7 +16674,7 @@
         <v>0.46035808007998508</v>
       </c>
       <c r="M104">
-        <v>0.35144960385110119</v>
+        <v>0.35144960266159431</v>
       </c>
       <c r="N104">
         <v>4</v>
@@ -16748,7 +16748,7 @@
         <v>0.49768682212704912</v>
       </c>
       <c r="M105">
-        <v>0.35073727150259759</v>
+        <v>0.35073727061166515</v>
       </c>
       <c r="N105">
         <v>1</v>
@@ -16822,7 +16822,7 @@
         <v>0.68281567437193502</v>
       </c>
       <c r="M106">
-        <v>0.34986851542082925</v>
+        <v>0.3498685138066509</v>
       </c>
       <c r="N106">
         <v>2</v>
@@ -16896,7 +16896,7 @@
         <v>2.6358605361198815</v>
       </c>
       <c r="M107">
-        <v>0.34453191309095799</v>
+        <v>0.3445319108948981</v>
       </c>
       <c r="N107">
         <v>1</v>
@@ -16970,7 +16970,7 @@
         <v>1.082021228437626</v>
       </c>
       <c r="M108">
-        <v>0.3435774552745246</v>
+        <v>0.34357745415483909</v>
       </c>
       <c r="N108">
         <v>3</v>
@@ -17044,7 +17044,7 @@
         <v>1.1916317680459974</v>
       </c>
       <c r="M109">
-        <v>0.33909339165080932</v>
+        <v>0.33909339033526548</v>
       </c>
       <c r="N109">
         <v>2</v>
@@ -17118,7 +17118,7 @@
         <v>8.0749243920253205E-2</v>
       </c>
       <c r="M110">
-        <v>0.33583868224971108</v>
+        <v>0.3358386809099897</v>
       </c>
       <c r="N110">
         <v>4</v>
@@ -17154,7 +17154,7 @@
         <v>3.9075000000000002</v>
       </c>
       <c r="AA110">
-        <v>0.35546102906482968</v>
+        <v>0.35546102906482974</v>
       </c>
       <c r="AB110">
         <v>4</v>
@@ -17192,7 +17192,7 @@
         <v>3.9567729542332599</v>
       </c>
       <c r="M111">
-        <v>0.33570005222980392</v>
+        <v>0.3357000508607037</v>
       </c>
       <c r="N111">
         <v>5</v>
@@ -17266,7 +17266,7 @@
         <v>2.5871512527835279</v>
       </c>
       <c r="M112">
-        <v>0.33220245354937217</v>
+        <v>0.3322024519474604</v>
       </c>
       <c r="N112">
         <v>2</v>
@@ -17340,7 +17340,7 @@
         <v>4.119883941947327</v>
       </c>
       <c r="M113">
-        <v>0.33121075513174725</v>
+        <v>0.33121075392189014</v>
       </c>
       <c r="N113">
         <v>3</v>
@@ -17376,7 +17376,7 @@
         <v>16.351500000000001</v>
       </c>
       <c r="AA113">
-        <v>0.34968676205364552</v>
+        <v>0.34968676205364557</v>
       </c>
       <c r="AB113">
         <v>2</v>
@@ -17414,7 +17414,7 @@
         <v>5.9616437511257114</v>
       </c>
       <c r="M114">
-        <v>0.32841498955297116</v>
+        <v>0.32841498785522849</v>
       </c>
       <c r="N114">
         <v>1</v>
@@ -17488,7 +17488,7 @@
         <v>0.5701796104853627</v>
       </c>
       <c r="M115">
-        <v>0.32800522313494851</v>
+        <v>0.32800522140882299</v>
       </c>
       <c r="N115">
         <v>5</v>
@@ -17524,7 +17524,7 @@
         <v>11.33175</v>
       </c>
       <c r="AA115">
-        <v>0.34728432576663976</v>
+        <v>0.34728432576663981</v>
       </c>
       <c r="AB115">
         <v>3</v>
@@ -17562,7 +17562,7 @@
         <v>5.0778765825359748</v>
       </c>
       <c r="M116">
-        <v>0.32783524946143322</v>
+        <v>0.32783524773038042</v>
       </c>
       <c r="N116">
         <v>4</v>
@@ -17636,7 +17636,7 @@
         <v>1.930026452811612</v>
       </c>
       <c r="M117">
-        <v>0.32326834091886941</v>
+        <v>0.32326833877152161</v>
       </c>
       <c r="N117">
         <v>3</v>
@@ -17710,7 +17710,7 @@
         <v>0.12655475198691574</v>
       </c>
       <c r="M118">
-        <v>0.32325845475265869</v>
+        <v>0.3232584531471534</v>
       </c>
       <c r="N118">
         <v>2</v>
@@ -17784,7 +17784,7 @@
         <v>2.6988006975839571</v>
       </c>
       <c r="M119">
-        <v>0.32139424439932041</v>
+        <v>0.3213942427507594</v>
       </c>
       <c r="N119">
         <v>1</v>
@@ -17820,7 +17820,7 @@
         <v>0.22875000000000001</v>
       </c>
       <c r="AA119">
-        <v>0.34053474530620526</v>
+        <v>0.34053474530620531</v>
       </c>
       <c r="AB119">
         <v>4</v>
@@ -17858,7 +17858,7 @@
         <v>2.9591079046712392</v>
       </c>
       <c r="M120">
-        <v>0.31680968880793048</v>
+        <v>0.31680968744336269</v>
       </c>
       <c r="N120">
         <v>4</v>
@@ -17932,7 +17932,7 @@
         <v>1.7085874251497006</v>
       </c>
       <c r="M121">
-        <v>0.31593895307014741</v>
+        <v>0.31593895176432329</v>
       </c>
       <c r="N121">
         <v>5</v>
@@ -18006,7 +18006,7 @@
         <v>2.7805279496200139</v>
       </c>
       <c r="M122">
-        <v>0.31284042189855682</v>
+        <v>0.31284041988922207</v>
       </c>
       <c r="N122">
         <v>4</v>
@@ -18042,7 +18042,7 @@
         <v>11.87175</v>
       </c>
       <c r="AA122">
-        <v>0.33074804025182636</v>
+        <v>0.33074804025182641</v>
       </c>
       <c r="AB122">
         <v>2</v>
@@ -18080,7 +18080,7 @@
         <v>7.4794605676373838</v>
       </c>
       <c r="M123">
-        <v>0.31259262208011729</v>
+        <v>0.31259261900875757</v>
       </c>
       <c r="N123">
         <v>2</v>
@@ -18154,7 +18154,7 @@
         <v>2.3327571098192692</v>
       </c>
       <c r="M124">
-        <v>0.31100787093112386</v>
+        <v>0.31100786982952766</v>
       </c>
       <c r="N124">
         <v>3</v>
@@ -18228,7 +18228,7 @@
         <v>8.9899915474857703</v>
       </c>
       <c r="M125">
-        <v>0.31034085738927747</v>
+        <v>0.31034085620175672</v>
       </c>
       <c r="N125">
         <v>1</v>
@@ -18264,7 +18264,7 @@
         <v>15.195</v>
       </c>
       <c r="AA125">
-        <v>0.32692883121810473</v>
+        <v>0.32692883121810484</v>
       </c>
       <c r="AB125">
         <v>1</v>
@@ -18302,7 +18302,7 @@
         <v>3.6231690229201132</v>
       </c>
       <c r="M126">
-        <v>0.30786894951753696</v>
+        <v>0.30786894777638102</v>
       </c>
       <c r="N126">
         <v>5</v>
@@ -18376,7 +18376,7 @@
         <v>3.8954162920336874</v>
       </c>
       <c r="M127">
-        <v>0.30404009189792658</v>
+        <v>0.30404009098386409</v>
       </c>
       <c r="N127">
         <v>1</v>
@@ -18450,7 +18450,7 @@
         <v>3.5767080790118708</v>
       </c>
       <c r="M128">
-        <v>0.30247130311977388</v>
+        <v>0.30247130301996056</v>
       </c>
       <c r="N128">
         <v>3</v>
@@ -18524,7 +18524,7 @@
         <v>2.2565906747040452</v>
       </c>
       <c r="M129">
-        <v>0.3008540584096499</v>
+        <v>0.3008540577361366</v>
       </c>
       <c r="N129">
         <v>4</v>
@@ -18598,7 +18598,7 @@
         <v>3.4518234842133215</v>
       </c>
       <c r="M130">
-        <v>0.29597343440273338</v>
+        <v>0.29597343378227459</v>
       </c>
       <c r="N130">
         <v>2</v>
@@ -18634,7 +18634,7 @@
         <v>11.89875</v>
       </c>
       <c r="AA130">
-        <v>0.31742233028817318</v>
+        <v>0.31742233028817329</v>
       </c>
       <c r="AB130">
         <v>3</v>
@@ -18672,7 +18672,7 @@
         <v>1.1062575258439435</v>
       </c>
       <c r="M131">
-        <v>0.29568926542758428</v>
+        <v>0.2956892640538441</v>
       </c>
       <c r="N131">
         <v>5</v>
@@ -18708,7 +18708,7 @@
         <v>0.14549999999999999</v>
       </c>
       <c r="AA131">
-        <v>0.31448244678979892</v>
+        <v>0.31448244678979898</v>
       </c>
       <c r="AB131">
         <v>5</v>
@@ -18746,7 +18746,7 @@
         <v>4.437106180443541</v>
       </c>
       <c r="M132">
-        <v>0.29369009043473132</v>
+        <v>0.2936900883485819</v>
       </c>
       <c r="N132">
         <v>3</v>
@@ -18782,7 +18782,7 @@
         <v>10.6485</v>
       </c>
       <c r="AA132">
-        <v>0.31332707420040312</v>
+        <v>0.31332707420040318</v>
       </c>
       <c r="AB132">
         <v>1</v>
@@ -18820,7 +18820,7 @@
         <v>0.93355957980274695</v>
       </c>
       <c r="M133">
-        <v>0.29348791386184808</v>
+        <v>0.29348791192136059</v>
       </c>
       <c r="N133">
         <v>2</v>
@@ -18894,7 +18894,7 @@
         <v>2.7631101955952566</v>
       </c>
       <c r="M134">
-        <v>0.29159868375129949</v>
+        <v>0.29159868231099279</v>
       </c>
       <c r="N134">
         <v>1</v>
@@ -18968,7 +18968,7 @@
         <v>2.9776716498520166</v>
       </c>
       <c r="M135">
-        <v>0.28994650655547199</v>
+        <v>0.28994650447041431</v>
       </c>
       <c r="N135">
         <v>4</v>
@@ -19042,7 +19042,7 @@
         <v>2.0870442206855278</v>
       </c>
       <c r="M136">
-        <v>0.28590023740774501</v>
+        <v>0.28590023553949229</v>
       </c>
       <c r="N136">
         <v>5</v>
@@ -19116,7 +19116,7 @@
         <v>5.722897504749815</v>
       </c>
       <c r="M137">
-        <v>0.28341917230727609</v>
+        <v>0.28341917080567991</v>
       </c>
       <c r="N137">
         <v>5</v>
@@ -19190,7 +19190,7 @@
         <v>4.5833316817825649</v>
       </c>
       <c r="M138">
-        <v>0.28208366265702323</v>
+        <v>0.28208366132717488</v>
       </c>
       <c r="N138">
         <v>2</v>
@@ -19264,7 +19264,7 @@
         <v>10.630714018160289</v>
       </c>
       <c r="M139">
-        <v>0.27867653356769356</v>
+        <v>0.27867653372585527</v>
       </c>
       <c r="N139">
         <v>1</v>
@@ -19338,7 +19338,7 @@
         <v>3.6734431712540059</v>
       </c>
       <c r="M140">
-        <v>0.27734536748646399</v>
+        <v>0.27734536611835942</v>
       </c>
       <c r="N140">
         <v>4</v>
@@ -19412,7 +19412,7 @@
         <v>5.5733807879342114</v>
       </c>
       <c r="M141">
-        <v>0.27594812737375835</v>
+        <v>0.27594812569145039</v>
       </c>
       <c r="N141">
         <v>3</v>
@@ -19486,7 +19486,7 @@
         <v>2.8457638428070613</v>
       </c>
       <c r="M142">
-        <v>0.27470069827435017</v>
+        <v>0.2747006968552031</v>
       </c>
       <c r="N142">
         <v>2</v>
@@ -19560,7 +19560,7 @@
         <v>0.90122894461234171</v>
       </c>
       <c r="M143">
-        <v>0.27153669155949578</v>
+        <v>0.27153668975141487</v>
       </c>
       <c r="N143">
         <v>1</v>
@@ -19596,7 +19596,7 @@
         <v>8.4292499999999997</v>
       </c>
       <c r="AA143">
-        <v>0.2911971442395383</v>
+        <v>0.29119714423953835</v>
       </c>
       <c r="AB143">
         <v>2</v>
@@ -19634,7 +19634,7 @@
         <v>4.3569049883085933</v>
       </c>
       <c r="M144">
-        <v>0.26305990459512235</v>
+        <v>0.26305990305294097</v>
       </c>
       <c r="N144">
         <v>4</v>
@@ -19708,7 +19708,7 @@
         <v>3.3075384822560077</v>
       </c>
       <c r="M145">
-        <v>0.25947817077488761</v>
+        <v>0.25947816923736483</v>
       </c>
       <c r="N145">
         <v>5</v>
@@ -19782,7 +19782,7 @@
         <v>9.6271409913150343</v>
       </c>
       <c r="M146">
-        <v>0.25863236619737145</v>
+        <v>0.25863236520772315</v>
       </c>
       <c r="N146">
         <v>1</v>
@@ -19856,7 +19856,7 @@
         <v>8.2601013176025404</v>
       </c>
       <c r="M147">
-        <v>0.25814559964518058</v>
+        <v>0.25814559353640942</v>
       </c>
       <c r="N147">
         <v>2</v>
@@ -19892,7 +19892,7 @@
         <v>2.0250000000000001E-2</v>
       </c>
       <c r="AA147">
-        <v>0.28053708416978951</v>
+        <v>0.28053708416978962</v>
       </c>
       <c r="AB147">
         <v>5</v>
@@ -19930,7 +19930,7 @@
         <v>7.1824859810313901</v>
       </c>
       <c r="M148">
-        <v>0.25722598545515429</v>
+        <v>0.25722598747093373</v>
       </c>
       <c r="N148">
         <v>3</v>
@@ -20004,7 +20004,7 @@
         <v>4.9585909575093545</v>
       </c>
       <c r="M149">
-        <v>0.25423997315365521</v>
+        <v>0.25423997146191413</v>
       </c>
       <c r="N149">
         <v>3</v>
@@ -20040,7 +20040,7 @@
         <v>4.0949999999999998</v>
       </c>
       <c r="AA149">
-        <v>0.27746408789986621</v>
+        <v>0.27746408789986632</v>
       </c>
       <c r="AB149">
         <v>2</v>
@@ -20078,7 +20078,7 @@
         <v>4.985714889357741</v>
       </c>
       <c r="M150">
-        <v>0.25207161957122692</v>
+        <v>0.25207162079307699</v>
       </c>
       <c r="N150">
         <v>1</v>
@@ -20114,7 +20114,7 @@
         <v>4.1204999999999998</v>
       </c>
       <c r="AA150">
-        <v>0.27579776453797028</v>
+        <v>0.27579776453797039</v>
       </c>
       <c r="AB150">
         <v>3</v>
@@ -20152,7 +20152,7 @@
         <v>3.7861485725941537</v>
       </c>
       <c r="M151">
-        <v>0.247501930426336</v>
+        <v>0.24750192807970139</v>
       </c>
       <c r="N151">
         <v>2</v>
@@ -20226,7 +20226,7 @@
         <v>8.0612876583840354</v>
       </c>
       <c r="M152">
-        <v>0.242540680747937</v>
+        <v>0.24254068087816927</v>
       </c>
       <c r="N152">
         <v>2</v>
@@ -20300,7 +20300,7 @@
         <v>3.2878265610237882</v>
       </c>
       <c r="M153">
-        <v>0.24151290534391567</v>
+        <v>0.24151290389292263</v>
       </c>
       <c r="N153">
         <v>5</v>
@@ -20336,7 +20336,7 @@
         <v>2.5852499999999998</v>
       </c>
       <c r="AA153">
-        <v>0.27012710394010869</v>
+        <v>0.2701271039401088</v>
       </c>
       <c r="AB153">
         <v>5</v>
@@ -20374,7 +20374,7 @@
         <v>10.077370647160729</v>
       </c>
       <c r="M154">
-        <v>0.23818515310754351</v>
+        <v>0.238185153808397</v>
       </c>
       <c r="N154">
         <v>1</v>
@@ -20448,7 +20448,7 @@
         <v>3.1126561605319103</v>
       </c>
       <c r="M155">
-        <v>0.23812978056304623</v>
+        <v>0.23812977928303386</v>
       </c>
       <c r="N155">
         <v>3</v>
@@ -20522,7 +20522,7 @@
         <v>2.2587529068002055</v>
       </c>
       <c r="M156">
-        <v>0.2350989057003342</v>
+        <v>0.2350989044451679</v>
       </c>
       <c r="N156">
         <v>4</v>
@@ -20596,7 +20596,7 @@
         <v>4.224073117148845</v>
       </c>
       <c r="M157">
-        <v>0.23335159644867851</v>
+        <v>0.23335159408114409</v>
       </c>
       <c r="N157">
         <v>2</v>
@@ -20632,7 +20632,7 @@
         <v>0.90300000000000002</v>
       </c>
       <c r="AA157">
-        <v>0.26287322884907061</v>
+        <v>0.26287322884907072</v>
       </c>
       <c r="AB157">
         <v>5</v>
@@ -20670,7 +20670,7 @@
         <v>2.1161785771130592</v>
       </c>
       <c r="M158">
-        <v>0.22955991431958619</v>
+        <v>0.22955991365633641</v>
       </c>
       <c r="N158">
         <v>5</v>
@@ -20744,7 +20744,7 @@
         <v>3.1387112373653965</v>
       </c>
       <c r="M159">
-        <v>0.22908245738783839</v>
+        <v>0.22908245603667929</v>
       </c>
       <c r="N159">
         <v>4</v>
@@ -20780,7 +20780,7 @@
         <v>1.851</v>
       </c>
       <c r="AA159">
-        <v>0.25985309495928388</v>
+        <v>0.25985309495928399</v>
       </c>
       <c r="AB159">
         <v>3</v>
@@ -20818,7 +20818,7 @@
         <v>3.477658910741301</v>
       </c>
       <c r="M160">
-        <v>0.2277579635590582</v>
+        <v>0.22775796334751691</v>
       </c>
       <c r="N160">
         <v>1</v>
@@ -20892,7 +20892,7 @@
         <v>2.1208173359511084</v>
       </c>
       <c r="M161">
-        <v>0.22651613048957131</v>
+        <v>0.2265161297061683</v>
       </c>
       <c r="N161">
         <v>3</v>
@@ -20966,7 +20966,7 @@
         <v>3.5532255555321965</v>
       </c>
       <c r="M162">
-        <v>0.2229381655813526</v>
+        <v>0.22293816440061759</v>
       </c>
       <c r="N162">
         <v>5</v>
@@ -21040,7 +21040,7 @@
         <v>9.7340080572413132</v>
       </c>
       <c r="M163">
-        <v>0.22102121186859752</v>
+        <v>0.22102121163527019</v>
       </c>
       <c r="N163">
         <v>1</v>
@@ -21076,7 +21076,7 @@
         <v>4.6612499999999999</v>
       </c>
       <c r="AA163">
-        <v>0.24814616567261744</v>
+        <v>0.24814616567261752</v>
       </c>
       <c r="AB163">
         <v>1</v>
@@ -21114,7 +21114,7 @@
         <v>1.7245071966171635</v>
       </c>
       <c r="M164">
-        <v>0.22001393540959741</v>
+        <v>0.2200139341684374</v>
       </c>
       <c r="N164">
         <v>2</v>
@@ -21188,7 +21188,7 @@
         <v>2.8901556673866517</v>
       </c>
       <c r="M165">
-        <v>0.21716418578518851</v>
+        <v>0.21716418312981281</v>
       </c>
       <c r="N165">
         <v>4</v>
@@ -21262,7 +21262,7 @@
         <v>9.0870978275099734</v>
       </c>
       <c r="M166">
-        <v>0.21627570040274063</v>
+        <v>0.21627569919583664</v>
       </c>
       <c r="N166">
         <v>3</v>
@@ -21336,7 +21336,7 @@
         <v>7.2584667467183186</v>
       </c>
       <c r="M167">
-        <v>0.21137914563506557</v>
+        <v>0.21137914396477206</v>
       </c>
       <c r="N167">
         <v>2</v>
@@ -21410,7 +21410,7 @@
         <v>7.4979945197514937</v>
       </c>
       <c r="M168">
-        <v>0.21111769489021798</v>
+        <v>0.21111769384812093</v>
       </c>
       <c r="N168">
         <v>5</v>
@@ -21484,7 +21484,7 @@
         <v>14.03247459712129</v>
       </c>
       <c r="M169">
-        <v>0.21048989813022959</v>
+        <v>0.21048989708397303</v>
       </c>
       <c r="N169">
         <v>1</v>
@@ -21520,7 +21520,7 @@
         <v>0.94199999999999995</v>
       </c>
       <c r="AA169">
-        <v>0.2364907186592401</v>
+        <v>0.23649071865924021</v>
       </c>
       <c r="AB169">
         <v>1</v>
@@ -21558,7 +21558,7 @@
         <v>7.8760900973950845</v>
       </c>
       <c r="M170">
-        <v>0.21012809909906782</v>
+        <v>0.21012809807607086</v>
       </c>
       <c r="N170">
         <v>4</v>
@@ -21632,7 +21632,7 @@
         <v>6.3935145495631582</v>
       </c>
       <c r="M171">
-        <v>0.20938731211989858</v>
+        <v>0.20938731077514613</v>
       </c>
       <c r="N171">
         <v>3</v>
@@ -21706,7 +21706,7 @@
         <v>5.2687756283486227</v>
       </c>
       <c r="M172">
-        <v>0.20184708427786169</v>
+        <v>0.20184708240149971</v>
       </c>
       <c r="N172">
         <v>1</v>
@@ -21742,7 +21742,7 @@
         <v>0.22425</v>
       </c>
       <c r="AA172">
-        <v>0.23064511722691161</v>
+        <v>0.23064511722691169</v>
       </c>
       <c r="AB172">
         <v>1</v>
@@ -21780,7 +21780,7 @@
         <v>2.5288703397139125</v>
       </c>
       <c r="M173">
-        <v>0.2011788731561634</v>
+        <v>0.20117887210952479</v>
       </c>
       <c r="N173">
         <v>3</v>
@@ -21854,7 +21854,7 @@
         <v>2.9083431654821106</v>
       </c>
       <c r="M174">
-        <v>0.19750062325734599</v>
+        <v>0.19750062237912569</v>
       </c>
       <c r="N174">
         <v>2</v>
@@ -21890,7 +21890,7 @@
         <v>8.2500000000000004E-2</v>
       </c>
       <c r="AA174">
-        <v>0.22530914389037693</v>
+        <v>0.22530914389037701</v>
       </c>
       <c r="AB174">
         <v>2</v>
@@ -21928,7 +21928,7 @@
         <v>7.4334898806643936</v>
       </c>
       <c r="M175">
-        <v>0.19298667137883921</v>
+        <v>0.19298666986359936</v>
       </c>
       <c r="N175">
         <v>2</v>
@@ -21964,7 +21964,7 @@
         <v>2.8500000000000001E-2</v>
       </c>
       <c r="AA175">
-        <v>0.22336141223414879</v>
+        <v>0.2233614122341489</v>
       </c>
       <c r="AB175">
         <v>4</v>
@@ -22002,7 +22002,7 @@
         <v>7.38820347927442</v>
       </c>
       <c r="M176">
-        <v>0.19055000349569082</v>
+        <v>0.19055000230772606</v>
       </c>
       <c r="N176">
         <v>3</v>
@@ -22076,7 +22076,7 @@
         <v>9.0953449583385275</v>
       </c>
       <c r="M177">
-        <v>0.18808796706401421</v>
+        <v>0.18808796577589121</v>
       </c>
       <c r="N177">
         <v>1</v>
@@ -22150,7 +22150,7 @@
         <v>3.0133100897090981</v>
       </c>
       <c r="M178">
-        <v>0.18807905497550029</v>
+        <v>0.18807905408760001</v>
       </c>
       <c r="N178">
         <v>5</v>
@@ -22224,7 +22224,7 @@
         <v>1.8394835454375038</v>
       </c>
       <c r="M179">
-        <v>0.18775731703101031</v>
+        <v>0.187757315460229</v>
       </c>
       <c r="N179">
         <v>4</v>
@@ -22260,7 +22260,7 @@
         <v>1.92075</v>
       </c>
       <c r="AA179">
-        <v>0.21771246297399605</v>
+        <v>0.21771246297399613</v>
       </c>
       <c r="AB179">
         <v>2</v>
@@ -22298,7 +22298,7 @@
         <v>4.3797343042366403</v>
       </c>
       <c r="M180">
-        <v>0.18356191776011779</v>
+        <v>0.18356191663671151</v>
       </c>
       <c r="N180">
         <v>4</v>
@@ -22372,7 +22372,7 @@
         <v>9.7247067679084545</v>
       </c>
       <c r="M181">
-        <v>0.18310503630514924</v>
+        <v>0.18310503560264543</v>
       </c>
       <c r="N181">
         <v>2</v>
@@ -22446,7 +22446,7 @@
         <v>9.2573382238903612</v>
       </c>
       <c r="M182">
-        <v>0.1819866611074511</v>
+        <v>0.18198666010232684</v>
       </c>
       <c r="N182">
         <v>3</v>
@@ -22520,7 +22520,7 @@
         <v>14.215571935999174</v>
       </c>
       <c r="M183">
-        <v>0.18088342691258424</v>
+        <v>0.18088342687138814</v>
       </c>
       <c r="N183">
         <v>1</v>
@@ -22594,7 +22594,7 @@
         <v>6.40454709471235</v>
       </c>
       <c r="M184">
-        <v>0.17602640815974313</v>
+        <v>0.17602640698531427</v>
       </c>
       <c r="N184">
         <v>5</v>
@@ -22668,7 +22668,7 @@
         <v>8.437042784777594</v>
       </c>
       <c r="M185">
-        <v>0.17099210028629605</v>
+        <v>0.17099209927225781</v>
       </c>
       <c r="N185">
         <v>3</v>
@@ -22742,7 +22742,7 @@
         <v>11.716284931407461</v>
       </c>
       <c r="M186">
-        <v>0.1706666839302006</v>
+        <v>0.17066668164159554</v>
       </c>
       <c r="N186">
         <v>2</v>
@@ -22816,7 +22816,7 @@
         <v>14.042520418871376</v>
       </c>
       <c r="M187">
-        <v>0.16757077121653138</v>
+        <v>0.16757077055548028</v>
       </c>
       <c r="N187">
         <v>1</v>
@@ -22852,7 +22852,7 @@
         <v>6.7499999999999999E-3</v>
       </c>
       <c r="AA187">
-        <v>0.1938132936343436</v>
+        <v>0.19381329363434371</v>
       </c>
       <c r="AB187">
         <v>4</v>
@@ -22890,7 +22890,7 @@
         <v>4.0647545329371013</v>
       </c>
       <c r="M188">
-        <v>0.16726844834868984</v>
+        <v>0.16726844747577305</v>
       </c>
       <c r="N188">
         <v>4</v>
@@ -22964,7 +22964,7 @@
         <v>5.9628185385678627</v>
       </c>
       <c r="M189">
-        <v>0.16687026264243102</v>
+        <v>0.16687026086525331</v>
       </c>
       <c r="N189">
         <v>5</v>
@@ -23038,7 +23038,7 @@
         <v>8.7820508906037897</v>
       </c>
       <c r="M190">
-        <v>0.16232899105347312</v>
+        <v>0.16232898939658419</v>
       </c>
       <c r="N190">
         <v>2</v>
@@ -23112,7 +23112,7 @@
         <v>13.116983201971063</v>
       </c>
       <c r="M191">
-        <v>0.16227401013607615</v>
+        <v>0.16227400938079081</v>
       </c>
       <c r="N191">
         <v>1</v>
@@ -23148,7 +23148,7 @@
         <v>3.7109999999999999</v>
       </c>
       <c r="AA191">
-        <v>0.1879443244798161</v>
+        <v>0.18794432447981621</v>
       </c>
       <c r="AB191">
         <v>3</v>
@@ -23186,7 +23186,7 @@
         <v>5.3975986705205488</v>
       </c>
       <c r="M192">
-        <v>0.16112406428027273</v>
+        <v>0.16112406307066152</v>
       </c>
       <c r="N192">
         <v>4</v>
@@ -23260,7 +23260,7 @@
         <v>8.2115626900617382</v>
       </c>
       <c r="M193">
-        <v>0.16046915696737057</v>
+        <v>0.16046915575607315</v>
       </c>
       <c r="N193">
         <v>5</v>
@@ -23334,7 +23334,7 @@
         <v>6.8049371627198321</v>
       </c>
       <c r="M194">
-        <v>0.15698634661161906</v>
+        <v>0.15698634473031547</v>
       </c>
       <c r="N194">
         <v>3</v>
@@ -23370,7 +23370,7 @@
         <v>0.26400000000000001</v>
       </c>
       <c r="AA194">
-        <v>0.1810041453385588</v>
+        <v>0.18100414533855891</v>
       </c>
       <c r="AB194">
         <v>1</v>
@@ -23408,7 +23408,7 @@
         <v>0.2188492248454757</v>
       </c>
       <c r="M195">
-        <v>0.154640745389552</v>
+        <v>0.1546407442459268</v>
       </c>
       <c r="N195">
         <v>5</v>
@@ -23482,7 +23482,7 @@
         <v>3.8894694256571345</v>
       </c>
       <c r="M196">
-        <v>0.1496883689011215</v>
+        <v>0.14968836800712701</v>
       </c>
       <c r="N196">
         <v>2</v>
@@ -23556,7 +23556,7 @@
         <v>2.365020148547377</v>
       </c>
       <c r="M197">
-        <v>0.14829316337006501</v>
+        <v>0.1482931623354162</v>
       </c>
       <c r="N197">
         <v>3</v>
@@ -23592,7 +23592,7 @@
         <v>0.24825</v>
       </c>
       <c r="AA197">
-        <v>0.16996282785853989</v>
+        <v>0.16996282785854</v>
       </c>
       <c r="AB197">
         <v>2</v>
@@ -23630,7 +23630,7 @@
         <v>1.6172661409762021</v>
       </c>
       <c r="M198">
-        <v>0.1478386784688889</v>
+        <v>0.1478386770915919</v>
       </c>
       <c r="N198">
         <v>4</v>
@@ -23704,7 +23704,7 @@
         <v>7.926161667413294</v>
       </c>
       <c r="M199">
-        <v>0.14688743091115503</v>
+        <v>0.14688742916091826</v>
       </c>
       <c r="N199">
         <v>1</v>
@@ -23740,7 +23740,7 @@
         <v>0.89775000000000005</v>
       </c>
       <c r="AA199">
-        <v>0.16830233816416171</v>
+        <v>0.16830233816416179</v>
       </c>
       <c r="AB199">
         <v>1</v>
@@ -23778,7 +23778,7 @@
         <v>2.0980900568860168</v>
       </c>
       <c r="M200">
-        <v>0.14462996363330979</v>
+        <v>0.14462996253182139</v>
       </c>
       <c r="N200">
         <v>2</v>
@@ -23814,7 +23814,7 @@
         <v>0.96525000000000005</v>
       </c>
       <c r="AA200">
-        <v>0.16347028364090868</v>
+        <v>0.16347028364090879</v>
       </c>
       <c r="AB200">
         <v>3</v>
@@ -23852,7 +23852,7 @@
         <v>1.9315919928791523</v>
       </c>
       <c r="M201">
-        <v>0.1425119031285286</v>
+        <v>0.1425119023006913</v>
       </c>
       <c r="N201">
         <v>4</v>
@@ -23926,7 +23926,7 @@
         <v>2.48933283553635</v>
       </c>
       <c r="M202">
-        <v>0.1422219482184012</v>
+        <v>0.14222194731706519</v>
       </c>
       <c r="N202">
         <v>3</v>
@@ -24000,7 +24000,7 @@
         <v>2.9043127741779688</v>
       </c>
       <c r="M203">
-        <v>0.1421912359397606</v>
+        <v>0.142191235185571</v>
       </c>
       <c r="N203">
         <v>5</v>
@@ -24074,7 +24074,7 @@
         <v>3.3187541118640951</v>
       </c>
       <c r="M204">
-        <v>0.14152862910693076</v>
+        <v>0.14152862868322966</v>
       </c>
       <c r="N204">
         <v>1</v>
@@ -24148,7 +24148,7 @@
         <v>4.1744072681478483</v>
       </c>
       <c r="M205">
-        <v>0.13326236655501239</v>
+        <v>0.13326236545928799</v>
       </c>
       <c r="N205">
         <v>3</v>
@@ -24222,7 +24222,7 @@
         <v>6.7085627728515904</v>
       </c>
       <c r="M206">
-        <v>0.13184812464182616</v>
+        <v>0.13184812346528343</v>
       </c>
       <c r="N206">
         <v>1</v>
@@ -24258,7 +24258,7 @@
         <v>0.30375000000000002</v>
       </c>
       <c r="AA206">
-        <v>0.14719542171494829</v>
+        <v>0.1471954217149484</v>
       </c>
       <c r="AB206">
         <v>2</v>
@@ -24296,7 +24296,7 @@
         <v>1.3517369156998773</v>
       </c>
       <c r="M207">
-        <v>0.13127532601331501</v>
+        <v>0.13127532503187531</v>
       </c>
       <c r="N207">
         <v>5</v>
@@ -24332,7 +24332,7 @@
         <v>9.75E-3</v>
       </c>
       <c r="AA207">
-        <v>0.1471886252262013</v>
+        <v>0.14718862522620141</v>
       </c>
       <c r="AB207">
         <v>1</v>
@@ -24370,7 +24370,7 @@
         <v>3.2678269060174125</v>
       </c>
       <c r="M208">
-        <v>0.12954530430657329</v>
+        <v>0.1295453033122155</v>
       </c>
       <c r="N208">
         <v>4</v>
@@ -24444,7 +24444,7 @@
         <v>3.6845292109056347</v>
       </c>
       <c r="M209">
-        <v>0.12837789971369901</v>
+        <v>0.12837789759582491</v>
       </c>
       <c r="N209">
         <v>2</v>
@@ -24518,7 +24518,7 @@
         <v>2.0859673682178026</v>
       </c>
       <c r="M210">
-        <v>0.1221231472393749</v>
+        <v>0.1221231459017683</v>
       </c>
       <c r="N210">
         <v>3</v>
@@ -24592,7 +24592,7 @@
         <v>4.5571326565726089</v>
       </c>
       <c r="M211">
-        <v>0.11877980288492092</v>
+        <v>0.1187798029139257</v>
       </c>
       <c r="N211">
         <v>1</v>
@@ -24666,7 +24666,7 @@
         <v>3.8642344750765805</v>
       </c>
       <c r="M212">
-        <v>0.11582201128351099</v>
+        <v>0.115822008658281</v>
       </c>
       <c r="N212">
         <v>2</v>
@@ -24740,7 +24740,7 @@
         <v>3.0356801491000578</v>
       </c>
       <c r="M213">
-        <v>0.1151728163575572</v>
+        <v>0.1151728143587276</v>
       </c>
       <c r="N213">
         <v>4</v>
@@ -24776,7 +24776,7 @@
         <v>2.2605</v>
       </c>
       <c r="AA213">
-        <v>0.1294285631677855</v>
+        <v>0.12942856316778559</v>
       </c>
       <c r="AB213">
         <v>1</v>
@@ -24814,7 +24814,7 @@
         <v>3.3673008750082656</v>
       </c>
       <c r="M214">
-        <v>0.11407178356489019</v>
+        <v>0.11407178246396241</v>
       </c>
       <c r="N214">
         <v>2</v>
@@ -24888,7 +24888,7 @@
         <v>2.9166326780077103</v>
       </c>
       <c r="M215">
-        <v>0.1139454350974745</v>
+        <v>0.11394543431849161</v>
       </c>
       <c r="N215">
         <v>4</v>
@@ -24924,7 +24924,7 @@
         <v>1.0500000000000001E-2</v>
       </c>
       <c r="AA215">
-        <v>0.1203567705074088</v>
+        <v>0.12035677050740891</v>
       </c>
       <c r="AB215">
         <v>3</v>
@@ -24962,7 +24962,7 @@
         <v>0.50100266242633718</v>
       </c>
       <c r="M216">
-        <v>0.1123423603571337</v>
+        <v>0.11234235912997929</v>
       </c>
       <c r="N216">
         <v>1</v>
@@ -25036,7 +25036,7 @@
         <v>1.6818505919224802</v>
       </c>
       <c r="M217">
-        <v>0.10552005736241149</v>
+        <v>0.10552005663737829</v>
       </c>
       <c r="N217">
         <v>3</v>
@@ -25072,7 +25072,7 @@
         <v>1.4032500000000001</v>
       </c>
       <c r="AA217">
-        <v>0.1189205158246216</v>
+        <v>0.11892051582462171</v>
       </c>
       <c r="AB217">
         <v>2</v>
@@ -25110,7 +25110,7 @@
         <v>3.5085398458748869</v>
       </c>
       <c r="M218">
-        <v>9.977075265601551E-2</v>
+        <v>9.97707510417946E-2</v>
       </c>
       <c r="N218">
         <v>1</v>
@@ -25184,7 +25184,7 @@
         <v>1.6801471785973865</v>
       </c>
       <c r="M219">
-        <v>9.7177892981614306E-2</v>
+        <v>9.7177892133076205E-2</v>
       </c>
       <c r="N219">
         <v>2</v>
@@ -25258,7 +25258,7 @@
         <v>1.7305667994244844</v>
       </c>
       <c r="M220">
-        <v>9.6049687486761182E-2</v>
+        <v>9.60496869779741E-2</v>
       </c>
       <c r="N220">
         <v>3</v>
@@ -25332,7 +25332,7 @@
         <v>2.2537596268317497</v>
       </c>
       <c r="M221">
-        <v>9.1361324752340503E-2</v>
+        <v>9.1361320706458707E-2</v>
       </c>
       <c r="N221">
         <v>1</v>
@@ -25368,7 +25368,7 @@
         <v>0.156</v>
       </c>
       <c r="AA221">
-        <v>0.10462627165815611</v>
+        <v>0.10462627165815619</v>
       </c>
       <c r="AB221">
         <v>2</v>
@@ -25406,7 +25406,7 @@
         <v>1.3332290746268656</v>
       </c>
       <c r="M222">
-        <v>8.8882280926081095E-2</v>
+        <v>8.8882280196096494E-2</v>
       </c>
       <c r="N222">
         <v>5</v>
@@ -25442,7 +25442,7 @@
         <v>7.5000000000000002E-4</v>
       </c>
       <c r="AA222">
-        <v>9.8463368962746101E-2</v>
+        <v>9.8463368962746198E-2</v>
       </c>
       <c r="AB222">
         <v>3</v>
@@ -25480,7 +25480,7 @@
         <v>0.79363369364395076</v>
       </c>
       <c r="M223">
-        <v>8.8071294439464196E-2</v>
+        <v>8.8071294291053218E-2</v>
       </c>
       <c r="N223">
         <v>3</v>
@@ -25516,7 +25516,7 @@
         <v>0.26400000000000001</v>
       </c>
       <c r="AA223">
-        <v>9.7934523586612698E-2</v>
+        <v>9.7934523586612796E-2</v>
       </c>
       <c r="AB223">
         <v>1</v>
@@ -25554,7 +25554,7 @@
         <v>1.8703447531124959</v>
       </c>
       <c r="M224">
-        <v>8.7058544346671402E-2</v>
+        <v>8.7058543703198016E-2</v>
       </c>
       <c r="N224">
         <v>4</v>
@@ -25628,7 +25628,7 @@
         <v>2.136429828455233</v>
       </c>
       <c r="M225">
-        <v>8.5476919420985703E-2</v>
+        <v>8.5476918698509097E-2</v>
       </c>
       <c r="N225">
         <v>2</v>
@@ -25702,7 +25702,7 @@
         <v>2.9902228837744058</v>
       </c>
       <c r="M226">
-        <v>8.2759689059080099E-2</v>
+        <v>8.2759688250374802E-2</v>
       </c>
       <c r="N226">
         <v>2</v>
@@ -25776,7 +25776,7 @@
         <v>0.81976113101330594</v>
       </c>
       <c r="M227">
-        <v>8.1686744709339995E-2</v>
+        <v>8.1686744155225505E-2</v>
       </c>
       <c r="N227">
         <v>5</v>
@@ -25812,7 +25812,7 @@
         <v>3.9750000000000001E-2</v>
       </c>
       <c r="AA227">
-        <v>7.9476639772107394E-2</v>
+        <v>7.9476639772107505E-2</v>
       </c>
       <c r="AB227">
         <v>1</v>
@@ -25850,7 +25850,7 @@
         <v>2.0178097216940154</v>
       </c>
       <c r="M228">
-        <v>8.0117635936464607E-2</v>
+        <v>8.01176352074673E-2</v>
       </c>
       <c r="N228">
         <v>3</v>
@@ -25924,7 +25924,7 @@
         <v>2.4006628901403739</v>
       </c>
       <c r="M229">
-        <v>7.9178762972175298E-2</v>
+        <v>7.9178761737466005E-2</v>
       </c>
       <c r="N229">
         <v>4</v>
@@ -25998,7 +25998,7 @@
         <v>2.9586862317386178</v>
       </c>
       <c r="M230">
-        <v>7.8224179356388798E-2</v>
+        <v>7.8224178269257205E-2</v>
       </c>
       <c r="N230">
         <v>1</v>
@@ -26036,7 +26036,7 @@
         <v>3.0073033200293811</v>
       </c>
       <c r="M231">
-        <v>7.4899694895753197E-2</v>
+        <v>7.4899694370453199E-2</v>
       </c>
       <c r="N231">
         <v>2</v>
@@ -26074,7 +26074,7 @@
         <v>2.3363667253637517</v>
       </c>
       <c r="M232">
-        <v>6.5620411654016206E-2</v>
+        <v>6.5620410914106905E-2</v>
       </c>
       <c r="N232">
         <v>1</v>
@@ -26112,7 +26112,7 @@
         <v>2.5392002018051336</v>
       </c>
       <c r="M233">
-        <v>6.1234415640421203E-2</v>
+        <v>6.1234413022407695E-2</v>
       </c>
       <c r="N233">
         <v>1</v>
@@ -26150,7 +26150,7 @@
         <v>2.3152872522458292</v>
       </c>
       <c r="M234">
-        <v>5.37682244578358E-2</v>
+        <v>5.3768223855669997E-2</v>
       </c>
       <c r="N234">
         <v>1</v>
@@ -26188,7 +26188,7 @@
         <v>0.79573817914735678</v>
       </c>
       <c r="M235">
-        <v>5.09076469351342E-2</v>
+        <v>5.0907646135443803E-2</v>
       </c>
       <c r="N235">
         <v>3</v>
@@ -26226,7 +26226,7 @@
         <v>1.8421426864619588</v>
       </c>
       <c r="M236">
-        <v>4.8040996790013502E-2</v>
+        <v>4.8040996102536503E-2</v>
       </c>
       <c r="N236">
         <v>4</v>
@@ -26264,7 +26264,7 @@
         <v>2.1641244827395534</v>
       </c>
       <c r="M237">
-        <v>4.7313566954455197E-2</v>
+        <v>4.7313566180776097E-2</v>
       </c>
       <c r="N237">
         <v>2</v>
@@ -26302,7 +26302,7 @@
         <v>3.9866858008604655</v>
       </c>
       <c r="M238">
-        <v>4.4214949296898599E-2</v>
+        <v>4.4214948756081701E-2</v>
       </c>
       <c r="N238">
         <v>1</v>
@@ -26340,7 +26340,7 @@
         <v>3.1452066630552546</v>
       </c>
       <c r="M239">
-        <v>4.3180538556199001E-2</v>
+        <v>4.3180538162455602E-2</v>
       </c>
       <c r="N239">
         <v>2</v>
@@ -26378,7 +26378,7 @@
         <v>1.5599962381547079</v>
       </c>
       <c r="M240">
-        <v>3.5959791363848297E-2</v>
+        <v>3.5959791120995697E-2</v>
       </c>
       <c r="N240">
         <v>3</v>
@@ -26416,7 +26416,7 @@
         <v>0.9558854555580093</v>
       </c>
       <c r="M241">
-        <v>3.4381811557280102E-2</v>
+        <v>3.4381811264893897E-2</v>
       </c>
       <c r="N241">
         <v>1</v>
@@ -26428,7 +26428,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05661A8E-2B62-49A2-AFE4-9CD86DE300CD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B19EBD35-52B1-4408-9EB5-E829352E194D}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{190C0929-BA9E-47C0-BE7E-9F6E2683EB30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C71B5066-7CDA-41CC-BB6B-F25085AF4BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8510,7 +8510,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F548C79-E837-477B-8006-A39A537A76B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28CFD7C4-51DF-4016-9958-CCECE61CEED5}">
   <dimension ref="B9:N39"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9668,7 +9668,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BC51EC8-3E25-49C1-858E-3BF1C946923B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB69581-4E89-433F-8BD6-10CA6C800DD8}">
   <dimension ref="B9:AB241"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -26428,7 +26428,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B19EBD35-52B1-4408-9EB5-E829352E194D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14E1A90F-3963-476B-91B2-9658330A08DE}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C71B5066-7CDA-41CC-BB6B-F25085AF4BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E0C5931-ABF5-4F8B-8A11-3855FAD91442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5079" uniqueCount="1175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5081" uniqueCount="1175">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -5192,7 +5192,9 @@
       <c r="F8" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="1"/>
+      <c r="G8" t="s">
+        <v>14</v>
+      </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="str">
@@ -5228,7 +5230,9 @@
       <c r="F9" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="1"/>
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="K9" s="1"/>
@@ -8510,7 +8514,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28CFD7C4-51DF-4016-9958-CCECE61CEED5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EC5C238-B9CD-498D-9B65-95B6F65081B1}">
   <dimension ref="B9:N39"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9668,7 +9672,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB69581-4E89-433F-8BD6-10CA6C800DD8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF41302-6226-408E-B251-2B31AB2C6A24}">
   <dimension ref="B9:AB241"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -26428,7 +26432,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14E1A90F-3963-476B-91B2-9658330A08DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD608A1B-7EA0-4B2B-AF5A-364DE8246974}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E0C5931-ABF5-4F8B-8A11-3855FAD91442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2E5345B-809C-4F8E-97B8-E4630896E948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8514,7 +8514,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EC5C238-B9CD-498D-9B65-95B6F65081B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AEC6E7F-5523-4A63-9A18-D8029A540311}">
   <dimension ref="B9:N39"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9672,7 +9672,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF41302-6226-408E-B251-2B31AB2C6A24}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FEB1845-3FBC-4C1C-AB9B-3B997CF215DE}">
   <dimension ref="B9:AB241"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -26432,7 +26432,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD608A1B-7EA0-4B2B-AF5A-364DE8246974}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9879DE1-FCF7-4CE2-9382-1CFB4DFBCCD0}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2E5345B-809C-4F8E-97B8-E4630896E948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{003CD53D-E5F0-4CD8-88C0-26F11AC49688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8514,7 +8514,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AEC6E7F-5523-4A63-9A18-D8029A540311}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E800B49A-E3FF-4577-80E6-A1E193CB4054}">
   <dimension ref="B9:N39"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9672,7 +9672,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FEB1845-3FBC-4C1C-AB9B-3B997CF215DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{552660D0-F3B0-4B75-8E5A-6A2659DE5450}">
   <dimension ref="B9:AB241"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -26432,7 +26432,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9879DE1-FCF7-4CE2-9382-1CFB4DFBCCD0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B12574F-B45B-47BD-B425-DF3552F569AE}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{003CD53D-E5F0-4CD8-88C0-26F11AC49688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4B87CD0-B586-4CDC-8D60-9334095BC048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8514,7 +8514,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E800B49A-E3FF-4577-80E6-A1E193CB4054}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6254FE7-32D3-4851-91A6-3E96EFD356A7}">
   <dimension ref="B9:N39"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9672,7 +9672,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{552660D0-F3B0-4B75-8E5A-6A2659DE5450}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5BB1278-07BE-47EA-B270-6EDCC15059BE}">
   <dimension ref="B9:AB241"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -26432,7 +26432,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B12574F-B45B-47BD-B425-DF3552F569AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBFE0899-2434-4DB1-96B5-F9AA160147CC}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4B87CD0-B586-4CDC-8D60-9334095BC048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{47908D9E-3EAE-4837-89C8-8D8622919513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8514,7 +8514,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6254FE7-32D3-4851-91A6-3E96EFD356A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CE58A2C-AE11-47B2-A51A-46B1E60942E6}">
   <dimension ref="B9:N39"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9672,7 +9672,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5BB1278-07BE-47EA-B270-6EDCC15059BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8BC06A9-646E-45D1-B6D0-1F42C09DB17E}">
   <dimension ref="B9:AB241"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -26432,7 +26432,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBFE0899-2434-4DB1-96B5-F9AA160147CC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5B9B7E-B9C6-44F2-BDC7-B87F30334D2F}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{47908D9E-3EAE-4837-89C8-8D8622919513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{215F13A8-4738-469B-8E0D-9F5AFECE2582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8514,7 +8514,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CE58A2C-AE11-47B2-A51A-46B1E60942E6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92D0186C-36BE-40AE-BCF9-F5DB73593165}">
   <dimension ref="B9:N39"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9672,7 +9672,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8BC06A9-646E-45D1-B6D0-1F42C09DB17E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{457E2D50-91F6-43F2-B968-58D10D47613B}">
   <dimension ref="B9:AB241"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -26432,7 +26432,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5B9B7E-B9C6-44F2-BDC7-B87F30334D2F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{615D0D19-041E-4FB2-9BA6-4EB3D6A88355}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68E1E95F-EA51-423B-86E4-56B90BAF1F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAC15761-B5EF-4F36-9E26-6E13700B3DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6582,7 +6582,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96696903-2F87-489F-889B-1096AC65BEC7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{823FF637-4DE9-49B8-AA86-BA4217CBC89C}">
   <dimension ref="B9:M41"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7720,7 +7720,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4558A20F-1581-44F6-8E18-A78ADC14AA3A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0456E4D2-1350-41B1-8063-129F80E9DADA}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10375,7 +10375,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{279A7045-2960-4860-B77C-65F3AD39C796}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{486A0509-FA7B-415B-8CD5-D5D8D0E721DB}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAC15761-B5EF-4F36-9E26-6E13700B3DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{759309BD-C82C-46C9-BD4F-86324631C8FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6582,7 +6582,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{823FF637-4DE9-49B8-AA86-BA4217CBC89C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB015653-B700-46EA-8112-EA6AE6FBC96D}">
   <dimension ref="B9:M41"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7720,7 +7720,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0456E4D2-1350-41B1-8063-129F80E9DADA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A34B9DE4-071E-437A-9A64-C6A93E52066C}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10375,7 +10375,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{486A0509-FA7B-415B-8CD5-D5D8D0E721DB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7A82995-CDFC-41F8-8222-BB47A00CFE7C}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,22 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{759309BD-C82C-46C9-BD4F-86324631C8FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEBF8322-B0DD-4F9F-814A-C706E65FCE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
-    <sheet name="hydro" sheetId="6" r:id="rId2"/>
-    <sheet name="ELC_Storage" sheetId="9" r:id="rId3"/>
-    <sheet name="EV Battery" sheetId="10" r:id="rId4"/>
-    <sheet name="H2 prod" sheetId="11" r:id="rId5"/>
-    <sheet name="solar" sheetId="12" r:id="rId6"/>
-    <sheet name="wind" sheetId="13" r:id="rId7"/>
-    <sheet name="conventional" sheetId="14" r:id="rId8"/>
+    <sheet name="ELC_Storage" sheetId="9" r:id="rId2"/>
+    <sheet name="EV Battery" sheetId="10" r:id="rId3"/>
+    <sheet name="H2 prod" sheetId="11" r:id="rId4"/>
+    <sheet name="solar" sheetId="12" r:id="rId5"/>
+    <sheet name="wind" sheetId="13" r:id="rId6"/>
+    <sheet name="conventional" sheetId="14" r:id="rId7"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
     <definedName name="FuelList">[1]ELC_Lists!$K$4:$K$113</definedName>
@@ -57,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1721" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1680" uniqueCount="521">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -622,253 +621,223 @@
     <t>~fi_process</t>
   </si>
   <si>
+    <t>set</t>
+  </si>
+  <si>
     <t>process</t>
   </si>
   <si>
     <t>description</t>
   </si>
   <si>
+    <t>capacity_unit</t>
+  </si>
+  <si>
+    <t>activity_unit</t>
+  </si>
+  <si>
     <t>timeslicelevel</t>
   </si>
   <si>
-    <t>EN_Hydro_JPN-1</t>
-  </si>
-  <si>
-    <t>New Hydro Potential - Japan - Step 1</t>
-  </si>
-  <si>
-    <t>PJ</t>
-  </si>
-  <si>
-    <t>EN_Hydro_JPN-2</t>
-  </si>
-  <si>
-    <t>New Hydro Potential - Japan - Step 2</t>
-  </si>
-  <si>
-    <t>EN_Hydro_JPN-3</t>
-  </si>
-  <si>
-    <t>New Hydro Potential - Japan - Step 3</t>
+    <t>vintage</t>
+  </si>
+  <si>
+    <t>ele</t>
+  </si>
+  <si>
+    <t>e_spv_001</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 1</t>
+  </si>
+  <si>
+    <t>annual</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>e_spv_002</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 2</t>
+  </si>
+  <si>
+    <t>e_spv_003</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 3</t>
+  </si>
+  <si>
+    <t>e_spv_004</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 4</t>
+  </si>
+  <si>
+    <t>e_spv_005</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 5</t>
+  </si>
+  <si>
+    <t>e_spv_006</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 6</t>
+  </si>
+  <si>
+    <t>e_spv_007</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 7</t>
+  </si>
+  <si>
+    <t>e_spv_008</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 8</t>
+  </si>
+  <si>
+    <t>e_spv_009</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 9</t>
+  </si>
+  <si>
+    <t>e_spv_010</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 10</t>
+  </si>
+  <si>
+    <t>e_spv_011</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 11</t>
+  </si>
+  <si>
+    <t>e_spv_012</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 12</t>
+  </si>
+  <si>
+    <t>e_spv_013</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 13</t>
+  </si>
+  <si>
+    <t>e_spv_014</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 14</t>
+  </si>
+  <si>
+    <t>e_spv_015</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 15</t>
+  </si>
+  <si>
+    <t>e_spv_016</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 16</t>
+  </si>
+  <si>
+    <t>e_spv_017</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 17</t>
+  </si>
+  <si>
+    <t>e_spv_018</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 18</t>
+  </si>
+  <si>
+    <t>e_spv_019</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 19</t>
+  </si>
+  <si>
+    <t>e_spv_020</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 20</t>
+  </si>
+  <si>
+    <t>e_spv_021</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 21</t>
+  </si>
+  <si>
+    <t>e_spv_022</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 22</t>
+  </si>
+  <si>
+    <t>e_spv_023</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 23</t>
+  </si>
+  <si>
+    <t>e_spv_024</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 24</t>
+  </si>
+  <si>
+    <t>e_spv_025</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 25</t>
+  </si>
+  <si>
+    <t>e_spv_026</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 26</t>
+  </si>
+  <si>
+    <t>e_spv_027</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 27</t>
+  </si>
+  <si>
+    <t>e_spv_028</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 28</t>
+  </si>
+  <si>
+    <t>e_spv_029</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 29</t>
+  </si>
+  <si>
+    <t>e_spv_030</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 30</t>
+  </si>
+  <si>
+    <t>e_spv_031</t>
+  </si>
+  <si>
+    <t>solar resource in cluster 31</t>
   </si>
   <si>
     <t>~fi_t</t>
-  </si>
-  <si>
-    <t>CAP_BND</t>
-  </si>
-  <si>
-    <t>INVCOST~USD21_alt</t>
-  </si>
-  <si>
-    <t>AF~FX</t>
-  </si>
-  <si>
-    <t>set</t>
-  </si>
-  <si>
-    <t>capacity_unit</t>
-  </si>
-  <si>
-    <t>activity_unit</t>
-  </si>
-  <si>
-    <t>vintage</t>
-  </si>
-  <si>
-    <t>ele</t>
-  </si>
-  <si>
-    <t>e_spv_001</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 1</t>
-  </si>
-  <si>
-    <t>annual</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>e_spv_002</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 2</t>
-  </si>
-  <si>
-    <t>e_spv_003</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 3</t>
-  </si>
-  <si>
-    <t>e_spv_004</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 4</t>
-  </si>
-  <si>
-    <t>e_spv_005</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 5</t>
-  </si>
-  <si>
-    <t>e_spv_006</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 6</t>
-  </si>
-  <si>
-    <t>e_spv_007</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 7</t>
-  </si>
-  <si>
-    <t>e_spv_008</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 8</t>
-  </si>
-  <si>
-    <t>e_spv_009</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 9</t>
-  </si>
-  <si>
-    <t>e_spv_010</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 10</t>
-  </si>
-  <si>
-    <t>e_spv_011</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 11</t>
-  </si>
-  <si>
-    <t>e_spv_012</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 12</t>
-  </si>
-  <si>
-    <t>e_spv_013</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 13</t>
-  </si>
-  <si>
-    <t>e_spv_014</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 14</t>
-  </si>
-  <si>
-    <t>e_spv_015</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 15</t>
-  </si>
-  <si>
-    <t>e_spv_016</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 16</t>
-  </si>
-  <si>
-    <t>e_spv_017</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 17</t>
-  </si>
-  <si>
-    <t>e_spv_018</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 18</t>
-  </si>
-  <si>
-    <t>e_spv_019</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 19</t>
-  </si>
-  <si>
-    <t>e_spv_020</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 20</t>
-  </si>
-  <si>
-    <t>e_spv_021</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 21</t>
-  </si>
-  <si>
-    <t>e_spv_022</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 22</t>
-  </si>
-  <si>
-    <t>e_spv_023</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 23</t>
-  </si>
-  <si>
-    <t>e_spv_024</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 24</t>
-  </si>
-  <si>
-    <t>e_spv_025</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 25</t>
-  </si>
-  <si>
-    <t>e_spv_026</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 26</t>
-  </si>
-  <si>
-    <t>e_spv_027</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 27</t>
-  </si>
-  <si>
-    <t>e_spv_028</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 28</t>
-  </si>
-  <si>
-    <t>e_spv_029</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 29</t>
-  </si>
-  <si>
-    <t>e_spv_030</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 30</t>
-  </si>
-  <si>
-    <t>e_spv_031</t>
-  </si>
-  <si>
-    <t>solar resource in cluster 31</t>
   </si>
   <si>
     <t>comm-out</t>
@@ -3637,158 +3606,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5417F31-D792-47CD-82F2-E942FCB1F74A}">
-  <dimension ref="B9:N13"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <sheetData>
-    <row r="9" spans="2:14">
-      <c r="B9" t="s">
-        <v>163</v>
-      </c>
-      <c r="I9" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14">
-      <c r="B10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" t="s">
-        <v>164</v>
-      </c>
-      <c r="D10" t="s">
-        <v>165</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" t="s">
-        <v>166</v>
-      </c>
-      <c r="I10" t="s">
-        <v>164</v>
-      </c>
-      <c r="J10" t="s">
-        <v>2</v>
-      </c>
-      <c r="K10" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" t="s">
-        <v>175</v>
-      </c>
-      <c r="M10" t="s">
-        <v>176</v>
-      </c>
-      <c r="N10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14">
-      <c r="B11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" t="s">
-        <v>167</v>
-      </c>
-      <c r="D11" t="s">
-        <v>168</v>
-      </c>
-      <c r="E11" t="s">
-        <v>169</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" t="s">
-        <v>167</v>
-      </c>
-      <c r="J11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K11" t="s">
-        <v>19</v>
-      </c>
-      <c r="L11">
-        <v>3.5045662100456627E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="2:14">
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" t="s">
-        <v>170</v>
-      </c>
-      <c r="D12" t="s">
-        <v>171</v>
-      </c>
-      <c r="E12" t="s">
-        <v>169</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" t="s">
-        <v>170</v>
-      </c>
-      <c r="J12" t="s">
-        <v>28</v>
-      </c>
-      <c r="K12" t="s">
-        <v>19</v>
-      </c>
-      <c r="L12">
-        <v>4.6619373776908078E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="2:14">
-      <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" t="s">
-        <v>172</v>
-      </c>
-      <c r="D13" t="s">
-        <v>173</v>
-      </c>
-      <c r="E13" t="s">
-        <v>169</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" t="s">
-        <v>172</v>
-      </c>
-      <c r="J13" t="s">
-        <v>28</v>
-      </c>
-      <c r="K13" t="s">
-        <v>19</v>
-      </c>
-      <c r="L13">
-        <v>4.7396173081104304E-2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FD6D8AA-F8A9-4BBE-94C7-C767CA3BCC03}">
   <dimension ref="B2:W61"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25"/>
@@ -5024,7 +4841,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12EA90E-43F0-4F26-A089-D51219939B11}">
   <dimension ref="B3:Y8"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -5295,7 +5112,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73A64BB3-8019-4461-A511-24783E2ADCDE}">
   <dimension ref="A1:Z29"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -6581,8 +6398,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB015653-B700-46EA-8112-EA6AE6FBC96D}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E376988-7750-490E-A31A-29E9D834FDE4}">
   <dimension ref="B9:M41"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6591,53 +6408,53 @@
         <v>163</v>
       </c>
       <c r="J9" t="s">
-        <v>174</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="C10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D10" t="s">
+        <v>166</v>
+      </c>
+      <c r="E10" t="s">
+        <v>167</v>
+      </c>
+      <c r="F10" t="s">
+        <v>168</v>
+      </c>
+      <c r="G10" t="s">
+        <v>169</v>
+      </c>
+      <c r="H10" t="s">
+        <v>170</v>
+      </c>
+      <c r="J10" t="s">
         <v>165</v>
       </c>
-      <c r="E10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F10" t="s">
-        <v>180</v>
-      </c>
-      <c r="G10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H10" t="s">
-        <v>181</v>
-      </c>
-      <c r="J10" t="s">
-        <v>164</v>
-      </c>
       <c r="K10" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="L10" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="M10" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C11" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="D11" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -6646,16 +6463,16 @@
         <v>21</v>
       </c>
       <c r="G11" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H11" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J11" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="K11" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="L11">
         <v>1.0868475837211775</v>
@@ -6666,13 +6483,13 @@
     </row>
     <row r="12" spans="2:13">
       <c r="B12" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C12" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D12" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -6681,16 +6498,16 @@
         <v>21</v>
       </c>
       <c r="G12" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H12" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J12" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="K12" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="L12">
         <v>0.49620812665820685</v>
@@ -6701,13 +6518,13 @@
     </row>
     <row r="13" spans="2:13">
       <c r="B13" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C13" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="D13" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -6716,16 +6533,16 @@
         <v>21</v>
       </c>
       <c r="G13" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H13" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J13" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="K13" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="L13">
         <v>4.0441125317019988E-2</v>
@@ -6736,13 +6553,13 @@
     </row>
     <row r="14" spans="2:13">
       <c r="B14" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C14" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="D14" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -6751,16 +6568,16 @@
         <v>21</v>
       </c>
       <c r="G14" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H14" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J14" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="K14" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="L14">
         <v>3.1156738745546861</v>
@@ -6771,13 +6588,13 @@
     </row>
     <row r="15" spans="2:13">
       <c r="B15" t="s">
+        <v>171</v>
+      </c>
+      <c r="C15" t="s">
         <v>182</v>
       </c>
-      <c r="C15" t="s">
-        <v>193</v>
-      </c>
       <c r="D15" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -6786,16 +6603,16 @@
         <v>21</v>
       </c>
       <c r="G15" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H15" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J15" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="K15" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="L15">
         <v>1.0095122884700507</v>
@@ -6806,13 +6623,13 @@
     </row>
     <row r="16" spans="2:13">
       <c r="B16" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C16" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="D16" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -6821,16 +6638,16 @@
         <v>21</v>
       </c>
       <c r="G16" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H16" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J16" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="K16" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="L16">
         <v>9.6014343718961292</v>
@@ -6841,13 +6658,13 @@
     </row>
     <row r="17" spans="2:13">
       <c r="B17" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C17" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="D17" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -6856,16 +6673,16 @@
         <v>21</v>
       </c>
       <c r="G17" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H17" t="s">
+        <v>175</v>
+      </c>
+      <c r="J17" t="s">
         <v>186</v>
       </c>
-      <c r="J17" t="s">
-        <v>197</v>
-      </c>
       <c r="K17" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="L17">
         <v>11.664406830498095</v>
@@ -6876,13 +6693,13 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C18" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="D18" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -6891,16 +6708,16 @@
         <v>21</v>
       </c>
       <c r="G18" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H18" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J18" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="K18" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="L18">
         <v>3.3207199574486039</v>
@@ -6911,13 +6728,13 @@
     </row>
     <row r="19" spans="2:13">
       <c r="B19" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C19" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="D19" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -6926,16 +6743,16 @@
         <v>21</v>
       </c>
       <c r="G19" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H19" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J19" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="K19" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="L19">
         <v>9.0718124098924431</v>
@@ -6946,13 +6763,13 @@
     </row>
     <row r="20" spans="2:13">
       <c r="B20" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C20" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="D20" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -6961,16 +6778,16 @@
         <v>21</v>
       </c>
       <c r="G20" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H20" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J20" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="K20" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="L20">
         <v>2.4919323033128578</v>
@@ -6981,13 +6798,13 @@
     </row>
     <row r="21" spans="2:13">
       <c r="B21" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C21" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="D21" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -6996,16 +6813,16 @@
         <v>21</v>
       </c>
       <c r="G21" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H21" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J21" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="K21" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="L21">
         <v>8.1269082914211843</v>
@@ -7016,13 +6833,13 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C22" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="D22" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -7031,16 +6848,16 @@
         <v>21</v>
       </c>
       <c r="G22" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H22" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J22" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="K22" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="L22">
         <v>2.0672282720381219</v>
@@ -7051,13 +6868,13 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C23" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="D23" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -7066,16 +6883,16 @@
         <v>21</v>
       </c>
       <c r="G23" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H23" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J23" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="K23" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="L23">
         <v>6.2367051121823778</v>
@@ -7086,13 +6903,13 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C24" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="D24" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -7101,16 +6918,16 @@
         <v>21</v>
       </c>
       <c r="G24" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H24" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J24" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="K24" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="L24">
         <v>4.9429022151581998</v>
@@ -7121,13 +6938,13 @@
     </row>
     <row r="25" spans="2:13">
       <c r="B25" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C25" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="D25" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -7136,16 +6953,16 @@
         <v>21</v>
       </c>
       <c r="G25" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H25" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J25" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="K25" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="L25">
         <v>6.0583925239792951</v>
@@ -7156,13 +6973,13 @@
     </row>
     <row r="26" spans="2:13">
       <c r="B26" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C26" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="D26" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -7171,16 +6988,16 @@
         <v>21</v>
       </c>
       <c r="G26" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H26" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J26" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="K26" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="L26">
         <v>8.8562728829669233</v>
@@ -7191,13 +7008,13 @@
     </row>
     <row r="27" spans="2:13">
       <c r="B27" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C27" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="D27" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
@@ -7206,16 +7023,16 @@
         <v>21</v>
       </c>
       <c r="G27" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H27" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J27" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="K27" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="L27">
         <v>3.1087651703643377</v>
@@ -7226,13 +7043,13 @@
     </row>
     <row r="28" spans="2:13">
       <c r="B28" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C28" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="D28" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
@@ -7241,16 +7058,16 @@
         <v>21</v>
       </c>
       <c r="G28" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H28" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J28" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="K28" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="L28">
         <v>7.6858099243981899</v>
@@ -7261,13 +7078,13 @@
     </row>
     <row r="29" spans="2:13">
       <c r="B29" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C29" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="D29" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -7276,16 +7093,16 @@
         <v>21</v>
       </c>
       <c r="G29" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H29" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J29" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="K29" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="L29">
         <v>8.8290491423659851</v>
@@ -7296,13 +7113,13 @@
     </row>
     <row r="30" spans="2:13">
       <c r="B30" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C30" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="D30" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -7311,16 +7128,16 @@
         <v>21</v>
       </c>
       <c r="G30" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H30" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J30" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="K30" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="L30">
         <v>3.8593591895550672</v>
@@ -7331,13 +7148,13 @@
     </row>
     <row r="31" spans="2:13">
       <c r="B31" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C31" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="D31" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
@@ -7346,16 +7163,16 @@
         <v>21</v>
       </c>
       <c r="G31" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H31" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J31" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="K31" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="L31">
         <v>8.2308495959667809</v>
@@ -7366,13 +7183,13 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C32" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="D32" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
@@ -7381,16 +7198,16 @@
         <v>21</v>
       </c>
       <c r="G32" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H32" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J32" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="K32" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="L32">
         <v>4.1919248573917418</v>
@@ -7401,13 +7218,13 @@
     </row>
     <row r="33" spans="2:13">
       <c r="B33" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C33" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="D33" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
@@ -7416,16 +7233,16 @@
         <v>21</v>
       </c>
       <c r="G33" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H33" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J33" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="K33" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="L33">
         <v>12.207707960945804</v>
@@ -7436,13 +7253,13 @@
     </row>
     <row r="34" spans="2:13">
       <c r="B34" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C34" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="D34" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E34" t="s">
         <v>10</v>
@@ -7451,16 +7268,16 @@
         <v>21</v>
       </c>
       <c r="G34" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H34" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J34" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="K34" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="L34">
         <v>11.84836321250885</v>
@@ -7471,13 +7288,13 @@
     </row>
     <row r="35" spans="2:13">
       <c r="B35" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C35" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="D35" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
@@ -7486,16 +7303,16 @@
         <v>21</v>
       </c>
       <c r="G35" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H35" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J35" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="K35" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="L35">
         <v>6.614368021654732</v>
@@ -7506,13 +7323,13 @@
     </row>
     <row r="36" spans="2:13">
       <c r="B36" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C36" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="D36" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
@@ -7521,16 +7338,16 @@
         <v>21</v>
       </c>
       <c r="G36" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H36" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J36" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="K36" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="L36">
         <v>2.2140559413717158</v>
@@ -7541,13 +7358,13 @@
     </row>
     <row r="37" spans="2:13">
       <c r="B37" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C37" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="D37" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="E37" t="s">
         <v>10</v>
@@ -7556,16 +7373,16 @@
         <v>21</v>
       </c>
       <c r="G37" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H37" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J37" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="K37" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="L37">
         <v>6.2355425421755246</v>
@@ -7576,13 +7393,13 @@
     </row>
     <row r="38" spans="2:13">
       <c r="B38" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C38" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="D38" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="E38" t="s">
         <v>10</v>
@@ -7591,16 +7408,16 @@
         <v>21</v>
       </c>
       <c r="G38" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H38" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J38" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="K38" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="L38">
         <v>8.5054017076497139</v>
@@ -7611,13 +7428,13 @@
     </row>
     <row r="39" spans="2:13">
       <c r="B39" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C39" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="D39" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="E39" t="s">
         <v>10</v>
@@ -7626,16 +7443,16 @@
         <v>21</v>
       </c>
       <c r="G39" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H39" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J39" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="K39" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="L39">
         <v>4.3103819501195213</v>
@@ -7646,13 +7463,13 @@
     </row>
     <row r="40" spans="2:13">
       <c r="B40" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C40" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="D40" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="E40" t="s">
         <v>10</v>
@@ -7661,16 +7478,16 @@
         <v>21</v>
       </c>
       <c r="G40" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H40" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J40" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="K40" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="L40">
         <v>4.1704201808042445</v>
@@ -7681,13 +7498,13 @@
     </row>
     <row r="41" spans="2:13">
       <c r="B41" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C41" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="D41" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="E41" t="s">
         <v>10</v>
@@ -7696,22 +7513,2677 @@
         <v>21</v>
       </c>
       <c r="G41" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H41" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J41" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="K41" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="L41">
         <v>1.8808781416844131</v>
       </c>
       <c r="M41">
         <v>0.17266493010223849</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{368140A0-F7F0-47A5-8C5D-12FF8C8CA629}">
+  <dimension ref="B9:Z54"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="9" spans="2:26">
+      <c r="B9" t="s">
+        <v>163</v>
+      </c>
+      <c r="J9" t="s">
+        <v>236</v>
+      </c>
+      <c r="O9" t="s">
+        <v>163</v>
+      </c>
+      <c r="W9" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="10" spans="2:26">
+      <c r="B10" t="s">
+        <v>164</v>
+      </c>
+      <c r="C10" t="s">
+        <v>165</v>
+      </c>
+      <c r="D10" t="s">
+        <v>166</v>
+      </c>
+      <c r="E10" t="s">
+        <v>167</v>
+      </c>
+      <c r="F10" t="s">
+        <v>168</v>
+      </c>
+      <c r="G10" t="s">
+        <v>169</v>
+      </c>
+      <c r="H10" t="s">
+        <v>170</v>
+      </c>
+      <c r="J10" t="s">
+        <v>165</v>
+      </c>
+      <c r="K10" t="s">
+        <v>237</v>
+      </c>
+      <c r="L10" t="s">
+        <v>238</v>
+      </c>
+      <c r="M10" t="s">
+        <v>239</v>
+      </c>
+      <c r="O10" t="s">
+        <v>164</v>
+      </c>
+      <c r="P10" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>166</v>
+      </c>
+      <c r="R10" t="s">
+        <v>167</v>
+      </c>
+      <c r="S10" t="s">
+        <v>168</v>
+      </c>
+      <c r="T10" t="s">
+        <v>169</v>
+      </c>
+      <c r="U10" t="s">
+        <v>170</v>
+      </c>
+      <c r="W10" t="s">
+        <v>165</v>
+      </c>
+      <c r="X10" t="s">
+        <v>237</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>238</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="11" spans="2:26">
+      <c r="B11" t="s">
+        <v>171</v>
+      </c>
+      <c r="C11" t="s">
+        <v>271</v>
+      </c>
+      <c r="D11" t="s">
+        <v>272</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" t="s">
+        <v>174</v>
+      </c>
+      <c r="H11" t="s">
+        <v>175</v>
+      </c>
+      <c r="J11" t="s">
+        <v>271</v>
+      </c>
+      <c r="K11" t="s">
+        <v>333</v>
+      </c>
+      <c r="L11">
+        <v>26.081770464705624</v>
+      </c>
+      <c r="M11">
+        <v>0.33938741610056822</v>
+      </c>
+      <c r="O11" t="s">
+        <v>171</v>
+      </c>
+      <c r="P11" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>365</v>
+      </c>
+      <c r="R11" t="s">
+        <v>10</v>
+      </c>
+      <c r="S11" t="s">
+        <v>21</v>
+      </c>
+      <c r="T11" t="s">
+        <v>174</v>
+      </c>
+      <c r="U11" t="s">
+        <v>175</v>
+      </c>
+      <c r="W11" t="s">
+        <v>364</v>
+      </c>
+      <c r="X11" t="s">
+        <v>452</v>
+      </c>
+      <c r="Y11">
+        <v>32.783999999999999</v>
+      </c>
+      <c r="Z11">
+        <v>0.44411288754139</v>
+      </c>
+    </row>
+    <row r="12" spans="2:26">
+      <c r="B12" t="s">
+        <v>171</v>
+      </c>
+      <c r="C12" t="s">
+        <v>273</v>
+      </c>
+      <c r="D12" t="s">
+        <v>274</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" t="s">
+        <v>174</v>
+      </c>
+      <c r="H12" t="s">
+        <v>175</v>
+      </c>
+      <c r="J12" t="s">
+        <v>273</v>
+      </c>
+      <c r="K12" t="s">
+        <v>334</v>
+      </c>
+      <c r="L12">
+        <v>28.326303899090867</v>
+      </c>
+      <c r="M12">
+        <v>0.31672699232591051</v>
+      </c>
+      <c r="O12" t="s">
+        <v>171</v>
+      </c>
+      <c r="P12" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>367</v>
+      </c>
+      <c r="R12" t="s">
+        <v>10</v>
+      </c>
+      <c r="S12" t="s">
+        <v>21</v>
+      </c>
+      <c r="T12" t="s">
+        <v>174</v>
+      </c>
+      <c r="U12" t="s">
+        <v>175</v>
+      </c>
+      <c r="W12" t="s">
+        <v>366</v>
+      </c>
+      <c r="X12" t="s">
+        <v>453</v>
+      </c>
+      <c r="Y12">
+        <v>36.320999999999998</v>
+      </c>
+      <c r="Z12">
+        <v>0.4267889026322102</v>
+      </c>
+    </row>
+    <row r="13" spans="2:26">
+      <c r="B13" t="s">
+        <v>171</v>
+      </c>
+      <c r="C13" t="s">
+        <v>275</v>
+      </c>
+      <c r="D13" t="s">
+        <v>276</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" t="s">
+        <v>174</v>
+      </c>
+      <c r="H13" t="s">
+        <v>175</v>
+      </c>
+      <c r="J13" t="s">
+        <v>275</v>
+      </c>
+      <c r="K13" t="s">
+        <v>335</v>
+      </c>
+      <c r="L13">
+        <v>36.748148815624823</v>
+      </c>
+      <c r="M13">
+        <v>0.24124293159761159</v>
+      </c>
+      <c r="O13" t="s">
+        <v>171</v>
+      </c>
+      <c r="P13" t="s">
+        <v>368</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>369</v>
+      </c>
+      <c r="R13" t="s">
+        <v>10</v>
+      </c>
+      <c r="S13" t="s">
+        <v>21</v>
+      </c>
+      <c r="T13" t="s">
+        <v>174</v>
+      </c>
+      <c r="U13" t="s">
+        <v>175</v>
+      </c>
+      <c r="W13" t="s">
+        <v>368</v>
+      </c>
+      <c r="X13" t="s">
+        <v>454</v>
+      </c>
+      <c r="Y13">
+        <v>43.956000000000003</v>
+      </c>
+      <c r="Z13">
+        <v>0.45005997451255592</v>
+      </c>
+    </row>
+    <row r="14" spans="2:26">
+      <c r="B14" t="s">
+        <v>171</v>
+      </c>
+      <c r="C14" t="s">
+        <v>277</v>
+      </c>
+      <c r="D14" t="s">
+        <v>278</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" t="s">
+        <v>174</v>
+      </c>
+      <c r="H14" t="s">
+        <v>175</v>
+      </c>
+      <c r="J14" t="s">
+        <v>277</v>
+      </c>
+      <c r="K14" t="s">
+        <v>336</v>
+      </c>
+      <c r="L14">
+        <v>33.851015501811965</v>
+      </c>
+      <c r="M14">
+        <v>0.17836569756942919</v>
+      </c>
+      <c r="O14" t="s">
+        <v>171</v>
+      </c>
+      <c r="P14" t="s">
+        <v>370</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>371</v>
+      </c>
+      <c r="R14" t="s">
+        <v>10</v>
+      </c>
+      <c r="S14" t="s">
+        <v>21</v>
+      </c>
+      <c r="T14" t="s">
+        <v>174</v>
+      </c>
+      <c r="U14" t="s">
+        <v>175</v>
+      </c>
+      <c r="W14" t="s">
+        <v>370</v>
+      </c>
+      <c r="X14" t="s">
+        <v>455</v>
+      </c>
+      <c r="Y14">
+        <v>62.099249999999998</v>
+      </c>
+      <c r="Z14">
+        <v>0.420776044292479</v>
+      </c>
+    </row>
+    <row r="15" spans="2:26">
+      <c r="B15" t="s">
+        <v>171</v>
+      </c>
+      <c r="C15" t="s">
+        <v>279</v>
+      </c>
+      <c r="D15" t="s">
+        <v>280</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" t="s">
+        <v>174</v>
+      </c>
+      <c r="H15" t="s">
+        <v>175</v>
+      </c>
+      <c r="J15" t="s">
+        <v>279</v>
+      </c>
+      <c r="K15" t="s">
+        <v>337</v>
+      </c>
+      <c r="L15">
+        <v>29.76120824924126</v>
+      </c>
+      <c r="M15">
+        <v>0.1835874284667649</v>
+      </c>
+      <c r="O15" t="s">
+        <v>171</v>
+      </c>
+      <c r="P15" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>373</v>
+      </c>
+      <c r="R15" t="s">
+        <v>10</v>
+      </c>
+      <c r="S15" t="s">
+        <v>21</v>
+      </c>
+      <c r="T15" t="s">
+        <v>174</v>
+      </c>
+      <c r="U15" t="s">
+        <v>175</v>
+      </c>
+      <c r="W15" t="s">
+        <v>372</v>
+      </c>
+      <c r="X15" t="s">
+        <v>456</v>
+      </c>
+      <c r="Y15">
+        <v>0.38324999999999998</v>
+      </c>
+      <c r="Z15">
+        <v>0.3586460374519268</v>
+      </c>
+    </row>
+    <row r="16" spans="2:26">
+      <c r="B16" t="s">
+        <v>171</v>
+      </c>
+      <c r="C16" t="s">
+        <v>281</v>
+      </c>
+      <c r="D16" t="s">
+        <v>282</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" t="s">
+        <v>174</v>
+      </c>
+      <c r="H16" t="s">
+        <v>175</v>
+      </c>
+      <c r="J16" t="s">
+        <v>281</v>
+      </c>
+      <c r="K16" t="s">
+        <v>338</v>
+      </c>
+      <c r="L16">
+        <v>13.047413180463023</v>
+      </c>
+      <c r="M16">
+        <v>0.11846842726897321</v>
+      </c>
+      <c r="O16" t="s">
+        <v>171</v>
+      </c>
+      <c r="P16" t="s">
+        <v>374</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>375</v>
+      </c>
+      <c r="R16" t="s">
+        <v>10</v>
+      </c>
+      <c r="S16" t="s">
+        <v>21</v>
+      </c>
+      <c r="T16" t="s">
+        <v>174</v>
+      </c>
+      <c r="U16" t="s">
+        <v>175</v>
+      </c>
+      <c r="W16" t="s">
+        <v>374</v>
+      </c>
+      <c r="X16" t="s">
+        <v>457</v>
+      </c>
+      <c r="Y16">
+        <v>56.725499999999997</v>
+      </c>
+      <c r="Z16">
+        <v>0.4678326459120476</v>
+      </c>
+    </row>
+    <row r="17" spans="2:26">
+      <c r="B17" t="s">
+        <v>171</v>
+      </c>
+      <c r="C17" t="s">
+        <v>283</v>
+      </c>
+      <c r="D17" t="s">
+        <v>284</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" t="s">
+        <v>174</v>
+      </c>
+      <c r="H17" t="s">
+        <v>175</v>
+      </c>
+      <c r="J17" t="s">
+        <v>283</v>
+      </c>
+      <c r="K17" t="s">
+        <v>339</v>
+      </c>
+      <c r="L17">
+        <v>23.637816650626842</v>
+      </c>
+      <c r="M17">
+        <v>0.1537391571572389</v>
+      </c>
+      <c r="O17" t="s">
+        <v>171</v>
+      </c>
+      <c r="P17" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>377</v>
+      </c>
+      <c r="R17" t="s">
+        <v>10</v>
+      </c>
+      <c r="S17" t="s">
+        <v>21</v>
+      </c>
+      <c r="T17" t="s">
+        <v>174</v>
+      </c>
+      <c r="U17" t="s">
+        <v>175</v>
+      </c>
+      <c r="W17" t="s">
+        <v>376</v>
+      </c>
+      <c r="X17" t="s">
+        <v>458</v>
+      </c>
+      <c r="Y17">
+        <v>58.03275</v>
+      </c>
+      <c r="Z17">
+        <v>0.41285964472242181</v>
+      </c>
+    </row>
+    <row r="18" spans="2:26">
+      <c r="B18" t="s">
+        <v>171</v>
+      </c>
+      <c r="C18" t="s">
+        <v>285</v>
+      </c>
+      <c r="D18" t="s">
+        <v>286</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" t="s">
+        <v>174</v>
+      </c>
+      <c r="H18" t="s">
+        <v>175</v>
+      </c>
+      <c r="J18" t="s">
+        <v>285</v>
+      </c>
+      <c r="K18" t="s">
+        <v>340</v>
+      </c>
+      <c r="L18">
+        <v>50.076680799526407</v>
+      </c>
+      <c r="M18">
+        <v>0.19002505627190239</v>
+      </c>
+      <c r="O18" t="s">
+        <v>171</v>
+      </c>
+      <c r="P18" t="s">
+        <v>378</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>379</v>
+      </c>
+      <c r="R18" t="s">
+        <v>10</v>
+      </c>
+      <c r="S18" t="s">
+        <v>21</v>
+      </c>
+      <c r="T18" t="s">
+        <v>174</v>
+      </c>
+      <c r="U18" t="s">
+        <v>175</v>
+      </c>
+      <c r="W18" t="s">
+        <v>378</v>
+      </c>
+      <c r="X18" t="s">
+        <v>459</v>
+      </c>
+      <c r="Y18">
+        <v>28.478249999999999</v>
+      </c>
+      <c r="Z18">
+        <v>0.31013048721759129</v>
+      </c>
+    </row>
+    <row r="19" spans="2:26">
+      <c r="B19" t="s">
+        <v>171</v>
+      </c>
+      <c r="C19" t="s">
+        <v>287</v>
+      </c>
+      <c r="D19" t="s">
+        <v>288</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" t="s">
+        <v>174</v>
+      </c>
+      <c r="H19" t="s">
+        <v>175</v>
+      </c>
+      <c r="J19" t="s">
+        <v>287</v>
+      </c>
+      <c r="K19" t="s">
+        <v>341</v>
+      </c>
+      <c r="L19">
+        <v>22.504679657777121</v>
+      </c>
+      <c r="M19">
+        <v>0.43998684438339841</v>
+      </c>
+      <c r="O19" t="s">
+        <v>171</v>
+      </c>
+      <c r="P19" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>381</v>
+      </c>
+      <c r="R19" t="s">
+        <v>10</v>
+      </c>
+      <c r="S19" t="s">
+        <v>21</v>
+      </c>
+      <c r="T19" t="s">
+        <v>174</v>
+      </c>
+      <c r="U19" t="s">
+        <v>175</v>
+      </c>
+      <c r="W19" t="s">
+        <v>380</v>
+      </c>
+      <c r="X19" t="s">
+        <v>460</v>
+      </c>
+      <c r="Y19">
+        <v>22.079249999999998</v>
+      </c>
+      <c r="Z19">
+        <v>0.3223061905611202</v>
+      </c>
+    </row>
+    <row r="20" spans="2:26">
+      <c r="B20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C20" t="s">
+        <v>289</v>
+      </c>
+      <c r="D20" t="s">
+        <v>290</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" t="s">
+        <v>174</v>
+      </c>
+      <c r="H20" t="s">
+        <v>175</v>
+      </c>
+      <c r="J20" t="s">
+        <v>289</v>
+      </c>
+      <c r="K20" t="s">
+        <v>342</v>
+      </c>
+      <c r="L20">
+        <v>39.022668784713879</v>
+      </c>
+      <c r="M20">
+        <v>0.30226720130549178</v>
+      </c>
+      <c r="O20" t="s">
+        <v>171</v>
+      </c>
+      <c r="P20" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>383</v>
+      </c>
+      <c r="R20" t="s">
+        <v>10</v>
+      </c>
+      <c r="S20" t="s">
+        <v>21</v>
+      </c>
+      <c r="T20" t="s">
+        <v>174</v>
+      </c>
+      <c r="U20" t="s">
+        <v>175</v>
+      </c>
+      <c r="W20" t="s">
+        <v>382</v>
+      </c>
+      <c r="X20" t="s">
+        <v>461</v>
+      </c>
+      <c r="Y20">
+        <v>29.961749999999999</v>
+      </c>
+      <c r="Z20">
+        <v>0.33421489525964382</v>
+      </c>
+    </row>
+    <row r="21" spans="2:26">
+      <c r="B21" t="s">
+        <v>171</v>
+      </c>
+      <c r="C21" t="s">
+        <v>291</v>
+      </c>
+      <c r="D21" t="s">
+        <v>292</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" t="s">
+        <v>174</v>
+      </c>
+      <c r="H21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J21" t="s">
+        <v>291</v>
+      </c>
+      <c r="K21" t="s">
+        <v>343</v>
+      </c>
+      <c r="L21">
+        <v>12.527007796473459</v>
+      </c>
+      <c r="M21">
+        <v>0.26335249621019208</v>
+      </c>
+      <c r="O21" t="s">
+        <v>171</v>
+      </c>
+      <c r="P21" t="s">
+        <v>384</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>385</v>
+      </c>
+      <c r="R21" t="s">
+        <v>10</v>
+      </c>
+      <c r="S21" t="s">
+        <v>21</v>
+      </c>
+      <c r="T21" t="s">
+        <v>174</v>
+      </c>
+      <c r="U21" t="s">
+        <v>175</v>
+      </c>
+      <c r="W21" t="s">
+        <v>384</v>
+      </c>
+      <c r="X21" t="s">
+        <v>462</v>
+      </c>
+      <c r="Y21">
+        <v>117.89700000000001</v>
+      </c>
+      <c r="Z21">
+        <v>0.4454005763280634</v>
+      </c>
+    </row>
+    <row r="22" spans="2:26">
+      <c r="B22" t="s">
+        <v>171</v>
+      </c>
+      <c r="C22" t="s">
+        <v>293</v>
+      </c>
+      <c r="D22" t="s">
+        <v>294</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" t="s">
+        <v>174</v>
+      </c>
+      <c r="H22" t="s">
+        <v>175</v>
+      </c>
+      <c r="J22" t="s">
+        <v>293</v>
+      </c>
+      <c r="K22" t="s">
+        <v>344</v>
+      </c>
+      <c r="L22">
+        <v>22.322239264526591</v>
+      </c>
+      <c r="M22">
+        <v>0.24546553943130331</v>
+      </c>
+      <c r="O22" t="s">
+        <v>171</v>
+      </c>
+      <c r="P22" t="s">
+        <v>386</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>387</v>
+      </c>
+      <c r="R22" t="s">
+        <v>10</v>
+      </c>
+      <c r="S22" t="s">
+        <v>21</v>
+      </c>
+      <c r="T22" t="s">
+        <v>174</v>
+      </c>
+      <c r="U22" t="s">
+        <v>175</v>
+      </c>
+      <c r="W22" t="s">
+        <v>386</v>
+      </c>
+      <c r="X22" t="s">
+        <v>463</v>
+      </c>
+      <c r="Y22">
+        <v>75.481499999999997</v>
+      </c>
+      <c r="Z22">
+        <v>0.39947482218024288</v>
+      </c>
+    </row>
+    <row r="23" spans="2:26">
+      <c r="B23" t="s">
+        <v>171</v>
+      </c>
+      <c r="C23" t="s">
+        <v>295</v>
+      </c>
+      <c r="D23" t="s">
+        <v>296</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" t="s">
+        <v>174</v>
+      </c>
+      <c r="H23" t="s">
+        <v>175</v>
+      </c>
+      <c r="J23" t="s">
+        <v>295</v>
+      </c>
+      <c r="K23" t="s">
+        <v>345</v>
+      </c>
+      <c r="L23">
+        <v>6.1151684514715345</v>
+      </c>
+      <c r="M23">
+        <v>0.44244733217755411</v>
+      </c>
+      <c r="O23" t="s">
+        <v>171</v>
+      </c>
+      <c r="P23" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>389</v>
+      </c>
+      <c r="R23" t="s">
+        <v>10</v>
+      </c>
+      <c r="S23" t="s">
+        <v>21</v>
+      </c>
+      <c r="T23" t="s">
+        <v>174</v>
+      </c>
+      <c r="U23" t="s">
+        <v>175</v>
+      </c>
+      <c r="W23" t="s">
+        <v>388</v>
+      </c>
+      <c r="X23" t="s">
+        <v>464</v>
+      </c>
+      <c r="Y23">
+        <v>10.68975</v>
+      </c>
+      <c r="Z23">
+        <v>0.2858957309818449</v>
+      </c>
+    </row>
+    <row r="24" spans="2:26">
+      <c r="B24" t="s">
+        <v>171</v>
+      </c>
+      <c r="C24" t="s">
+        <v>297</v>
+      </c>
+      <c r="D24" t="s">
+        <v>298</v>
+      </c>
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24" t="s">
+        <v>174</v>
+      </c>
+      <c r="H24" t="s">
+        <v>175</v>
+      </c>
+      <c r="J24" t="s">
+        <v>297</v>
+      </c>
+      <c r="K24" t="s">
+        <v>346</v>
+      </c>
+      <c r="L24">
+        <v>4.1221966299799098</v>
+      </c>
+      <c r="M24">
+        <v>0.47272019788829328</v>
+      </c>
+      <c r="O24" t="s">
+        <v>171</v>
+      </c>
+      <c r="P24" t="s">
+        <v>390</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>391</v>
+      </c>
+      <c r="R24" t="s">
+        <v>10</v>
+      </c>
+      <c r="S24" t="s">
+        <v>21</v>
+      </c>
+      <c r="T24" t="s">
+        <v>174</v>
+      </c>
+      <c r="U24" t="s">
+        <v>175</v>
+      </c>
+      <c r="W24" t="s">
+        <v>390</v>
+      </c>
+      <c r="X24" t="s">
+        <v>465</v>
+      </c>
+      <c r="Y24">
+        <v>82.607249999999993</v>
+      </c>
+      <c r="Z24">
+        <v>0.4138948789420363</v>
+      </c>
+    </row>
+    <row r="25" spans="2:26">
+      <c r="B25" t="s">
+        <v>171</v>
+      </c>
+      <c r="C25" t="s">
+        <v>299</v>
+      </c>
+      <c r="D25" t="s">
+        <v>300</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" t="s">
+        <v>174</v>
+      </c>
+      <c r="H25" t="s">
+        <v>175</v>
+      </c>
+      <c r="J25" t="s">
+        <v>299</v>
+      </c>
+      <c r="K25" t="s">
+        <v>347</v>
+      </c>
+      <c r="L25">
+        <v>6.7028485191473308E-2</v>
+      </c>
+      <c r="M25">
+        <v>0.41432793234675691</v>
+      </c>
+      <c r="O25" t="s">
+        <v>171</v>
+      </c>
+      <c r="P25" t="s">
+        <v>392</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>393</v>
+      </c>
+      <c r="R25" t="s">
+        <v>10</v>
+      </c>
+      <c r="S25" t="s">
+        <v>21</v>
+      </c>
+      <c r="T25" t="s">
+        <v>174</v>
+      </c>
+      <c r="U25" t="s">
+        <v>175</v>
+      </c>
+      <c r="W25" t="s">
+        <v>392</v>
+      </c>
+      <c r="X25" t="s">
+        <v>466</v>
+      </c>
+      <c r="Y25">
+        <v>28.239750000000001</v>
+      </c>
+      <c r="Z25">
+        <v>0.39283819950969068</v>
+      </c>
+    </row>
+    <row r="26" spans="2:26">
+      <c r="B26" t="s">
+        <v>171</v>
+      </c>
+      <c r="C26" t="s">
+        <v>301</v>
+      </c>
+      <c r="D26" t="s">
+        <v>302</v>
+      </c>
+      <c r="E26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" t="s">
+        <v>174</v>
+      </c>
+      <c r="H26" t="s">
+        <v>175</v>
+      </c>
+      <c r="J26" t="s">
+        <v>301</v>
+      </c>
+      <c r="K26" t="s">
+        <v>348</v>
+      </c>
+      <c r="L26">
+        <v>1.3102559495532347</v>
+      </c>
+      <c r="M26">
+        <v>0.51823166137173471</v>
+      </c>
+      <c r="O26" t="s">
+        <v>171</v>
+      </c>
+      <c r="P26" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>395</v>
+      </c>
+      <c r="R26" t="s">
+        <v>10</v>
+      </c>
+      <c r="S26" t="s">
+        <v>21</v>
+      </c>
+      <c r="T26" t="s">
+        <v>174</v>
+      </c>
+      <c r="U26" t="s">
+        <v>175</v>
+      </c>
+      <c r="W26" t="s">
+        <v>394</v>
+      </c>
+      <c r="X26" t="s">
+        <v>467</v>
+      </c>
+      <c r="Y26">
+        <v>1.9132499999999999</v>
+      </c>
+      <c r="Z26">
+        <v>0.24373705543466159</v>
+      </c>
+    </row>
+    <row r="27" spans="2:26">
+      <c r="B27" t="s">
+        <v>171</v>
+      </c>
+      <c r="C27" t="s">
+        <v>303</v>
+      </c>
+      <c r="D27" t="s">
+        <v>304</v>
+      </c>
+      <c r="E27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27" t="s">
+        <v>174</v>
+      </c>
+      <c r="H27" t="s">
+        <v>175</v>
+      </c>
+      <c r="J27" t="s">
+        <v>303</v>
+      </c>
+      <c r="K27" t="s">
+        <v>349</v>
+      </c>
+      <c r="L27">
+        <v>51.171736048895305</v>
+      </c>
+      <c r="M27">
+        <v>0.1753269736233318</v>
+      </c>
+      <c r="O27" t="s">
+        <v>171</v>
+      </c>
+      <c r="P27" t="s">
+        <v>396</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>397</v>
+      </c>
+      <c r="R27" t="s">
+        <v>10</v>
+      </c>
+      <c r="S27" t="s">
+        <v>21</v>
+      </c>
+      <c r="T27" t="s">
+        <v>174</v>
+      </c>
+      <c r="U27" t="s">
+        <v>175</v>
+      </c>
+      <c r="W27" t="s">
+        <v>396</v>
+      </c>
+      <c r="X27" t="s">
+        <v>468</v>
+      </c>
+      <c r="Y27">
+        <v>63.731250000000003</v>
+      </c>
+      <c r="Z27">
+        <v>0.4483325413452795</v>
+      </c>
+    </row>
+    <row r="28" spans="2:26">
+      <c r="B28" t="s">
+        <v>171</v>
+      </c>
+      <c r="C28" t="s">
+        <v>305</v>
+      </c>
+      <c r="D28" t="s">
+        <v>306</v>
+      </c>
+      <c r="E28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28" t="s">
+        <v>174</v>
+      </c>
+      <c r="H28" t="s">
+        <v>175</v>
+      </c>
+      <c r="J28" t="s">
+        <v>305</v>
+      </c>
+      <c r="K28" t="s">
+        <v>350</v>
+      </c>
+      <c r="L28">
+        <v>27.131882337818411</v>
+      </c>
+      <c r="M28">
+        <v>0.13421919246645389</v>
+      </c>
+      <c r="O28" t="s">
+        <v>171</v>
+      </c>
+      <c r="P28" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>399</v>
+      </c>
+      <c r="R28" t="s">
+        <v>10</v>
+      </c>
+      <c r="S28" t="s">
+        <v>21</v>
+      </c>
+      <c r="T28" t="s">
+        <v>174</v>
+      </c>
+      <c r="U28" t="s">
+        <v>175</v>
+      </c>
+      <c r="W28" t="s">
+        <v>398</v>
+      </c>
+      <c r="X28" t="s">
+        <v>469</v>
+      </c>
+      <c r="Y28">
+        <v>38.451000000000001</v>
+      </c>
+      <c r="Z28">
+        <v>0.41699608360155571</v>
+      </c>
+    </row>
+    <row r="29" spans="2:26">
+      <c r="B29" t="s">
+        <v>171</v>
+      </c>
+      <c r="C29" t="s">
+        <v>307</v>
+      </c>
+      <c r="D29" t="s">
+        <v>308</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" t="s">
+        <v>174</v>
+      </c>
+      <c r="H29" t="s">
+        <v>175</v>
+      </c>
+      <c r="J29" t="s">
+        <v>307</v>
+      </c>
+      <c r="K29" t="s">
+        <v>351</v>
+      </c>
+      <c r="L29">
+        <v>8.7915989873091043</v>
+      </c>
+      <c r="M29">
+        <v>0.33157900311052629</v>
+      </c>
+      <c r="O29" t="s">
+        <v>171</v>
+      </c>
+      <c r="P29" t="s">
+        <v>400</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>401</v>
+      </c>
+      <c r="R29" t="s">
+        <v>10</v>
+      </c>
+      <c r="S29" t="s">
+        <v>21</v>
+      </c>
+      <c r="T29" t="s">
+        <v>174</v>
+      </c>
+      <c r="U29" t="s">
+        <v>175</v>
+      </c>
+      <c r="W29" t="s">
+        <v>400</v>
+      </c>
+      <c r="X29" t="s">
+        <v>470</v>
+      </c>
+      <c r="Y29">
+        <v>64.533749999999998</v>
+      </c>
+      <c r="Z29">
+        <v>0.49947203939427631</v>
+      </c>
+    </row>
+    <row r="30" spans="2:26">
+      <c r="B30" t="s">
+        <v>171</v>
+      </c>
+      <c r="C30" t="s">
+        <v>309</v>
+      </c>
+      <c r="D30" t="s">
+        <v>310</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30" t="s">
+        <v>174</v>
+      </c>
+      <c r="H30" t="s">
+        <v>175</v>
+      </c>
+      <c r="J30" t="s">
+        <v>309</v>
+      </c>
+      <c r="K30" t="s">
+        <v>352</v>
+      </c>
+      <c r="L30">
+        <v>26.915511431987859</v>
+      </c>
+      <c r="M30">
+        <v>0.17204244166879709</v>
+      </c>
+      <c r="O30" t="s">
+        <v>171</v>
+      </c>
+      <c r="P30" t="s">
+        <v>402</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>403</v>
+      </c>
+      <c r="R30" t="s">
+        <v>10</v>
+      </c>
+      <c r="S30" t="s">
+        <v>21</v>
+      </c>
+      <c r="T30" t="s">
+        <v>174</v>
+      </c>
+      <c r="U30" t="s">
+        <v>175</v>
+      </c>
+      <c r="W30" t="s">
+        <v>402</v>
+      </c>
+      <c r="X30" t="s">
+        <v>471</v>
+      </c>
+      <c r="Y30">
+        <v>44.370750000000001</v>
+      </c>
+      <c r="Z30">
+        <v>0.45077590772414738</v>
+      </c>
+    </row>
+    <row r="31" spans="2:26">
+      <c r="B31" t="s">
+        <v>171</v>
+      </c>
+      <c r="C31" t="s">
+        <v>311</v>
+      </c>
+      <c r="D31" t="s">
+        <v>312</v>
+      </c>
+      <c r="E31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" t="s">
+        <v>174</v>
+      </c>
+      <c r="H31" t="s">
+        <v>175</v>
+      </c>
+      <c r="J31" t="s">
+        <v>311</v>
+      </c>
+      <c r="K31" t="s">
+        <v>353</v>
+      </c>
+      <c r="L31">
+        <v>7.5025171344716721</v>
+      </c>
+      <c r="M31">
+        <v>0.102078386690078</v>
+      </c>
+      <c r="O31" t="s">
+        <v>171</v>
+      </c>
+      <c r="P31" t="s">
+        <v>404</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>405</v>
+      </c>
+      <c r="R31" t="s">
+        <v>10</v>
+      </c>
+      <c r="S31" t="s">
+        <v>21</v>
+      </c>
+      <c r="T31" t="s">
+        <v>174</v>
+      </c>
+      <c r="U31" t="s">
+        <v>175</v>
+      </c>
+      <c r="W31" t="s">
+        <v>404</v>
+      </c>
+      <c r="X31" t="s">
+        <v>472</v>
+      </c>
+      <c r="Y31">
+        <v>38.15925</v>
+      </c>
+      <c r="Z31">
+        <v>0.42518909184060127</v>
+      </c>
+    </row>
+    <row r="32" spans="2:26">
+      <c r="B32" t="s">
+        <v>171</v>
+      </c>
+      <c r="C32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D32" t="s">
+        <v>314</v>
+      </c>
+      <c r="E32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" t="s">
+        <v>174</v>
+      </c>
+      <c r="H32" t="s">
+        <v>175</v>
+      </c>
+      <c r="J32" t="s">
+        <v>313</v>
+      </c>
+      <c r="K32" t="s">
+        <v>354</v>
+      </c>
+      <c r="L32">
+        <v>21.853336570084423</v>
+      </c>
+      <c r="M32">
+        <v>0.2470260197032213</v>
+      </c>
+      <c r="O32" t="s">
+        <v>171</v>
+      </c>
+      <c r="P32" t="s">
+        <v>406</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>407</v>
+      </c>
+      <c r="R32" t="s">
+        <v>10</v>
+      </c>
+      <c r="S32" t="s">
+        <v>21</v>
+      </c>
+      <c r="T32" t="s">
+        <v>174</v>
+      </c>
+      <c r="U32" t="s">
+        <v>175</v>
+      </c>
+      <c r="W32" t="s">
+        <v>406</v>
+      </c>
+      <c r="X32" t="s">
+        <v>473</v>
+      </c>
+      <c r="Y32">
+        <v>3.38625</v>
+      </c>
+      <c r="Z32">
+        <v>0.27397097122901398</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26">
+      <c r="B33" t="s">
+        <v>171</v>
+      </c>
+      <c r="C33" t="s">
+        <v>315</v>
+      </c>
+      <c r="D33" t="s">
+        <v>316</v>
+      </c>
+      <c r="E33" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33" t="s">
+        <v>174</v>
+      </c>
+      <c r="H33" t="s">
+        <v>175</v>
+      </c>
+      <c r="J33" t="s">
+        <v>315</v>
+      </c>
+      <c r="K33" t="s">
+        <v>355</v>
+      </c>
+      <c r="L33">
+        <v>40.036304639772588</v>
+      </c>
+      <c r="M33">
+        <v>0.22158847806059459</v>
+      </c>
+      <c r="O33" t="s">
+        <v>171</v>
+      </c>
+      <c r="P33" t="s">
+        <v>408</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>409</v>
+      </c>
+      <c r="R33" t="s">
+        <v>10</v>
+      </c>
+      <c r="S33" t="s">
+        <v>21</v>
+      </c>
+      <c r="T33" t="s">
+        <v>174</v>
+      </c>
+      <c r="U33" t="s">
+        <v>175</v>
+      </c>
+      <c r="W33" t="s">
+        <v>408</v>
+      </c>
+      <c r="X33" t="s">
+        <v>474</v>
+      </c>
+      <c r="Y33">
+        <v>30.597750000000001</v>
+      </c>
+      <c r="Z33">
+        <v>0.45321604354945533</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26">
+      <c r="B34" t="s">
+        <v>171</v>
+      </c>
+      <c r="C34" t="s">
+        <v>317</v>
+      </c>
+      <c r="D34" t="s">
+        <v>318</v>
+      </c>
+      <c r="E34" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34" t="s">
+        <v>174</v>
+      </c>
+      <c r="H34" t="s">
+        <v>175</v>
+      </c>
+      <c r="J34" t="s">
+        <v>317</v>
+      </c>
+      <c r="K34" t="s">
+        <v>356</v>
+      </c>
+      <c r="L34">
+        <v>7.0903888161806279</v>
+      </c>
+      <c r="M34">
+        <v>0.126349887785319</v>
+      </c>
+      <c r="O34" t="s">
+        <v>171</v>
+      </c>
+      <c r="P34" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>411</v>
+      </c>
+      <c r="R34" t="s">
+        <v>10</v>
+      </c>
+      <c r="S34" t="s">
+        <v>21</v>
+      </c>
+      <c r="T34" t="s">
+        <v>174</v>
+      </c>
+      <c r="U34" t="s">
+        <v>175</v>
+      </c>
+      <c r="W34" t="s">
+        <v>410</v>
+      </c>
+      <c r="X34" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y34">
+        <v>33.609749999999998</v>
+      </c>
+      <c r="Z34">
+        <v>0.397480074831774</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26">
+      <c r="B35" t="s">
+        <v>171</v>
+      </c>
+      <c r="C35" t="s">
+        <v>319</v>
+      </c>
+      <c r="D35" t="s">
+        <v>320</v>
+      </c>
+      <c r="E35" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35" t="s">
+        <v>174</v>
+      </c>
+      <c r="H35" t="s">
+        <v>175</v>
+      </c>
+      <c r="J35" t="s">
+        <v>319</v>
+      </c>
+      <c r="K35" t="s">
+        <v>357</v>
+      </c>
+      <c r="L35">
+        <v>16.970662525397827</v>
+      </c>
+      <c r="M35">
+        <v>0.2876476609673595</v>
+      </c>
+      <c r="O35" t="s">
+        <v>171</v>
+      </c>
+      <c r="P35" t="s">
+        <v>412</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>413</v>
+      </c>
+      <c r="R35" t="s">
+        <v>10</v>
+      </c>
+      <c r="S35" t="s">
+        <v>21</v>
+      </c>
+      <c r="T35" t="s">
+        <v>174</v>
+      </c>
+      <c r="U35" t="s">
+        <v>175</v>
+      </c>
+      <c r="W35" t="s">
+        <v>412</v>
+      </c>
+      <c r="X35" t="s">
+        <v>476</v>
+      </c>
+      <c r="Y35">
+        <v>58.474499999999999</v>
+      </c>
+      <c r="Z35">
+        <v>0.3742804525886429</v>
+      </c>
+    </row>
+    <row r="36" spans="2:26">
+      <c r="B36" t="s">
+        <v>171</v>
+      </c>
+      <c r="C36" t="s">
+        <v>321</v>
+      </c>
+      <c r="D36" t="s">
+        <v>322</v>
+      </c>
+      <c r="E36" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" t="s">
+        <v>21</v>
+      </c>
+      <c r="G36" t="s">
+        <v>174</v>
+      </c>
+      <c r="H36" t="s">
+        <v>175</v>
+      </c>
+      <c r="J36" t="s">
+        <v>321</v>
+      </c>
+      <c r="K36" t="s">
+        <v>358</v>
+      </c>
+      <c r="L36">
+        <v>2.5242004930684354</v>
+      </c>
+      <c r="M36">
+        <v>9.3541201112904898E-2</v>
+      </c>
+      <c r="O36" t="s">
+        <v>171</v>
+      </c>
+      <c r="P36" t="s">
+        <v>414</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>415</v>
+      </c>
+      <c r="R36" t="s">
+        <v>10</v>
+      </c>
+      <c r="S36" t="s">
+        <v>21</v>
+      </c>
+      <c r="T36" t="s">
+        <v>174</v>
+      </c>
+      <c r="U36" t="s">
+        <v>175</v>
+      </c>
+      <c r="W36" t="s">
+        <v>414</v>
+      </c>
+      <c r="X36" t="s">
+        <v>477</v>
+      </c>
+      <c r="Y36">
+        <v>18.711749999999999</v>
+      </c>
+      <c r="Z36">
+        <v>0.2850753309410175</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26">
+      <c r="B37" t="s">
+        <v>171</v>
+      </c>
+      <c r="C37" t="s">
+        <v>323</v>
+      </c>
+      <c r="D37" t="s">
+        <v>324</v>
+      </c>
+      <c r="E37" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" t="s">
+        <v>21</v>
+      </c>
+      <c r="G37" t="s">
+        <v>174</v>
+      </c>
+      <c r="H37" t="s">
+        <v>175</v>
+      </c>
+      <c r="J37" t="s">
+        <v>323</v>
+      </c>
+      <c r="K37" t="s">
+        <v>359</v>
+      </c>
+      <c r="L37">
+        <v>5.5071261071764246</v>
+      </c>
+      <c r="M37">
+        <v>0.34206800892605482</v>
+      </c>
+      <c r="O37" t="s">
+        <v>171</v>
+      </c>
+      <c r="P37" t="s">
+        <v>416</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>417</v>
+      </c>
+      <c r="R37" t="s">
+        <v>10</v>
+      </c>
+      <c r="S37" t="s">
+        <v>21</v>
+      </c>
+      <c r="T37" t="s">
+        <v>174</v>
+      </c>
+      <c r="U37" t="s">
+        <v>175</v>
+      </c>
+      <c r="W37" t="s">
+        <v>416</v>
+      </c>
+      <c r="X37" t="s">
+        <v>478</v>
+      </c>
+      <c r="Y37">
+        <v>29.186250000000001</v>
+      </c>
+      <c r="Z37">
+        <v>0.35239758613659811</v>
+      </c>
+    </row>
+    <row r="38" spans="2:26">
+      <c r="B38" t="s">
+        <v>171</v>
+      </c>
+      <c r="C38" t="s">
+        <v>325</v>
+      </c>
+      <c r="D38" t="s">
+        <v>326</v>
+      </c>
+      <c r="E38" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" t="s">
+        <v>21</v>
+      </c>
+      <c r="G38" t="s">
+        <v>174</v>
+      </c>
+      <c r="H38" t="s">
+        <v>175</v>
+      </c>
+      <c r="J38" t="s">
+        <v>325</v>
+      </c>
+      <c r="K38" t="s">
+        <v>360</v>
+      </c>
+      <c r="L38">
+        <v>8.4886449615793467</v>
+      </c>
+      <c r="M38">
+        <v>0.33231574315319728</v>
+      </c>
+      <c r="O38" t="s">
+        <v>171</v>
+      </c>
+      <c r="P38" t="s">
+        <v>418</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>419</v>
+      </c>
+      <c r="R38" t="s">
+        <v>10</v>
+      </c>
+      <c r="S38" t="s">
+        <v>21</v>
+      </c>
+      <c r="T38" t="s">
+        <v>174</v>
+      </c>
+      <c r="U38" t="s">
+        <v>175</v>
+      </c>
+      <c r="W38" t="s">
+        <v>418</v>
+      </c>
+      <c r="X38" t="s">
+        <v>479</v>
+      </c>
+      <c r="Y38">
+        <v>14.49</v>
+      </c>
+      <c r="Z38">
+        <v>0.4104874743436856</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26">
+      <c r="B39" t="s">
+        <v>171</v>
+      </c>
+      <c r="C39" t="s">
+        <v>327</v>
+      </c>
+      <c r="D39" t="s">
+        <v>328</v>
+      </c>
+      <c r="E39" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" t="s">
+        <v>21</v>
+      </c>
+      <c r="G39" t="s">
+        <v>174</v>
+      </c>
+      <c r="H39" t="s">
+        <v>175</v>
+      </c>
+      <c r="J39" t="s">
+        <v>327</v>
+      </c>
+      <c r="K39" t="s">
+        <v>361</v>
+      </c>
+      <c r="L39">
+        <v>8.4075540995285696</v>
+      </c>
+      <c r="M39">
+        <v>0.28011366210530497</v>
+      </c>
+      <c r="O39" t="s">
+        <v>171</v>
+      </c>
+      <c r="P39" t="s">
+        <v>420</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>421</v>
+      </c>
+      <c r="R39" t="s">
+        <v>10</v>
+      </c>
+      <c r="S39" t="s">
+        <v>21</v>
+      </c>
+      <c r="T39" t="s">
+        <v>174</v>
+      </c>
+      <c r="U39" t="s">
+        <v>175</v>
+      </c>
+      <c r="W39" t="s">
+        <v>420</v>
+      </c>
+      <c r="X39" t="s">
+        <v>480</v>
+      </c>
+      <c r="Y39">
+        <v>64.437749999999994</v>
+      </c>
+      <c r="Z39">
+        <v>0.4224374651715968</v>
+      </c>
+    </row>
+    <row r="40" spans="2:26">
+      <c r="B40" t="s">
+        <v>171</v>
+      </c>
+      <c r="C40" t="s">
+        <v>329</v>
+      </c>
+      <c r="D40" t="s">
+        <v>330</v>
+      </c>
+      <c r="E40" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" t="s">
+        <v>21</v>
+      </c>
+      <c r="G40" t="s">
+        <v>174</v>
+      </c>
+      <c r="H40" t="s">
+        <v>175</v>
+      </c>
+      <c r="J40" t="s">
+        <v>329</v>
+      </c>
+      <c r="K40" t="s">
+        <v>362</v>
+      </c>
+      <c r="L40">
+        <v>15.703622047270191</v>
+      </c>
+      <c r="M40">
+        <v>0.2902999058993756</v>
+      </c>
+      <c r="O40" t="s">
+        <v>171</v>
+      </c>
+      <c r="P40" t="s">
+        <v>422</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>423</v>
+      </c>
+      <c r="R40" t="s">
+        <v>10</v>
+      </c>
+      <c r="S40" t="s">
+        <v>21</v>
+      </c>
+      <c r="T40" t="s">
+        <v>174</v>
+      </c>
+      <c r="U40" t="s">
+        <v>175</v>
+      </c>
+      <c r="W40" t="s">
+        <v>422</v>
+      </c>
+      <c r="X40" t="s">
+        <v>481</v>
+      </c>
+      <c r="Y40">
+        <v>59.085000000000001</v>
+      </c>
+      <c r="Z40">
+        <v>0.3909895628623698</v>
+      </c>
+    </row>
+    <row r="41" spans="2:26">
+      <c r="B41" t="s">
+        <v>171</v>
+      </c>
+      <c r="C41" t="s">
+        <v>331</v>
+      </c>
+      <c r="D41" t="s">
+        <v>332</v>
+      </c>
+      <c r="E41" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" t="s">
+        <v>21</v>
+      </c>
+      <c r="G41" t="s">
+        <v>174</v>
+      </c>
+      <c r="H41" t="s">
+        <v>175</v>
+      </c>
+      <c r="J41" t="s">
+        <v>331</v>
+      </c>
+      <c r="K41" t="s">
+        <v>363</v>
+      </c>
+      <c r="L41">
+        <v>24.074478129461852</v>
+      </c>
+      <c r="M41">
+        <v>0.32175887833734967</v>
+      </c>
+      <c r="O41" t="s">
+        <v>171</v>
+      </c>
+      <c r="P41" t="s">
+        <v>424</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>425</v>
+      </c>
+      <c r="R41" t="s">
+        <v>10</v>
+      </c>
+      <c r="S41" t="s">
+        <v>21</v>
+      </c>
+      <c r="T41" t="s">
+        <v>174</v>
+      </c>
+      <c r="U41" t="s">
+        <v>175</v>
+      </c>
+      <c r="W41" t="s">
+        <v>424</v>
+      </c>
+      <c r="X41" t="s">
+        <v>482</v>
+      </c>
+      <c r="Y41">
+        <v>37.460250000000002</v>
+      </c>
+      <c r="Z41">
+        <v>0.4156656148053956</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26">
+      <c r="O42" t="s">
+        <v>171</v>
+      </c>
+      <c r="P42" t="s">
+        <v>426</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>427</v>
+      </c>
+      <c r="R42" t="s">
+        <v>10</v>
+      </c>
+      <c r="S42" t="s">
+        <v>21</v>
+      </c>
+      <c r="T42" t="s">
+        <v>174</v>
+      </c>
+      <c r="U42" t="s">
+        <v>175</v>
+      </c>
+      <c r="W42" t="s">
+        <v>426</v>
+      </c>
+      <c r="X42" t="s">
+        <v>483</v>
+      </c>
+      <c r="Y42">
+        <v>27.642749999999999</v>
+      </c>
+      <c r="Z42">
+        <v>0.36206437671723612</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26">
+      <c r="O43" t="s">
+        <v>171</v>
+      </c>
+      <c r="P43" t="s">
+        <v>428</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>429</v>
+      </c>
+      <c r="R43" t="s">
+        <v>10</v>
+      </c>
+      <c r="S43" t="s">
+        <v>21</v>
+      </c>
+      <c r="T43" t="s">
+        <v>174</v>
+      </c>
+      <c r="U43" t="s">
+        <v>175</v>
+      </c>
+      <c r="W43" t="s">
+        <v>428</v>
+      </c>
+      <c r="X43" t="s">
+        <v>484</v>
+      </c>
+      <c r="Y43">
+        <v>62.597250000000003</v>
+      </c>
+      <c r="Z43">
+        <v>0.36639621425278329</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26">
+      <c r="O44" t="s">
+        <v>171</v>
+      </c>
+      <c r="P44" t="s">
+        <v>430</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>431</v>
+      </c>
+      <c r="R44" t="s">
+        <v>10</v>
+      </c>
+      <c r="S44" t="s">
+        <v>21</v>
+      </c>
+      <c r="T44" t="s">
+        <v>174</v>
+      </c>
+      <c r="U44" t="s">
+        <v>175</v>
+      </c>
+      <c r="W44" t="s">
+        <v>430</v>
+      </c>
+      <c r="X44" t="s">
+        <v>485</v>
+      </c>
+      <c r="Y44">
+        <v>17.07525</v>
+      </c>
+      <c r="Z44">
+        <v>0.366335622458484</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26">
+      <c r="O45" t="s">
+        <v>171</v>
+      </c>
+      <c r="P45" t="s">
+        <v>432</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>433</v>
+      </c>
+      <c r="R45" t="s">
+        <v>10</v>
+      </c>
+      <c r="S45" t="s">
+        <v>21</v>
+      </c>
+      <c r="T45" t="s">
+        <v>174</v>
+      </c>
+      <c r="U45" t="s">
+        <v>175</v>
+      </c>
+      <c r="W45" t="s">
+        <v>432</v>
+      </c>
+      <c r="X45" t="s">
+        <v>486</v>
+      </c>
+      <c r="Y45">
+        <v>0.42149999999999999</v>
+      </c>
+      <c r="Z45">
+        <v>0.28906735909449488</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26">
+      <c r="O46" t="s">
+        <v>171</v>
+      </c>
+      <c r="P46" t="s">
+        <v>434</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>435</v>
+      </c>
+      <c r="R46" t="s">
+        <v>10</v>
+      </c>
+      <c r="S46" t="s">
+        <v>21</v>
+      </c>
+      <c r="T46" t="s">
+        <v>174</v>
+      </c>
+      <c r="U46" t="s">
+        <v>175</v>
+      </c>
+      <c r="W46" t="s">
+        <v>434</v>
+      </c>
+      <c r="X46" t="s">
+        <v>487</v>
+      </c>
+      <c r="Y46">
+        <v>5.7389999999999999</v>
+      </c>
+      <c r="Z46">
+        <v>0.33165266509529728</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26">
+      <c r="O47" t="s">
+        <v>171</v>
+      </c>
+      <c r="P47" t="s">
+        <v>436</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>437</v>
+      </c>
+      <c r="R47" t="s">
+        <v>10</v>
+      </c>
+      <c r="S47" t="s">
+        <v>21</v>
+      </c>
+      <c r="T47" t="s">
+        <v>174</v>
+      </c>
+      <c r="U47" t="s">
+        <v>175</v>
+      </c>
+      <c r="W47" t="s">
+        <v>436</v>
+      </c>
+      <c r="X47" t="s">
+        <v>488</v>
+      </c>
+      <c r="Y47">
+        <v>1.81725</v>
+      </c>
+      <c r="Z47">
+        <v>0.3242980885897736</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26">
+      <c r="O48" t="s">
+        <v>171</v>
+      </c>
+      <c r="P48" t="s">
+        <v>438</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>439</v>
+      </c>
+      <c r="R48" t="s">
+        <v>10</v>
+      </c>
+      <c r="S48" t="s">
+        <v>21</v>
+      </c>
+      <c r="T48" t="s">
+        <v>174</v>
+      </c>
+      <c r="U48" t="s">
+        <v>175</v>
+      </c>
+      <c r="W48" t="s">
+        <v>438</v>
+      </c>
+      <c r="X48" t="s">
+        <v>489</v>
+      </c>
+      <c r="Y48">
+        <v>10.709250000000001</v>
+      </c>
+      <c r="Z48">
+        <v>0.50948065857827751</v>
+      </c>
+    </row>
+    <row r="49" spans="15:26">
+      <c r="O49" t="s">
+        <v>171</v>
+      </c>
+      <c r="P49" t="s">
+        <v>440</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>441</v>
+      </c>
+      <c r="R49" t="s">
+        <v>10</v>
+      </c>
+      <c r="S49" t="s">
+        <v>21</v>
+      </c>
+      <c r="T49" t="s">
+        <v>174</v>
+      </c>
+      <c r="U49" t="s">
+        <v>175</v>
+      </c>
+      <c r="W49" t="s">
+        <v>440</v>
+      </c>
+      <c r="X49" t="s">
+        <v>490</v>
+      </c>
+      <c r="Y49">
+        <v>16.497</v>
+      </c>
+      <c r="Z49">
+        <v>0.45133214213550138</v>
+      </c>
+    </row>
+    <row r="50" spans="15:26">
+      <c r="O50" t="s">
+        <v>171</v>
+      </c>
+      <c r="P50" t="s">
+        <v>442</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>443</v>
+      </c>
+      <c r="R50" t="s">
+        <v>10</v>
+      </c>
+      <c r="S50" t="s">
+        <v>21</v>
+      </c>
+      <c r="T50" t="s">
+        <v>174</v>
+      </c>
+      <c r="U50" t="s">
+        <v>175</v>
+      </c>
+      <c r="W50" t="s">
+        <v>442</v>
+      </c>
+      <c r="X50" t="s">
+        <v>491</v>
+      </c>
+      <c r="Y50">
+        <v>53.960999999999999</v>
+      </c>
+      <c r="Z50">
+        <v>0.52956978618689865</v>
+      </c>
+    </row>
+    <row r="51" spans="15:26">
+      <c r="O51" t="s">
+        <v>171</v>
+      </c>
+      <c r="P51" t="s">
+        <v>444</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>445</v>
+      </c>
+      <c r="R51" t="s">
+        <v>10</v>
+      </c>
+      <c r="S51" t="s">
+        <v>21</v>
+      </c>
+      <c r="T51" t="s">
+        <v>174</v>
+      </c>
+      <c r="U51" t="s">
+        <v>175</v>
+      </c>
+      <c r="W51" t="s">
+        <v>444</v>
+      </c>
+      <c r="X51" t="s">
+        <v>492</v>
+      </c>
+      <c r="Y51">
+        <v>33.036000000000001</v>
+      </c>
+      <c r="Z51">
+        <v>0.43414290231109598</v>
+      </c>
+    </row>
+    <row r="52" spans="15:26">
+      <c r="O52" t="s">
+        <v>171</v>
+      </c>
+      <c r="P52" t="s">
+        <v>446</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>447</v>
+      </c>
+      <c r="R52" t="s">
+        <v>10</v>
+      </c>
+      <c r="S52" t="s">
+        <v>21</v>
+      </c>
+      <c r="T52" t="s">
+        <v>174</v>
+      </c>
+      <c r="U52" t="s">
+        <v>175</v>
+      </c>
+      <c r="W52" t="s">
+        <v>446</v>
+      </c>
+      <c r="X52" t="s">
+        <v>493</v>
+      </c>
+      <c r="Y52">
+        <v>31.234500000000001</v>
+      </c>
+      <c r="Z52">
+        <v>0.35182361384055583</v>
+      </c>
+    </row>
+    <row r="53" spans="15:26">
+      <c r="O53" t="s">
+        <v>171</v>
+      </c>
+      <c r="P53" t="s">
+        <v>448</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>449</v>
+      </c>
+      <c r="R53" t="s">
+        <v>10</v>
+      </c>
+      <c r="S53" t="s">
+        <v>21</v>
+      </c>
+      <c r="T53" t="s">
+        <v>174</v>
+      </c>
+      <c r="U53" t="s">
+        <v>175</v>
+      </c>
+      <c r="W53" t="s">
+        <v>448</v>
+      </c>
+      <c r="X53" t="s">
+        <v>494</v>
+      </c>
+      <c r="Y53">
+        <v>30.527249999999999</v>
+      </c>
+      <c r="Z53">
+        <v>0.3536163889541305</v>
+      </c>
+    </row>
+    <row r="54" spans="15:26">
+      <c r="O54" t="s">
+        <v>171</v>
+      </c>
+      <c r="P54" t="s">
+        <v>450</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>451</v>
+      </c>
+      <c r="R54" t="s">
+        <v>10</v>
+      </c>
+      <c r="S54" t="s">
+        <v>21</v>
+      </c>
+      <c r="T54" t="s">
+        <v>174</v>
+      </c>
+      <c r="U54" t="s">
+        <v>175</v>
+      </c>
+      <c r="W54" t="s">
+        <v>450</v>
+      </c>
+      <c r="X54" t="s">
+        <v>495</v>
+      </c>
+      <c r="Y54">
+        <v>17.390999999999998</v>
+      </c>
+      <c r="Z54">
+        <v>0.37382047274922298</v>
       </c>
     </row>
   </sheetData>
@@ -7720,2668 +10192,13 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A34B9DE4-071E-437A-9A64-C6A93E52066C}">
-  <dimension ref="B9:Z54"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <sheetData>
-    <row r="9" spans="2:26">
-      <c r="B9" t="s">
-        <v>163</v>
-      </c>
-      <c r="J9" t="s">
-        <v>174</v>
-      </c>
-      <c r="O9" t="s">
-        <v>163</v>
-      </c>
-      <c r="W9" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="10" spans="2:26">
-      <c r="B10" t="s">
-        <v>178</v>
-      </c>
-      <c r="C10" t="s">
-        <v>164</v>
-      </c>
-      <c r="D10" t="s">
-        <v>165</v>
-      </c>
-      <c r="E10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F10" t="s">
-        <v>180</v>
-      </c>
-      <c r="G10" t="s">
-        <v>166</v>
-      </c>
-      <c r="H10" t="s">
-        <v>181</v>
-      </c>
-      <c r="J10" t="s">
-        <v>164</v>
-      </c>
-      <c r="K10" t="s">
-        <v>247</v>
-      </c>
-      <c r="L10" t="s">
-        <v>248</v>
-      </c>
-      <c r="M10" t="s">
-        <v>249</v>
-      </c>
-      <c r="O10" t="s">
-        <v>178</v>
-      </c>
-      <c r="P10" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>165</v>
-      </c>
-      <c r="R10" t="s">
-        <v>179</v>
-      </c>
-      <c r="S10" t="s">
-        <v>180</v>
-      </c>
-      <c r="T10" t="s">
-        <v>166</v>
-      </c>
-      <c r="U10" t="s">
-        <v>181</v>
-      </c>
-      <c r="W10" t="s">
-        <v>164</v>
-      </c>
-      <c r="X10" t="s">
-        <v>247</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>248</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="11" spans="2:26">
-      <c r="B11" t="s">
-        <v>182</v>
-      </c>
-      <c r="C11" t="s">
-        <v>281</v>
-      </c>
-      <c r="D11" t="s">
-        <v>282</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" t="s">
-        <v>185</v>
-      </c>
-      <c r="H11" t="s">
-        <v>186</v>
-      </c>
-      <c r="J11" t="s">
-        <v>281</v>
-      </c>
-      <c r="K11" t="s">
-        <v>343</v>
-      </c>
-      <c r="L11">
-        <v>26.081770464705624</v>
-      </c>
-      <c r="M11">
-        <v>0.33938741610056822</v>
-      </c>
-      <c r="O11" t="s">
-        <v>182</v>
-      </c>
-      <c r="P11" t="s">
-        <v>374</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>375</v>
-      </c>
-      <c r="R11" t="s">
-        <v>10</v>
-      </c>
-      <c r="S11" t="s">
-        <v>21</v>
-      </c>
-      <c r="T11" t="s">
-        <v>185</v>
-      </c>
-      <c r="U11" t="s">
-        <v>186</v>
-      </c>
-      <c r="W11" t="s">
-        <v>374</v>
-      </c>
-      <c r="X11" t="s">
-        <v>462</v>
-      </c>
-      <c r="Y11">
-        <v>32.783999999999999</v>
-      </c>
-      <c r="Z11">
-        <v>0.44411288754139</v>
-      </c>
-    </row>
-    <row r="12" spans="2:26">
-      <c r="B12" t="s">
-        <v>182</v>
-      </c>
-      <c r="C12" t="s">
-        <v>283</v>
-      </c>
-      <c r="D12" t="s">
-        <v>284</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" t="s">
-        <v>185</v>
-      </c>
-      <c r="H12" t="s">
-        <v>186</v>
-      </c>
-      <c r="J12" t="s">
-        <v>283</v>
-      </c>
-      <c r="K12" t="s">
-        <v>344</v>
-      </c>
-      <c r="L12">
-        <v>28.326303899090867</v>
-      </c>
-      <c r="M12">
-        <v>0.31672699232591051</v>
-      </c>
-      <c r="O12" t="s">
-        <v>182</v>
-      </c>
-      <c r="P12" t="s">
-        <v>376</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>377</v>
-      </c>
-      <c r="R12" t="s">
-        <v>10</v>
-      </c>
-      <c r="S12" t="s">
-        <v>21</v>
-      </c>
-      <c r="T12" t="s">
-        <v>185</v>
-      </c>
-      <c r="U12" t="s">
-        <v>186</v>
-      </c>
-      <c r="W12" t="s">
-        <v>376</v>
-      </c>
-      <c r="X12" t="s">
-        <v>463</v>
-      </c>
-      <c r="Y12">
-        <v>36.320999999999998</v>
-      </c>
-      <c r="Z12">
-        <v>0.4267889026322102</v>
-      </c>
-    </row>
-    <row r="13" spans="2:26">
-      <c r="B13" t="s">
-        <v>182</v>
-      </c>
-      <c r="C13" t="s">
-        <v>285</v>
-      </c>
-      <c r="D13" t="s">
-        <v>286</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" t="s">
-        <v>185</v>
-      </c>
-      <c r="H13" t="s">
-        <v>186</v>
-      </c>
-      <c r="J13" t="s">
-        <v>285</v>
-      </c>
-      <c r="K13" t="s">
-        <v>345</v>
-      </c>
-      <c r="L13">
-        <v>36.748148815624823</v>
-      </c>
-      <c r="M13">
-        <v>0.24124293159761159</v>
-      </c>
-      <c r="O13" t="s">
-        <v>182</v>
-      </c>
-      <c r="P13" t="s">
-        <v>378</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>379</v>
-      </c>
-      <c r="R13" t="s">
-        <v>10</v>
-      </c>
-      <c r="S13" t="s">
-        <v>21</v>
-      </c>
-      <c r="T13" t="s">
-        <v>185</v>
-      </c>
-      <c r="U13" t="s">
-        <v>186</v>
-      </c>
-      <c r="W13" t="s">
-        <v>378</v>
-      </c>
-      <c r="X13" t="s">
-        <v>464</v>
-      </c>
-      <c r="Y13">
-        <v>43.956000000000003</v>
-      </c>
-      <c r="Z13">
-        <v>0.45005997451255592</v>
-      </c>
-    </row>
-    <row r="14" spans="2:26">
-      <c r="B14" t="s">
-        <v>182</v>
-      </c>
-      <c r="C14" t="s">
-        <v>287</v>
-      </c>
-      <c r="D14" t="s">
-        <v>288</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" t="s">
-        <v>185</v>
-      </c>
-      <c r="H14" t="s">
-        <v>186</v>
-      </c>
-      <c r="J14" t="s">
-        <v>287</v>
-      </c>
-      <c r="K14" t="s">
-        <v>346</v>
-      </c>
-      <c r="L14">
-        <v>33.851015501811965</v>
-      </c>
-      <c r="M14">
-        <v>0.17836569756942919</v>
-      </c>
-      <c r="O14" t="s">
-        <v>182</v>
-      </c>
-      <c r="P14" t="s">
-        <v>380</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>381</v>
-      </c>
-      <c r="R14" t="s">
-        <v>10</v>
-      </c>
-      <c r="S14" t="s">
-        <v>21</v>
-      </c>
-      <c r="T14" t="s">
-        <v>185</v>
-      </c>
-      <c r="U14" t="s">
-        <v>186</v>
-      </c>
-      <c r="W14" t="s">
-        <v>380</v>
-      </c>
-      <c r="X14" t="s">
-        <v>465</v>
-      </c>
-      <c r="Y14">
-        <v>62.099249999999998</v>
-      </c>
-      <c r="Z14">
-        <v>0.420776044292479</v>
-      </c>
-    </row>
-    <row r="15" spans="2:26">
-      <c r="B15" t="s">
-        <v>182</v>
-      </c>
-      <c r="C15" t="s">
-        <v>289</v>
-      </c>
-      <c r="D15" t="s">
-        <v>290</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" t="s">
-        <v>185</v>
-      </c>
-      <c r="H15" t="s">
-        <v>186</v>
-      </c>
-      <c r="J15" t="s">
-        <v>289</v>
-      </c>
-      <c r="K15" t="s">
-        <v>347</v>
-      </c>
-      <c r="L15">
-        <v>29.76120824924126</v>
-      </c>
-      <c r="M15">
-        <v>0.1835874284667649</v>
-      </c>
-      <c r="O15" t="s">
-        <v>182</v>
-      </c>
-      <c r="P15" t="s">
-        <v>382</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>383</v>
-      </c>
-      <c r="R15" t="s">
-        <v>10</v>
-      </c>
-      <c r="S15" t="s">
-        <v>21</v>
-      </c>
-      <c r="T15" t="s">
-        <v>185</v>
-      </c>
-      <c r="U15" t="s">
-        <v>186</v>
-      </c>
-      <c r="W15" t="s">
-        <v>382</v>
-      </c>
-      <c r="X15" t="s">
-        <v>466</v>
-      </c>
-      <c r="Y15">
-        <v>0.38324999999999998</v>
-      </c>
-      <c r="Z15">
-        <v>0.3586460374519268</v>
-      </c>
-    </row>
-    <row r="16" spans="2:26">
-      <c r="B16" t="s">
-        <v>182</v>
-      </c>
-      <c r="C16" t="s">
-        <v>291</v>
-      </c>
-      <c r="D16" t="s">
-        <v>292</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>21</v>
-      </c>
-      <c r="G16" t="s">
-        <v>185</v>
-      </c>
-      <c r="H16" t="s">
-        <v>186</v>
-      </c>
-      <c r="J16" t="s">
-        <v>291</v>
-      </c>
-      <c r="K16" t="s">
-        <v>348</v>
-      </c>
-      <c r="L16">
-        <v>13.047413180463023</v>
-      </c>
-      <c r="M16">
-        <v>0.11846842726897321</v>
-      </c>
-      <c r="O16" t="s">
-        <v>182</v>
-      </c>
-      <c r="P16" t="s">
-        <v>384</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>385</v>
-      </c>
-      <c r="R16" t="s">
-        <v>10</v>
-      </c>
-      <c r="S16" t="s">
-        <v>21</v>
-      </c>
-      <c r="T16" t="s">
-        <v>185</v>
-      </c>
-      <c r="U16" t="s">
-        <v>186</v>
-      </c>
-      <c r="W16" t="s">
-        <v>384</v>
-      </c>
-      <c r="X16" t="s">
-        <v>467</v>
-      </c>
-      <c r="Y16">
-        <v>56.725499999999997</v>
-      </c>
-      <c r="Z16">
-        <v>0.4678326459120476</v>
-      </c>
-    </row>
-    <row r="17" spans="2:26">
-      <c r="B17" t="s">
-        <v>182</v>
-      </c>
-      <c r="C17" t="s">
-        <v>293</v>
-      </c>
-      <c r="D17" t="s">
-        <v>294</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>21</v>
-      </c>
-      <c r="G17" t="s">
-        <v>185</v>
-      </c>
-      <c r="H17" t="s">
-        <v>186</v>
-      </c>
-      <c r="J17" t="s">
-        <v>293</v>
-      </c>
-      <c r="K17" t="s">
-        <v>349</v>
-      </c>
-      <c r="L17">
-        <v>23.637816650626842</v>
-      </c>
-      <c r="M17">
-        <v>0.1537391571572389</v>
-      </c>
-      <c r="O17" t="s">
-        <v>182</v>
-      </c>
-      <c r="P17" t="s">
-        <v>386</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>387</v>
-      </c>
-      <c r="R17" t="s">
-        <v>10</v>
-      </c>
-      <c r="S17" t="s">
-        <v>21</v>
-      </c>
-      <c r="T17" t="s">
-        <v>185</v>
-      </c>
-      <c r="U17" t="s">
-        <v>186</v>
-      </c>
-      <c r="W17" t="s">
-        <v>386</v>
-      </c>
-      <c r="X17" t="s">
-        <v>468</v>
-      </c>
-      <c r="Y17">
-        <v>58.03275</v>
-      </c>
-      <c r="Z17">
-        <v>0.41285964472242181</v>
-      </c>
-    </row>
-    <row r="18" spans="2:26">
-      <c r="B18" t="s">
-        <v>182</v>
-      </c>
-      <c r="C18" t="s">
-        <v>295</v>
-      </c>
-      <c r="D18" t="s">
-        <v>296</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>21</v>
-      </c>
-      <c r="G18" t="s">
-        <v>185</v>
-      </c>
-      <c r="H18" t="s">
-        <v>186</v>
-      </c>
-      <c r="J18" t="s">
-        <v>295</v>
-      </c>
-      <c r="K18" t="s">
-        <v>350</v>
-      </c>
-      <c r="L18">
-        <v>50.076680799526407</v>
-      </c>
-      <c r="M18">
-        <v>0.19002505627190239</v>
-      </c>
-      <c r="O18" t="s">
-        <v>182</v>
-      </c>
-      <c r="P18" t="s">
-        <v>388</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>389</v>
-      </c>
-      <c r="R18" t="s">
-        <v>10</v>
-      </c>
-      <c r="S18" t="s">
-        <v>21</v>
-      </c>
-      <c r="T18" t="s">
-        <v>185</v>
-      </c>
-      <c r="U18" t="s">
-        <v>186</v>
-      </c>
-      <c r="W18" t="s">
-        <v>388</v>
-      </c>
-      <c r="X18" t="s">
-        <v>469</v>
-      </c>
-      <c r="Y18">
-        <v>28.478249999999999</v>
-      </c>
-      <c r="Z18">
-        <v>0.31013048721759129</v>
-      </c>
-    </row>
-    <row r="19" spans="2:26">
-      <c r="B19" t="s">
-        <v>182</v>
-      </c>
-      <c r="C19" t="s">
-        <v>297</v>
-      </c>
-      <c r="D19" t="s">
-        <v>298</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>21</v>
-      </c>
-      <c r="G19" t="s">
-        <v>185</v>
-      </c>
-      <c r="H19" t="s">
-        <v>186</v>
-      </c>
-      <c r="J19" t="s">
-        <v>297</v>
-      </c>
-      <c r="K19" t="s">
-        <v>351</v>
-      </c>
-      <c r="L19">
-        <v>22.504679657777121</v>
-      </c>
-      <c r="M19">
-        <v>0.43998684438339841</v>
-      </c>
-      <c r="O19" t="s">
-        <v>182</v>
-      </c>
-      <c r="P19" t="s">
-        <v>390</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>391</v>
-      </c>
-      <c r="R19" t="s">
-        <v>10</v>
-      </c>
-      <c r="S19" t="s">
-        <v>21</v>
-      </c>
-      <c r="T19" t="s">
-        <v>185</v>
-      </c>
-      <c r="U19" t="s">
-        <v>186</v>
-      </c>
-      <c r="W19" t="s">
-        <v>390</v>
-      </c>
-      <c r="X19" t="s">
-        <v>470</v>
-      </c>
-      <c r="Y19">
-        <v>22.079249999999998</v>
-      </c>
-      <c r="Z19">
-        <v>0.3223061905611202</v>
-      </c>
-    </row>
-    <row r="20" spans="2:26">
-      <c r="B20" t="s">
-        <v>182</v>
-      </c>
-      <c r="C20" t="s">
-        <v>299</v>
-      </c>
-      <c r="D20" t="s">
-        <v>300</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>21</v>
-      </c>
-      <c r="G20" t="s">
-        <v>185</v>
-      </c>
-      <c r="H20" t="s">
-        <v>186</v>
-      </c>
-      <c r="J20" t="s">
-        <v>299</v>
-      </c>
-      <c r="K20" t="s">
-        <v>352</v>
-      </c>
-      <c r="L20">
-        <v>39.022668784713879</v>
-      </c>
-      <c r="M20">
-        <v>0.30226720130549178</v>
-      </c>
-      <c r="O20" t="s">
-        <v>182</v>
-      </c>
-      <c r="P20" t="s">
-        <v>392</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>393</v>
-      </c>
-      <c r="R20" t="s">
-        <v>10</v>
-      </c>
-      <c r="S20" t="s">
-        <v>21</v>
-      </c>
-      <c r="T20" t="s">
-        <v>185</v>
-      </c>
-      <c r="U20" t="s">
-        <v>186</v>
-      </c>
-      <c r="W20" t="s">
-        <v>392</v>
-      </c>
-      <c r="X20" t="s">
-        <v>471</v>
-      </c>
-      <c r="Y20">
-        <v>29.961749999999999</v>
-      </c>
-      <c r="Z20">
-        <v>0.33421489525964382</v>
-      </c>
-    </row>
-    <row r="21" spans="2:26">
-      <c r="B21" t="s">
-        <v>182</v>
-      </c>
-      <c r="C21" t="s">
-        <v>301</v>
-      </c>
-      <c r="D21" t="s">
-        <v>302</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>21</v>
-      </c>
-      <c r="G21" t="s">
-        <v>185</v>
-      </c>
-      <c r="H21" t="s">
-        <v>186</v>
-      </c>
-      <c r="J21" t="s">
-        <v>301</v>
-      </c>
-      <c r="K21" t="s">
-        <v>353</v>
-      </c>
-      <c r="L21">
-        <v>12.527007796473459</v>
-      </c>
-      <c r="M21">
-        <v>0.26335249621019208</v>
-      </c>
-      <c r="O21" t="s">
-        <v>182</v>
-      </c>
-      <c r="P21" t="s">
-        <v>394</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>395</v>
-      </c>
-      <c r="R21" t="s">
-        <v>10</v>
-      </c>
-      <c r="S21" t="s">
-        <v>21</v>
-      </c>
-      <c r="T21" t="s">
-        <v>185</v>
-      </c>
-      <c r="U21" t="s">
-        <v>186</v>
-      </c>
-      <c r="W21" t="s">
-        <v>394</v>
-      </c>
-      <c r="X21" t="s">
-        <v>472</v>
-      </c>
-      <c r="Y21">
-        <v>117.89700000000001</v>
-      </c>
-      <c r="Z21">
-        <v>0.4454005763280634</v>
-      </c>
-    </row>
-    <row r="22" spans="2:26">
-      <c r="B22" t="s">
-        <v>182</v>
-      </c>
-      <c r="C22" t="s">
-        <v>303</v>
-      </c>
-      <c r="D22" t="s">
-        <v>304</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>21</v>
-      </c>
-      <c r="G22" t="s">
-        <v>185</v>
-      </c>
-      <c r="H22" t="s">
-        <v>186</v>
-      </c>
-      <c r="J22" t="s">
-        <v>303</v>
-      </c>
-      <c r="K22" t="s">
-        <v>354</v>
-      </c>
-      <c r="L22">
-        <v>22.322239264526591</v>
-      </c>
-      <c r="M22">
-        <v>0.24546553943130331</v>
-      </c>
-      <c r="O22" t="s">
-        <v>182</v>
-      </c>
-      <c r="P22" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>397</v>
-      </c>
-      <c r="R22" t="s">
-        <v>10</v>
-      </c>
-      <c r="S22" t="s">
-        <v>21</v>
-      </c>
-      <c r="T22" t="s">
-        <v>185</v>
-      </c>
-      <c r="U22" t="s">
-        <v>186</v>
-      </c>
-      <c r="W22" t="s">
-        <v>396</v>
-      </c>
-      <c r="X22" t="s">
-        <v>473</v>
-      </c>
-      <c r="Y22">
-        <v>75.481499999999997</v>
-      </c>
-      <c r="Z22">
-        <v>0.39947482218024288</v>
-      </c>
-    </row>
-    <row r="23" spans="2:26">
-      <c r="B23" t="s">
-        <v>182</v>
-      </c>
-      <c r="C23" t="s">
-        <v>305</v>
-      </c>
-      <c r="D23" t="s">
-        <v>306</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G23" t="s">
-        <v>185</v>
-      </c>
-      <c r="H23" t="s">
-        <v>186</v>
-      </c>
-      <c r="J23" t="s">
-        <v>305</v>
-      </c>
-      <c r="K23" t="s">
-        <v>355</v>
-      </c>
-      <c r="L23">
-        <v>6.1151684514715345</v>
-      </c>
-      <c r="M23">
-        <v>0.44244733217755411</v>
-      </c>
-      <c r="O23" t="s">
-        <v>182</v>
-      </c>
-      <c r="P23" t="s">
-        <v>398</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>399</v>
-      </c>
-      <c r="R23" t="s">
-        <v>10</v>
-      </c>
-      <c r="S23" t="s">
-        <v>21</v>
-      </c>
-      <c r="T23" t="s">
-        <v>185</v>
-      </c>
-      <c r="U23" t="s">
-        <v>186</v>
-      </c>
-      <c r="W23" t="s">
-        <v>398</v>
-      </c>
-      <c r="X23" t="s">
-        <v>474</v>
-      </c>
-      <c r="Y23">
-        <v>10.68975</v>
-      </c>
-      <c r="Z23">
-        <v>0.2858957309818449</v>
-      </c>
-    </row>
-    <row r="24" spans="2:26">
-      <c r="B24" t="s">
-        <v>182</v>
-      </c>
-      <c r="C24" t="s">
-        <v>307</v>
-      </c>
-      <c r="D24" t="s">
-        <v>308</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>21</v>
-      </c>
-      <c r="G24" t="s">
-        <v>185</v>
-      </c>
-      <c r="H24" t="s">
-        <v>186</v>
-      </c>
-      <c r="J24" t="s">
-        <v>307</v>
-      </c>
-      <c r="K24" t="s">
-        <v>356</v>
-      </c>
-      <c r="L24">
-        <v>4.1221966299799098</v>
-      </c>
-      <c r="M24">
-        <v>0.47272019788829328</v>
-      </c>
-      <c r="O24" t="s">
-        <v>182</v>
-      </c>
-      <c r="P24" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>401</v>
-      </c>
-      <c r="R24" t="s">
-        <v>10</v>
-      </c>
-      <c r="S24" t="s">
-        <v>21</v>
-      </c>
-      <c r="T24" t="s">
-        <v>185</v>
-      </c>
-      <c r="U24" t="s">
-        <v>186</v>
-      </c>
-      <c r="W24" t="s">
-        <v>400</v>
-      </c>
-      <c r="X24" t="s">
-        <v>475</v>
-      </c>
-      <c r="Y24">
-        <v>82.607249999999993</v>
-      </c>
-      <c r="Z24">
-        <v>0.4138948789420363</v>
-      </c>
-    </row>
-    <row r="25" spans="2:26">
-      <c r="B25" t="s">
-        <v>182</v>
-      </c>
-      <c r="C25" t="s">
-        <v>309</v>
-      </c>
-      <c r="D25" t="s">
-        <v>310</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>21</v>
-      </c>
-      <c r="G25" t="s">
-        <v>185</v>
-      </c>
-      <c r="H25" t="s">
-        <v>186</v>
-      </c>
-      <c r="J25" t="s">
-        <v>309</v>
-      </c>
-      <c r="K25" t="s">
-        <v>357</v>
-      </c>
-      <c r="L25">
-        <v>6.7028485191473308E-2</v>
-      </c>
-      <c r="M25">
-        <v>0.41432793234675691</v>
-      </c>
-      <c r="O25" t="s">
-        <v>182</v>
-      </c>
-      <c r="P25" t="s">
-        <v>402</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>403</v>
-      </c>
-      <c r="R25" t="s">
-        <v>10</v>
-      </c>
-      <c r="S25" t="s">
-        <v>21</v>
-      </c>
-      <c r="T25" t="s">
-        <v>185</v>
-      </c>
-      <c r="U25" t="s">
-        <v>186</v>
-      </c>
-      <c r="W25" t="s">
-        <v>402</v>
-      </c>
-      <c r="X25" t="s">
-        <v>476</v>
-      </c>
-      <c r="Y25">
-        <v>28.239750000000001</v>
-      </c>
-      <c r="Z25">
-        <v>0.39283819950969068</v>
-      </c>
-    </row>
-    <row r="26" spans="2:26">
-      <c r="B26" t="s">
-        <v>182</v>
-      </c>
-      <c r="C26" t="s">
-        <v>311</v>
-      </c>
-      <c r="D26" t="s">
-        <v>312</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G26" t="s">
-        <v>185</v>
-      </c>
-      <c r="H26" t="s">
-        <v>186</v>
-      </c>
-      <c r="J26" t="s">
-        <v>311</v>
-      </c>
-      <c r="K26" t="s">
-        <v>358</v>
-      </c>
-      <c r="L26">
-        <v>1.3102559495532347</v>
-      </c>
-      <c r="M26">
-        <v>0.51823166137173471</v>
-      </c>
-      <c r="O26" t="s">
-        <v>182</v>
-      </c>
-      <c r="P26" t="s">
-        <v>404</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>405</v>
-      </c>
-      <c r="R26" t="s">
-        <v>10</v>
-      </c>
-      <c r="S26" t="s">
-        <v>21</v>
-      </c>
-      <c r="T26" t="s">
-        <v>185</v>
-      </c>
-      <c r="U26" t="s">
-        <v>186</v>
-      </c>
-      <c r="W26" t="s">
-        <v>404</v>
-      </c>
-      <c r="X26" t="s">
-        <v>477</v>
-      </c>
-      <c r="Y26">
-        <v>1.9132499999999999</v>
-      </c>
-      <c r="Z26">
-        <v>0.24373705543466159</v>
-      </c>
-    </row>
-    <row r="27" spans="2:26">
-      <c r="B27" t="s">
-        <v>182</v>
-      </c>
-      <c r="C27" t="s">
-        <v>313</v>
-      </c>
-      <c r="D27" t="s">
-        <v>314</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>21</v>
-      </c>
-      <c r="G27" t="s">
-        <v>185</v>
-      </c>
-      <c r="H27" t="s">
-        <v>186</v>
-      </c>
-      <c r="J27" t="s">
-        <v>313</v>
-      </c>
-      <c r="K27" t="s">
-        <v>359</v>
-      </c>
-      <c r="L27">
-        <v>51.171736048895305</v>
-      </c>
-      <c r="M27">
-        <v>0.1753269736233318</v>
-      </c>
-      <c r="O27" t="s">
-        <v>182</v>
-      </c>
-      <c r="P27" t="s">
-        <v>406</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>407</v>
-      </c>
-      <c r="R27" t="s">
-        <v>10</v>
-      </c>
-      <c r="S27" t="s">
-        <v>21</v>
-      </c>
-      <c r="T27" t="s">
-        <v>185</v>
-      </c>
-      <c r="U27" t="s">
-        <v>186</v>
-      </c>
-      <c r="W27" t="s">
-        <v>406</v>
-      </c>
-      <c r="X27" t="s">
-        <v>478</v>
-      </c>
-      <c r="Y27">
-        <v>63.731250000000003</v>
-      </c>
-      <c r="Z27">
-        <v>0.4483325413452795</v>
-      </c>
-    </row>
-    <row r="28" spans="2:26">
-      <c r="B28" t="s">
-        <v>182</v>
-      </c>
-      <c r="C28" t="s">
-        <v>315</v>
-      </c>
-      <c r="D28" t="s">
-        <v>316</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>21</v>
-      </c>
-      <c r="G28" t="s">
-        <v>185</v>
-      </c>
-      <c r="H28" t="s">
-        <v>186</v>
-      </c>
-      <c r="J28" t="s">
-        <v>315</v>
-      </c>
-      <c r="K28" t="s">
-        <v>360</v>
-      </c>
-      <c r="L28">
-        <v>27.131882337818411</v>
-      </c>
-      <c r="M28">
-        <v>0.13421919246645389</v>
-      </c>
-      <c r="O28" t="s">
-        <v>182</v>
-      </c>
-      <c r="P28" t="s">
-        <v>408</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>409</v>
-      </c>
-      <c r="R28" t="s">
-        <v>10</v>
-      </c>
-      <c r="S28" t="s">
-        <v>21</v>
-      </c>
-      <c r="T28" t="s">
-        <v>185</v>
-      </c>
-      <c r="U28" t="s">
-        <v>186</v>
-      </c>
-      <c r="W28" t="s">
-        <v>408</v>
-      </c>
-      <c r="X28" t="s">
-        <v>479</v>
-      </c>
-      <c r="Y28">
-        <v>38.451000000000001</v>
-      </c>
-      <c r="Z28">
-        <v>0.41699608360155571</v>
-      </c>
-    </row>
-    <row r="29" spans="2:26">
-      <c r="B29" t="s">
-        <v>182</v>
-      </c>
-      <c r="C29" t="s">
-        <v>317</v>
-      </c>
-      <c r="D29" t="s">
-        <v>318</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>21</v>
-      </c>
-      <c r="G29" t="s">
-        <v>185</v>
-      </c>
-      <c r="H29" t="s">
-        <v>186</v>
-      </c>
-      <c r="J29" t="s">
-        <v>317</v>
-      </c>
-      <c r="K29" t="s">
-        <v>361</v>
-      </c>
-      <c r="L29">
-        <v>8.7915989873091043</v>
-      </c>
-      <c r="M29">
-        <v>0.33157900311052629</v>
-      </c>
-      <c r="O29" t="s">
-        <v>182</v>
-      </c>
-      <c r="P29" t="s">
-        <v>410</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>411</v>
-      </c>
-      <c r="R29" t="s">
-        <v>10</v>
-      </c>
-      <c r="S29" t="s">
-        <v>21</v>
-      </c>
-      <c r="T29" t="s">
-        <v>185</v>
-      </c>
-      <c r="U29" t="s">
-        <v>186</v>
-      </c>
-      <c r="W29" t="s">
-        <v>410</v>
-      </c>
-      <c r="X29" t="s">
-        <v>480</v>
-      </c>
-      <c r="Y29">
-        <v>64.533749999999998</v>
-      </c>
-      <c r="Z29">
-        <v>0.49947203939427631</v>
-      </c>
-    </row>
-    <row r="30" spans="2:26">
-      <c r="B30" t="s">
-        <v>182</v>
-      </c>
-      <c r="C30" t="s">
-        <v>319</v>
-      </c>
-      <c r="D30" t="s">
-        <v>320</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>21</v>
-      </c>
-      <c r="G30" t="s">
-        <v>185</v>
-      </c>
-      <c r="H30" t="s">
-        <v>186</v>
-      </c>
-      <c r="J30" t="s">
-        <v>319</v>
-      </c>
-      <c r="K30" t="s">
-        <v>362</v>
-      </c>
-      <c r="L30">
-        <v>26.915511431987859</v>
-      </c>
-      <c r="M30">
-        <v>0.17204244166879709</v>
-      </c>
-      <c r="O30" t="s">
-        <v>182</v>
-      </c>
-      <c r="P30" t="s">
-        <v>412</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>413</v>
-      </c>
-      <c r="R30" t="s">
-        <v>10</v>
-      </c>
-      <c r="S30" t="s">
-        <v>21</v>
-      </c>
-      <c r="T30" t="s">
-        <v>185</v>
-      </c>
-      <c r="U30" t="s">
-        <v>186</v>
-      </c>
-      <c r="W30" t="s">
-        <v>412</v>
-      </c>
-      <c r="X30" t="s">
-        <v>481</v>
-      </c>
-      <c r="Y30">
-        <v>44.370750000000001</v>
-      </c>
-      <c r="Z30">
-        <v>0.45077590772414738</v>
-      </c>
-    </row>
-    <row r="31" spans="2:26">
-      <c r="B31" t="s">
-        <v>182</v>
-      </c>
-      <c r="C31" t="s">
-        <v>321</v>
-      </c>
-      <c r="D31" t="s">
-        <v>322</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>21</v>
-      </c>
-      <c r="G31" t="s">
-        <v>185</v>
-      </c>
-      <c r="H31" t="s">
-        <v>186</v>
-      </c>
-      <c r="J31" t="s">
-        <v>321</v>
-      </c>
-      <c r="K31" t="s">
-        <v>363</v>
-      </c>
-      <c r="L31">
-        <v>7.5025171344716721</v>
-      </c>
-      <c r="M31">
-        <v>0.102078386690078</v>
-      </c>
-      <c r="O31" t="s">
-        <v>182</v>
-      </c>
-      <c r="P31" t="s">
-        <v>414</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>415</v>
-      </c>
-      <c r="R31" t="s">
-        <v>10</v>
-      </c>
-      <c r="S31" t="s">
-        <v>21</v>
-      </c>
-      <c r="T31" t="s">
-        <v>185</v>
-      </c>
-      <c r="U31" t="s">
-        <v>186</v>
-      </c>
-      <c r="W31" t="s">
-        <v>414</v>
-      </c>
-      <c r="X31" t="s">
-        <v>482</v>
-      </c>
-      <c r="Y31">
-        <v>38.15925</v>
-      </c>
-      <c r="Z31">
-        <v>0.42518909184060127</v>
-      </c>
-    </row>
-    <row r="32" spans="2:26">
-      <c r="B32" t="s">
-        <v>182</v>
-      </c>
-      <c r="C32" t="s">
-        <v>323</v>
-      </c>
-      <c r="D32" t="s">
-        <v>324</v>
-      </c>
-      <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32" t="s">
-        <v>185</v>
-      </c>
-      <c r="H32" t="s">
-        <v>186</v>
-      </c>
-      <c r="J32" t="s">
-        <v>323</v>
-      </c>
-      <c r="K32" t="s">
-        <v>364</v>
-      </c>
-      <c r="L32">
-        <v>21.853336570084423</v>
-      </c>
-      <c r="M32">
-        <v>0.2470260197032213</v>
-      </c>
-      <c r="O32" t="s">
-        <v>182</v>
-      </c>
-      <c r="P32" t="s">
-        <v>416</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>417</v>
-      </c>
-      <c r="R32" t="s">
-        <v>10</v>
-      </c>
-      <c r="S32" t="s">
-        <v>21</v>
-      </c>
-      <c r="T32" t="s">
-        <v>185</v>
-      </c>
-      <c r="U32" t="s">
-        <v>186</v>
-      </c>
-      <c r="W32" t="s">
-        <v>416</v>
-      </c>
-      <c r="X32" t="s">
-        <v>483</v>
-      </c>
-      <c r="Y32">
-        <v>3.38625</v>
-      </c>
-      <c r="Z32">
-        <v>0.27397097122901398</v>
-      </c>
-    </row>
-    <row r="33" spans="2:26">
-      <c r="B33" t="s">
-        <v>182</v>
-      </c>
-      <c r="C33" t="s">
-        <v>325</v>
-      </c>
-      <c r="D33" t="s">
-        <v>326</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>21</v>
-      </c>
-      <c r="G33" t="s">
-        <v>185</v>
-      </c>
-      <c r="H33" t="s">
-        <v>186</v>
-      </c>
-      <c r="J33" t="s">
-        <v>325</v>
-      </c>
-      <c r="K33" t="s">
-        <v>365</v>
-      </c>
-      <c r="L33">
-        <v>40.036304639772588</v>
-      </c>
-      <c r="M33">
-        <v>0.22158847806059459</v>
-      </c>
-      <c r="O33" t="s">
-        <v>182</v>
-      </c>
-      <c r="P33" t="s">
-        <v>418</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>419</v>
-      </c>
-      <c r="R33" t="s">
-        <v>10</v>
-      </c>
-      <c r="S33" t="s">
-        <v>21</v>
-      </c>
-      <c r="T33" t="s">
-        <v>185</v>
-      </c>
-      <c r="U33" t="s">
-        <v>186</v>
-      </c>
-      <c r="W33" t="s">
-        <v>418</v>
-      </c>
-      <c r="X33" t="s">
-        <v>484</v>
-      </c>
-      <c r="Y33">
-        <v>30.597750000000001</v>
-      </c>
-      <c r="Z33">
-        <v>0.45321604354945533</v>
-      </c>
-    </row>
-    <row r="34" spans="2:26">
-      <c r="B34" t="s">
-        <v>182</v>
-      </c>
-      <c r="C34" t="s">
-        <v>327</v>
-      </c>
-      <c r="D34" t="s">
-        <v>328</v>
-      </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" t="s">
-        <v>21</v>
-      </c>
-      <c r="G34" t="s">
-        <v>185</v>
-      </c>
-      <c r="H34" t="s">
-        <v>186</v>
-      </c>
-      <c r="J34" t="s">
-        <v>327</v>
-      </c>
-      <c r="K34" t="s">
-        <v>366</v>
-      </c>
-      <c r="L34">
-        <v>7.0903888161806279</v>
-      </c>
-      <c r="M34">
-        <v>0.126349887785319</v>
-      </c>
-      <c r="O34" t="s">
-        <v>182</v>
-      </c>
-      <c r="P34" t="s">
-        <v>420</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>421</v>
-      </c>
-      <c r="R34" t="s">
-        <v>10</v>
-      </c>
-      <c r="S34" t="s">
-        <v>21</v>
-      </c>
-      <c r="T34" t="s">
-        <v>185</v>
-      </c>
-      <c r="U34" t="s">
-        <v>186</v>
-      </c>
-      <c r="W34" t="s">
-        <v>420</v>
-      </c>
-      <c r="X34" t="s">
-        <v>485</v>
-      </c>
-      <c r="Y34">
-        <v>33.609749999999998</v>
-      </c>
-      <c r="Z34">
-        <v>0.397480074831774</v>
-      </c>
-    </row>
-    <row r="35" spans="2:26">
-      <c r="B35" t="s">
-        <v>182</v>
-      </c>
-      <c r="C35" t="s">
-        <v>329</v>
-      </c>
-      <c r="D35" t="s">
-        <v>330</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>21</v>
-      </c>
-      <c r="G35" t="s">
-        <v>185</v>
-      </c>
-      <c r="H35" t="s">
-        <v>186</v>
-      </c>
-      <c r="J35" t="s">
-        <v>329</v>
-      </c>
-      <c r="K35" t="s">
-        <v>367</v>
-      </c>
-      <c r="L35">
-        <v>16.970662525397827</v>
-      </c>
-      <c r="M35">
-        <v>0.2876476609673595</v>
-      </c>
-      <c r="O35" t="s">
-        <v>182</v>
-      </c>
-      <c r="P35" t="s">
-        <v>422</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>423</v>
-      </c>
-      <c r="R35" t="s">
-        <v>10</v>
-      </c>
-      <c r="S35" t="s">
-        <v>21</v>
-      </c>
-      <c r="T35" t="s">
-        <v>185</v>
-      </c>
-      <c r="U35" t="s">
-        <v>186</v>
-      </c>
-      <c r="W35" t="s">
-        <v>422</v>
-      </c>
-      <c r="X35" t="s">
-        <v>486</v>
-      </c>
-      <c r="Y35">
-        <v>58.474499999999999</v>
-      </c>
-      <c r="Z35">
-        <v>0.3742804525886429</v>
-      </c>
-    </row>
-    <row r="36" spans="2:26">
-      <c r="B36" t="s">
-        <v>182</v>
-      </c>
-      <c r="C36" t="s">
-        <v>331</v>
-      </c>
-      <c r="D36" t="s">
-        <v>332</v>
-      </c>
-      <c r="E36" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" t="s">
-        <v>21</v>
-      </c>
-      <c r="G36" t="s">
-        <v>185</v>
-      </c>
-      <c r="H36" t="s">
-        <v>186</v>
-      </c>
-      <c r="J36" t="s">
-        <v>331</v>
-      </c>
-      <c r="K36" t="s">
-        <v>368</v>
-      </c>
-      <c r="L36">
-        <v>2.5242004930684354</v>
-      </c>
-      <c r="M36">
-        <v>9.3541201112904898E-2</v>
-      </c>
-      <c r="O36" t="s">
-        <v>182</v>
-      </c>
-      <c r="P36" t="s">
-        <v>424</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>425</v>
-      </c>
-      <c r="R36" t="s">
-        <v>10</v>
-      </c>
-      <c r="S36" t="s">
-        <v>21</v>
-      </c>
-      <c r="T36" t="s">
-        <v>185</v>
-      </c>
-      <c r="U36" t="s">
-        <v>186</v>
-      </c>
-      <c r="W36" t="s">
-        <v>424</v>
-      </c>
-      <c r="X36" t="s">
-        <v>487</v>
-      </c>
-      <c r="Y36">
-        <v>18.711749999999999</v>
-      </c>
-      <c r="Z36">
-        <v>0.2850753309410175</v>
-      </c>
-    </row>
-    <row r="37" spans="2:26">
-      <c r="B37" t="s">
-        <v>182</v>
-      </c>
-      <c r="C37" t="s">
-        <v>333</v>
-      </c>
-      <c r="D37" t="s">
-        <v>334</v>
-      </c>
-      <c r="E37" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" t="s">
-        <v>21</v>
-      </c>
-      <c r="G37" t="s">
-        <v>185</v>
-      </c>
-      <c r="H37" t="s">
-        <v>186</v>
-      </c>
-      <c r="J37" t="s">
-        <v>333</v>
-      </c>
-      <c r="K37" t="s">
-        <v>369</v>
-      </c>
-      <c r="L37">
-        <v>5.5071261071764246</v>
-      </c>
-      <c r="M37">
-        <v>0.34206800892605482</v>
-      </c>
-      <c r="O37" t="s">
-        <v>182</v>
-      </c>
-      <c r="P37" t="s">
-        <v>426</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>427</v>
-      </c>
-      <c r="R37" t="s">
-        <v>10</v>
-      </c>
-      <c r="S37" t="s">
-        <v>21</v>
-      </c>
-      <c r="T37" t="s">
-        <v>185</v>
-      </c>
-      <c r="U37" t="s">
-        <v>186</v>
-      </c>
-      <c r="W37" t="s">
-        <v>426</v>
-      </c>
-      <c r="X37" t="s">
-        <v>488</v>
-      </c>
-      <c r="Y37">
-        <v>29.186250000000001</v>
-      </c>
-      <c r="Z37">
-        <v>0.35239758613659811</v>
-      </c>
-    </row>
-    <row r="38" spans="2:26">
-      <c r="B38" t="s">
-        <v>182</v>
-      </c>
-      <c r="C38" t="s">
-        <v>335</v>
-      </c>
-      <c r="D38" t="s">
-        <v>336</v>
-      </c>
-      <c r="E38" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" t="s">
-        <v>21</v>
-      </c>
-      <c r="G38" t="s">
-        <v>185</v>
-      </c>
-      <c r="H38" t="s">
-        <v>186</v>
-      </c>
-      <c r="J38" t="s">
-        <v>335</v>
-      </c>
-      <c r="K38" t="s">
-        <v>370</v>
-      </c>
-      <c r="L38">
-        <v>8.4886449615793467</v>
-      </c>
-      <c r="M38">
-        <v>0.33231574315319728</v>
-      </c>
-      <c r="O38" t="s">
-        <v>182</v>
-      </c>
-      <c r="P38" t="s">
-        <v>428</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>429</v>
-      </c>
-      <c r="R38" t="s">
-        <v>10</v>
-      </c>
-      <c r="S38" t="s">
-        <v>21</v>
-      </c>
-      <c r="T38" t="s">
-        <v>185</v>
-      </c>
-      <c r="U38" t="s">
-        <v>186</v>
-      </c>
-      <c r="W38" t="s">
-        <v>428</v>
-      </c>
-      <c r="X38" t="s">
-        <v>489</v>
-      </c>
-      <c r="Y38">
-        <v>14.49</v>
-      </c>
-      <c r="Z38">
-        <v>0.4104874743436856</v>
-      </c>
-    </row>
-    <row r="39" spans="2:26">
-      <c r="B39" t="s">
-        <v>182</v>
-      </c>
-      <c r="C39" t="s">
-        <v>337</v>
-      </c>
-      <c r="D39" t="s">
-        <v>338</v>
-      </c>
-      <c r="E39" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" t="s">
-        <v>21</v>
-      </c>
-      <c r="G39" t="s">
-        <v>185</v>
-      </c>
-      <c r="H39" t="s">
-        <v>186</v>
-      </c>
-      <c r="J39" t="s">
-        <v>337</v>
-      </c>
-      <c r="K39" t="s">
-        <v>371</v>
-      </c>
-      <c r="L39">
-        <v>8.4075540995285696</v>
-      </c>
-      <c r="M39">
-        <v>0.28011366210530497</v>
-      </c>
-      <c r="O39" t="s">
-        <v>182</v>
-      </c>
-      <c r="P39" t="s">
-        <v>430</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>431</v>
-      </c>
-      <c r="R39" t="s">
-        <v>10</v>
-      </c>
-      <c r="S39" t="s">
-        <v>21</v>
-      </c>
-      <c r="T39" t="s">
-        <v>185</v>
-      </c>
-      <c r="U39" t="s">
-        <v>186</v>
-      </c>
-      <c r="W39" t="s">
-        <v>430</v>
-      </c>
-      <c r="X39" t="s">
-        <v>490</v>
-      </c>
-      <c r="Y39">
-        <v>64.437749999999994</v>
-      </c>
-      <c r="Z39">
-        <v>0.4224374651715968</v>
-      </c>
-    </row>
-    <row r="40" spans="2:26">
-      <c r="B40" t="s">
-        <v>182</v>
-      </c>
-      <c r="C40" t="s">
-        <v>339</v>
-      </c>
-      <c r="D40" t="s">
-        <v>340</v>
-      </c>
-      <c r="E40" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" t="s">
-        <v>21</v>
-      </c>
-      <c r="G40" t="s">
-        <v>185</v>
-      </c>
-      <c r="H40" t="s">
-        <v>186</v>
-      </c>
-      <c r="J40" t="s">
-        <v>339</v>
-      </c>
-      <c r="K40" t="s">
-        <v>372</v>
-      </c>
-      <c r="L40">
-        <v>15.703622047270191</v>
-      </c>
-      <c r="M40">
-        <v>0.2902999058993756</v>
-      </c>
-      <c r="O40" t="s">
-        <v>182</v>
-      </c>
-      <c r="P40" t="s">
-        <v>432</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>433</v>
-      </c>
-      <c r="R40" t="s">
-        <v>10</v>
-      </c>
-      <c r="S40" t="s">
-        <v>21</v>
-      </c>
-      <c r="T40" t="s">
-        <v>185</v>
-      </c>
-      <c r="U40" t="s">
-        <v>186</v>
-      </c>
-      <c r="W40" t="s">
-        <v>432</v>
-      </c>
-      <c r="X40" t="s">
-        <v>491</v>
-      </c>
-      <c r="Y40">
-        <v>59.085000000000001</v>
-      </c>
-      <c r="Z40">
-        <v>0.3909895628623698</v>
-      </c>
-    </row>
-    <row r="41" spans="2:26">
-      <c r="B41" t="s">
-        <v>182</v>
-      </c>
-      <c r="C41" t="s">
-        <v>341</v>
-      </c>
-      <c r="D41" t="s">
-        <v>342</v>
-      </c>
-      <c r="E41" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" t="s">
-        <v>21</v>
-      </c>
-      <c r="G41" t="s">
-        <v>185</v>
-      </c>
-      <c r="H41" t="s">
-        <v>186</v>
-      </c>
-      <c r="J41" t="s">
-        <v>341</v>
-      </c>
-      <c r="K41" t="s">
-        <v>373</v>
-      </c>
-      <c r="L41">
-        <v>24.074478129461852</v>
-      </c>
-      <c r="M41">
-        <v>0.32175887833734967</v>
-      </c>
-      <c r="O41" t="s">
-        <v>182</v>
-      </c>
-      <c r="P41" t="s">
-        <v>434</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>435</v>
-      </c>
-      <c r="R41" t="s">
-        <v>10</v>
-      </c>
-      <c r="S41" t="s">
-        <v>21</v>
-      </c>
-      <c r="T41" t="s">
-        <v>185</v>
-      </c>
-      <c r="U41" t="s">
-        <v>186</v>
-      </c>
-      <c r="W41" t="s">
-        <v>434</v>
-      </c>
-      <c r="X41" t="s">
-        <v>492</v>
-      </c>
-      <c r="Y41">
-        <v>37.460250000000002</v>
-      </c>
-      <c r="Z41">
-        <v>0.4156656148053956</v>
-      </c>
-    </row>
-    <row r="42" spans="2:26">
-      <c r="O42" t="s">
-        <v>182</v>
-      </c>
-      <c r="P42" t="s">
-        <v>436</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>437</v>
-      </c>
-      <c r="R42" t="s">
-        <v>10</v>
-      </c>
-      <c r="S42" t="s">
-        <v>21</v>
-      </c>
-      <c r="T42" t="s">
-        <v>185</v>
-      </c>
-      <c r="U42" t="s">
-        <v>186</v>
-      </c>
-      <c r="W42" t="s">
-        <v>436</v>
-      </c>
-      <c r="X42" t="s">
-        <v>493</v>
-      </c>
-      <c r="Y42">
-        <v>27.642749999999999</v>
-      </c>
-      <c r="Z42">
-        <v>0.36206437671723612</v>
-      </c>
-    </row>
-    <row r="43" spans="2:26">
-      <c r="O43" t="s">
-        <v>182</v>
-      </c>
-      <c r="P43" t="s">
-        <v>438</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>439</v>
-      </c>
-      <c r="R43" t="s">
-        <v>10</v>
-      </c>
-      <c r="S43" t="s">
-        <v>21</v>
-      </c>
-      <c r="T43" t="s">
-        <v>185</v>
-      </c>
-      <c r="U43" t="s">
-        <v>186</v>
-      </c>
-      <c r="W43" t="s">
-        <v>438</v>
-      </c>
-      <c r="X43" t="s">
-        <v>494</v>
-      </c>
-      <c r="Y43">
-        <v>62.597250000000003</v>
-      </c>
-      <c r="Z43">
-        <v>0.36639621425278329</v>
-      </c>
-    </row>
-    <row r="44" spans="2:26">
-      <c r="O44" t="s">
-        <v>182</v>
-      </c>
-      <c r="P44" t="s">
-        <v>440</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>441</v>
-      </c>
-      <c r="R44" t="s">
-        <v>10</v>
-      </c>
-      <c r="S44" t="s">
-        <v>21</v>
-      </c>
-      <c r="T44" t="s">
-        <v>185</v>
-      </c>
-      <c r="U44" t="s">
-        <v>186</v>
-      </c>
-      <c r="W44" t="s">
-        <v>440</v>
-      </c>
-      <c r="X44" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y44">
-        <v>17.07525</v>
-      </c>
-      <c r="Z44">
-        <v>0.366335622458484</v>
-      </c>
-    </row>
-    <row r="45" spans="2:26">
-      <c r="O45" t="s">
-        <v>182</v>
-      </c>
-      <c r="P45" t="s">
-        <v>442</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>443</v>
-      </c>
-      <c r="R45" t="s">
-        <v>10</v>
-      </c>
-      <c r="S45" t="s">
-        <v>21</v>
-      </c>
-      <c r="T45" t="s">
-        <v>185</v>
-      </c>
-      <c r="U45" t="s">
-        <v>186</v>
-      </c>
-      <c r="W45" t="s">
-        <v>442</v>
-      </c>
-      <c r="X45" t="s">
-        <v>496</v>
-      </c>
-      <c r="Y45">
-        <v>0.42149999999999999</v>
-      </c>
-      <c r="Z45">
-        <v>0.28906735909449488</v>
-      </c>
-    </row>
-    <row r="46" spans="2:26">
-      <c r="O46" t="s">
-        <v>182</v>
-      </c>
-      <c r="P46" t="s">
-        <v>444</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>445</v>
-      </c>
-      <c r="R46" t="s">
-        <v>10</v>
-      </c>
-      <c r="S46" t="s">
-        <v>21</v>
-      </c>
-      <c r="T46" t="s">
-        <v>185</v>
-      </c>
-      <c r="U46" t="s">
-        <v>186</v>
-      </c>
-      <c r="W46" t="s">
-        <v>444</v>
-      </c>
-      <c r="X46" t="s">
-        <v>497</v>
-      </c>
-      <c r="Y46">
-        <v>5.7389999999999999</v>
-      </c>
-      <c r="Z46">
-        <v>0.33165266509529728</v>
-      </c>
-    </row>
-    <row r="47" spans="2:26">
-      <c r="O47" t="s">
-        <v>182</v>
-      </c>
-      <c r="P47" t="s">
-        <v>446</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>447</v>
-      </c>
-      <c r="R47" t="s">
-        <v>10</v>
-      </c>
-      <c r="S47" t="s">
-        <v>21</v>
-      </c>
-      <c r="T47" t="s">
-        <v>185</v>
-      </c>
-      <c r="U47" t="s">
-        <v>186</v>
-      </c>
-      <c r="W47" t="s">
-        <v>446</v>
-      </c>
-      <c r="X47" t="s">
-        <v>498</v>
-      </c>
-      <c r="Y47">
-        <v>1.81725</v>
-      </c>
-      <c r="Z47">
-        <v>0.3242980885897736</v>
-      </c>
-    </row>
-    <row r="48" spans="2:26">
-      <c r="O48" t="s">
-        <v>182</v>
-      </c>
-      <c r="P48" t="s">
-        <v>448</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>449</v>
-      </c>
-      <c r="R48" t="s">
-        <v>10</v>
-      </c>
-      <c r="S48" t="s">
-        <v>21</v>
-      </c>
-      <c r="T48" t="s">
-        <v>185</v>
-      </c>
-      <c r="U48" t="s">
-        <v>186</v>
-      </c>
-      <c r="W48" t="s">
-        <v>448</v>
-      </c>
-      <c r="X48" t="s">
-        <v>499</v>
-      </c>
-      <c r="Y48">
-        <v>10.709250000000001</v>
-      </c>
-      <c r="Z48">
-        <v>0.50948065857827751</v>
-      </c>
-    </row>
-    <row r="49" spans="15:26">
-      <c r="O49" t="s">
-        <v>182</v>
-      </c>
-      <c r="P49" t="s">
-        <v>450</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>451</v>
-      </c>
-      <c r="R49" t="s">
-        <v>10</v>
-      </c>
-      <c r="S49" t="s">
-        <v>21</v>
-      </c>
-      <c r="T49" t="s">
-        <v>185</v>
-      </c>
-      <c r="U49" t="s">
-        <v>186</v>
-      </c>
-      <c r="W49" t="s">
-        <v>450</v>
-      </c>
-      <c r="X49" t="s">
-        <v>500</v>
-      </c>
-      <c r="Y49">
-        <v>16.497</v>
-      </c>
-      <c r="Z49">
-        <v>0.45133214213550138</v>
-      </c>
-    </row>
-    <row r="50" spans="15:26">
-      <c r="O50" t="s">
-        <v>182</v>
-      </c>
-      <c r="P50" t="s">
-        <v>452</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>453</v>
-      </c>
-      <c r="R50" t="s">
-        <v>10</v>
-      </c>
-      <c r="S50" t="s">
-        <v>21</v>
-      </c>
-      <c r="T50" t="s">
-        <v>185</v>
-      </c>
-      <c r="U50" t="s">
-        <v>186</v>
-      </c>
-      <c r="W50" t="s">
-        <v>452</v>
-      </c>
-      <c r="X50" t="s">
-        <v>501</v>
-      </c>
-      <c r="Y50">
-        <v>53.960999999999999</v>
-      </c>
-      <c r="Z50">
-        <v>0.52956978618689865</v>
-      </c>
-    </row>
-    <row r="51" spans="15:26">
-      <c r="O51" t="s">
-        <v>182</v>
-      </c>
-      <c r="P51" t="s">
-        <v>454</v>
-      </c>
-      <c r="Q51" t="s">
-        <v>455</v>
-      </c>
-      <c r="R51" t="s">
-        <v>10</v>
-      </c>
-      <c r="S51" t="s">
-        <v>21</v>
-      </c>
-      <c r="T51" t="s">
-        <v>185</v>
-      </c>
-      <c r="U51" t="s">
-        <v>186</v>
-      </c>
-      <c r="W51" t="s">
-        <v>454</v>
-      </c>
-      <c r="X51" t="s">
-        <v>502</v>
-      </c>
-      <c r="Y51">
-        <v>33.036000000000001</v>
-      </c>
-      <c r="Z51">
-        <v>0.43414290231109598</v>
-      </c>
-    </row>
-    <row r="52" spans="15:26">
-      <c r="O52" t="s">
-        <v>182</v>
-      </c>
-      <c r="P52" t="s">
-        <v>456</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>457</v>
-      </c>
-      <c r="R52" t="s">
-        <v>10</v>
-      </c>
-      <c r="S52" t="s">
-        <v>21</v>
-      </c>
-      <c r="T52" t="s">
-        <v>185</v>
-      </c>
-      <c r="U52" t="s">
-        <v>186</v>
-      </c>
-      <c r="W52" t="s">
-        <v>456</v>
-      </c>
-      <c r="X52" t="s">
-        <v>503</v>
-      </c>
-      <c r="Y52">
-        <v>31.234500000000001</v>
-      </c>
-      <c r="Z52">
-        <v>0.35182361384055583</v>
-      </c>
-    </row>
-    <row r="53" spans="15:26">
-      <c r="O53" t="s">
-        <v>182</v>
-      </c>
-      <c r="P53" t="s">
-        <v>458</v>
-      </c>
-      <c r="Q53" t="s">
-        <v>459</v>
-      </c>
-      <c r="R53" t="s">
-        <v>10</v>
-      </c>
-      <c r="S53" t="s">
-        <v>21</v>
-      </c>
-      <c r="T53" t="s">
-        <v>185</v>
-      </c>
-      <c r="U53" t="s">
-        <v>186</v>
-      </c>
-      <c r="W53" t="s">
-        <v>458</v>
-      </c>
-      <c r="X53" t="s">
-        <v>504</v>
-      </c>
-      <c r="Y53">
-        <v>30.527249999999999</v>
-      </c>
-      <c r="Z53">
-        <v>0.3536163889541305</v>
-      </c>
-    </row>
-    <row r="54" spans="15:26">
-      <c r="O54" t="s">
-        <v>182</v>
-      </c>
-      <c r="P54" t="s">
-        <v>460</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>461</v>
-      </c>
-      <c r="R54" t="s">
-        <v>10</v>
-      </c>
-      <c r="S54" t="s">
-        <v>21</v>
-      </c>
-      <c r="T54" t="s">
-        <v>185</v>
-      </c>
-      <c r="U54" t="s">
-        <v>186</v>
-      </c>
-      <c r="W54" t="s">
-        <v>460</v>
-      </c>
-      <c r="X54" t="s">
-        <v>505</v>
-      </c>
-      <c r="Y54">
-        <v>17.390999999999998</v>
-      </c>
-      <c r="Z54">
-        <v>0.37382047274922298</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7A82995-CDFC-41F8-8222-BB47A00CFE7C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3DBD152-E5F8-40A9-B485-1C866F0478FC}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:16">
       <c r="B9" t="s">
-        <v>174</v>
+        <v>236</v>
       </c>
       <c r="J9" t="s">
         <v>163</v>
@@ -10389,13 +10206,13 @@
     </row>
     <row r="10" spans="2:16">
       <c r="B10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C10" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="D10" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="E10">
         <v>2023</v>
@@ -10410,30 +10227,30 @@
         <v>54</v>
       </c>
       <c r="J10" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="K10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M10" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="N10" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="O10" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="P10" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="2:16">
       <c r="B11" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
@@ -10454,10 +10271,10 @@
         <v>146</v>
       </c>
       <c r="J11" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K11" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="M11" t="s">
         <v>10</v>
@@ -10466,15 +10283,15 @@
         <v>21</v>
       </c>
       <c r="O11" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="P11" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="12" spans="2:16">
       <c r="B12" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="C12" t="s">
         <v>31</v>
@@ -10492,13 +10309,13 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H12" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="J12" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K12" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="M12" t="s">
         <v>10</v>
@@ -10507,15 +10324,15 @@
         <v>21</v>
       </c>
       <c r="O12" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="P12" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="13" spans="2:16">
       <c r="B13" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
@@ -10533,13 +10350,13 @@
         <v>5100</v>
       </c>
       <c r="H13" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="J13" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K13" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="M13" t="s">
         <v>10</v>
@@ -10548,15 +10365,15 @@
         <v>21</v>
       </c>
       <c r="O13" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="P13" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="14" spans="2:16">
       <c r="B14" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
@@ -10574,13 +10391,13 @@
         <v>175</v>
       </c>
       <c r="H14" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="J14" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K14" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="M14" t="s">
         <v>10</v>
@@ -10589,15 +10406,15 @@
         <v>21</v>
       </c>
       <c r="O14" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="P14" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="15" spans="2:16">
       <c r="B15" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
@@ -10615,13 +10432,13 @@
         <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="J15" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K15" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="M15" t="s">
         <v>10</v>
@@ -10630,15 +10447,15 @@
         <v>21</v>
       </c>
       <c r="O15" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="P15" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="16" spans="2:16">
       <c r="B16" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="C16" t="s">
         <v>31</v>
@@ -10659,10 +10476,10 @@
         <v>146</v>
       </c>
       <c r="J16" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K16" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="M16" t="s">
         <v>10</v>
@@ -10671,15 +10488,15 @@
         <v>21</v>
       </c>
       <c r="O16" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="P16" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="17" spans="2:16">
       <c r="B17" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="C17" t="s">
         <v>31</v>
@@ -10697,13 +10514,13 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H17" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="J17" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K17" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="M17" t="s">
         <v>10</v>
@@ -10712,15 +10529,15 @@
         <v>21</v>
       </c>
       <c r="O17" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="P17" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="18" spans="2:16">
       <c r="B18" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="C18" t="s">
         <v>31</v>
@@ -10738,13 +10555,13 @@
         <v>2250</v>
       </c>
       <c r="H18" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="J18" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K18" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="M18" t="s">
         <v>10</v>
@@ -10753,15 +10570,15 @@
         <v>21</v>
       </c>
       <c r="O18" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="P18" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="19" spans="2:16">
       <c r="B19" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
@@ -10779,30 +10596,30 @@
         <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="J19" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K19" t="s">
+        <v>509</v>
+      </c>
+      <c r="M19" t="s">
+        <v>10</v>
+      </c>
+      <c r="N19" t="s">
+        <v>21</v>
+      </c>
+      <c r="O19" t="s">
         <v>519</v>
       </c>
-      <c r="M19" t="s">
-        <v>10</v>
-      </c>
-      <c r="N19" t="s">
-        <v>21</v>
-      </c>
-      <c r="O19" t="s">
-        <v>529</v>
-      </c>
       <c r="P19" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="C20" t="s">
         <v>31</v>
@@ -10820,30 +10637,30 @@
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="J20" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K20" t="s">
+        <v>510</v>
+      </c>
+      <c r="M20" t="s">
+        <v>10</v>
+      </c>
+      <c r="N20" t="s">
+        <v>21</v>
+      </c>
+      <c r="O20" t="s">
+        <v>519</v>
+      </c>
+      <c r="P20" t="s">
         <v>520</v>
-      </c>
-      <c r="M20" t="s">
-        <v>10</v>
-      </c>
-      <c r="N20" t="s">
-        <v>21</v>
-      </c>
-      <c r="O20" t="s">
-        <v>529</v>
-      </c>
-      <c r="P20" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="21" spans="2:16">
       <c r="B21" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="C21" t="s">
         <v>33</v>
@@ -10864,10 +10681,10 @@
         <v>146</v>
       </c>
       <c r="J21" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K21" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="M21" t="s">
         <v>10</v>
@@ -10876,15 +10693,15 @@
         <v>21</v>
       </c>
       <c r="O21" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="P21" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="22" spans="2:16">
       <c r="B22" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="C22" t="s">
         <v>33</v>
@@ -10902,13 +10719,13 @@
         <v>1100</v>
       </c>
       <c r="H22" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="J22" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K22" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="M22" t="s">
         <v>10</v>
@@ -10917,15 +10734,15 @@
         <v>21</v>
       </c>
       <c r="O22" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="P22" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="23" spans="2:16">
       <c r="B23" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="C23" t="s">
         <v>33</v>
@@ -10943,13 +10760,13 @@
         <v>30</v>
       </c>
       <c r="H23" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="J23" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K23" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="M23" t="s">
         <v>10</v>
@@ -10958,15 +10775,15 @@
         <v>21</v>
       </c>
       <c r="O23" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="P23" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="24" spans="2:16">
       <c r="B24" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="C24" t="s">
         <v>33</v>
@@ -10987,10 +10804,10 @@
         <v>146</v>
       </c>
       <c r="J24" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K24" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="M24" t="s">
         <v>10</v>
@@ -10999,15 +10816,15 @@
         <v>21</v>
       </c>
       <c r="O24" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="P24" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="25" spans="2:16">
       <c r="B25" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="C25" t="s">
         <v>33</v>
@@ -11025,13 +10842,13 @@
         <v>2500</v>
       </c>
       <c r="H25" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="J25" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K25" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="M25" t="s">
         <v>10</v>
@@ -11040,15 +10857,15 @@
         <v>21</v>
       </c>
       <c r="O25" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="P25" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="26" spans="2:16">
       <c r="B26" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="C26" t="s">
         <v>33</v>
@@ -11066,13 +10883,13 @@
         <v>65</v>
       </c>
       <c r="H26" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="J26" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K26" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="M26" t="s">
         <v>10</v>
@@ -11081,15 +10898,15 @@
         <v>21</v>
       </c>
       <c r="O26" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="P26" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="27" spans="2:16">
       <c r="B27" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
@@ -11110,10 +10927,10 @@
         <v>146</v>
       </c>
       <c r="J27" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K27" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="M27" t="s">
         <v>10</v>
@@ -11122,15 +10939,15 @@
         <v>21</v>
       </c>
       <c r="O27" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="P27" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="28" spans="2:16">
       <c r="B28" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="C28" t="s">
         <v>32</v>
@@ -11148,12 +10965,12 @@
         <v>4750</v>
       </c>
       <c r="H28" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
     </row>
     <row r="29" spans="2:16">
       <c r="B29" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="C29" t="s">
         <v>32</v>
@@ -11171,12 +10988,12 @@
         <v>140</v>
       </c>
       <c r="H29" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
     </row>
     <row r="30" spans="2:16">
       <c r="B30" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="C30" t="s">
         <v>33</v>
@@ -11199,7 +11016,7 @@
     </row>
     <row r="31" spans="2:16">
       <c r="B31" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
@@ -11217,12 +11034,12 @@
         <v>500</v>
       </c>
       <c r="H31" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
     </row>
     <row r="32" spans="2:16">
       <c r="B32" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="C32" t="s">
         <v>33</v>
@@ -11240,12 +11057,12 @@
         <v>20</v>
       </c>
       <c r="H32" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
     </row>
     <row r="33" spans="2:8">
       <c r="B33" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="C33" t="s">
         <v>28</v>
@@ -11268,7 +11085,7 @@
     </row>
     <row r="34" spans="2:8">
       <c r="B34" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="C34" t="s">
         <v>28</v>
@@ -11286,12 +11103,12 @@
         <v>0.5</v>
       </c>
       <c r="H34" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
     </row>
     <row r="35" spans="2:8">
       <c r="B35" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="C35" t="s">
         <v>28</v>
@@ -11309,12 +11126,12 @@
         <v>2400</v>
       </c>
       <c r="H35" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
     </row>
     <row r="36" spans="2:8">
       <c r="B36" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="C36" t="s">
         <v>28</v>
@@ -11332,12 +11149,12 @@
         <v>60</v>
       </c>
       <c r="H36" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
     </row>
     <row r="37" spans="2:8">
       <c r="B37" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="C37" t="s">
         <v>28</v>
@@ -11355,12 +11172,12 @@
         <v>4</v>
       </c>
       <c r="H37" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
     </row>
     <row r="38" spans="2:8">
       <c r="B38" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="C38" t="s">
         <v>33</v>
@@ -11383,7 +11200,7 @@
     </row>
     <row r="39" spans="2:8">
       <c r="B39" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="C39" t="s">
         <v>33</v>
@@ -11401,12 +11218,12 @@
         <v>2700</v>
       </c>
       <c r="H39" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
     </row>
     <row r="40" spans="2:8">
       <c r="B40" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="C40" t="s">
         <v>33</v>
@@ -11424,12 +11241,12 @@
         <v>95</v>
       </c>
       <c r="H40" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="C41" t="s">
         <v>32</v>
@@ -11452,7 +11269,7 @@
     </row>
     <row r="42" spans="2:8">
       <c r="B42" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
@@ -11470,12 +11287,12 @@
         <v>5500</v>
       </c>
       <c r="H42" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="C43" t="s">
         <v>32</v>
@@ -11493,12 +11310,12 @@
         <v>190</v>
       </c>
       <c r="H43" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
     </row>
     <row r="44" spans="2:8">
       <c r="B44" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="C44" t="s">
         <v>36</v>
@@ -11521,7 +11338,7 @@
     </row>
     <row r="45" spans="2:8">
       <c r="B45" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="C45" t="s">
         <v>36</v>
@@ -11539,12 +11356,12 @@
         <v>4000</v>
       </c>
       <c r="H45" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
     </row>
     <row r="46" spans="2:8">
       <c r="B46" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="C46" t="s">
         <v>36</v>
@@ -11562,12 +11379,12 @@
         <v>225</v>
       </c>
       <c r="H46" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
     </row>
     <row r="47" spans="2:8">
       <c r="B47" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="C47" t="s">
         <v>32</v>
@@ -11590,7 +11407,7 @@
     </row>
     <row r="48" spans="2:8">
       <c r="B48" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="C48" t="s">
         <v>32</v>
@@ -11608,12 +11425,12 @@
         <v>5500</v>
       </c>
       <c r="H48" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
     </row>
     <row r="49" spans="2:8">
       <c r="B49" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="C49" t="s">
         <v>32</v>
@@ -11631,12 +11448,12 @@
         <v>165</v>
       </c>
       <c r="H49" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
     </row>
     <row r="50" spans="2:8">
       <c r="B50" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="C50" t="s">
         <v>27</v>
@@ -11659,7 +11476,7 @@
     </row>
     <row r="51" spans="2:8">
       <c r="B51" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
@@ -11677,12 +11494,12 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="H51" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
     </row>
     <row r="52" spans="2:8">
       <c r="B52" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="C52" t="s">
         <v>27</v>
@@ -11700,12 +11517,12 @@
         <v>940</v>
       </c>
       <c r="H52" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
     </row>
     <row r="53" spans="2:8">
       <c r="B53" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="C53" t="s">
         <v>27</v>
@@ -11723,12 +11540,12 @@
         <v>24</v>
       </c>
       <c r="H53" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
     </row>
     <row r="54" spans="2:8">
       <c r="B54" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="C54" t="s">
         <v>27</v>
@@ -11746,12 +11563,12 @@
         <v>1.5</v>
       </c>
       <c r="H54" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
     </row>
     <row r="55" spans="2:8">
       <c r="B55" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="C55" t="s">
         <v>32</v>
@@ -11774,7 +11591,7 @@
     </row>
     <row r="56" spans="2:8">
       <c r="B56" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="C56" t="s">
         <v>32</v>
@@ -11792,12 +11609,12 @@
         <v>2100</v>
       </c>
       <c r="H56" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
     </row>
     <row r="57" spans="2:8">
       <c r="B57" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="C57" t="s">
         <v>32</v>
@@ -11815,12 +11632,12 @@
         <v>55</v>
       </c>
       <c r="H57" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
     </row>
     <row r="58" spans="2:8">
       <c r="B58" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="C58" t="s">
         <v>32</v>
@@ -11843,7 +11660,7 @@
     </row>
     <row r="59" spans="2:8">
       <c r="B59" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="C59" t="s">
         <v>32</v>
@@ -11861,12 +11678,12 @@
         <v>2400</v>
       </c>
       <c r="H59" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
     </row>
     <row r="60" spans="2:8">
       <c r="B60" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="C60" t="s">
         <v>32</v>
@@ -11884,12 +11701,12 @@
         <v>70</v>
       </c>
       <c r="H60" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
     </row>
     <row r="61" spans="2:8">
       <c r="B61" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="C61" t="s">
         <v>32</v>
@@ -11912,7 +11729,7 @@
     </row>
     <row r="62" spans="2:8">
       <c r="B62" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="C62" t="s">
         <v>32</v>
@@ -11930,12 +11747,12 @@
         <v>2600</v>
       </c>
       <c r="H62" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
     </row>
     <row r="63" spans="2:8">
       <c r="B63" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="C63" t="s">
         <v>32</v>
@@ -11953,15 +11770,15 @@
         <v>80</v>
       </c>
       <c r="H63" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
     </row>
     <row r="64" spans="2:8">
       <c r="B64" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="C64" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="D64" t="s">
         <v>19</v>
@@ -11981,10 +11798,10 @@
     </row>
     <row r="65" spans="2:8">
       <c r="B65" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="C65" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="D65" t="s">
         <v>19</v>
@@ -11999,15 +11816,15 @@
         <v>0.46</v>
       </c>
       <c r="H65" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
     </row>
     <row r="66" spans="2:8">
       <c r="B66" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="C66" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="D66" t="s">
         <v>19</v>
@@ -12022,15 +11839,15 @@
         <v>2760</v>
       </c>
       <c r="H66" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
     </row>
     <row r="67" spans="2:8">
       <c r="B67" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="C67" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="D67" t="s">
         <v>19</v>
@@ -12045,15 +11862,15 @@
         <v>85</v>
       </c>
       <c r="H67" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
     </row>
     <row r="68" spans="2:8">
       <c r="B68" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="C68" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="D68" t="s">
         <v>19</v>
@@ -12068,15 +11885,15 @@
         <v>3</v>
       </c>
       <c r="H68" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
     </row>
     <row r="69" spans="2:8">
       <c r="B69" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="C69" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="D69" t="s">
         <v>19</v>
@@ -12096,10 +11913,10 @@
     </row>
     <row r="70" spans="2:8">
       <c r="B70" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="C70" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="D70" t="s">
         <v>19</v>
@@ -12114,15 +11931,15 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H70" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
     </row>
     <row r="71" spans="2:8">
       <c r="B71" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="C71" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="D71" t="s">
         <v>19</v>
@@ -12137,15 +11954,15 @@
         <v>2140</v>
       </c>
       <c r="H71" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
     </row>
     <row r="72" spans="2:8">
       <c r="B72" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="C72" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="D72" t="s">
         <v>19</v>
@@ -12160,15 +11977,15 @@
         <v>56</v>
       </c>
       <c r="H72" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
     </row>
     <row r="73" spans="2:8">
       <c r="B73" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="C73" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="D73" t="s">
         <v>19</v>
@@ -12183,7 +12000,7 @@
         <v>1.5</v>
       </c>
       <c r="H73" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEBF8322-B0DD-4F9F-814A-C706E65FCE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D9381EA-2956-4B38-BDDC-C48FF7BC7BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6399,7 +6399,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E376988-7750-490E-A31A-29E9D834FDE4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9AB1B24-FF36-404D-9650-A001BC968ED5}">
   <dimension ref="B9:M41"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6720,10 +6720,10 @@
         <v>247</v>
       </c>
       <c r="L18">
-        <v>3.3207199574486039</v>
+        <v>11.049590277797785</v>
       </c>
       <c r="M18">
-        <v>0.1885405557074413</v>
+        <v>0.19454864451673889</v>
       </c>
     </row>
     <row r="19" spans="2:13">
@@ -6755,10 +6755,10 @@
         <v>248</v>
       </c>
       <c r="L19">
-        <v>9.0718124098924431</v>
+        <v>2.0672282720381219</v>
       </c>
       <c r="M19">
-        <v>0.1955082967785822</v>
+        <v>0.1897242685700597</v>
       </c>
     </row>
     <row r="20" spans="2:13">
@@ -6790,10 +6790,10 @@
         <v>249</v>
       </c>
       <c r="L20">
-        <v>2.4919323033128578</v>
+        <v>6.2367051121823778</v>
       </c>
       <c r="M20">
-        <v>0.1849714119787586</v>
+        <v>0.19008013066509069</v>
       </c>
     </row>
     <row r="21" spans="2:13">
@@ -6825,10 +6825,10 @@
         <v>250</v>
       </c>
       <c r="L21">
-        <v>8.1269082914211843</v>
+        <v>3.4507474395717592</v>
       </c>
       <c r="M21">
-        <v>0.19077375643859301</v>
+        <v>0.18572183333239789</v>
       </c>
     </row>
     <row r="22" spans="2:13">
@@ -6860,10 +6860,10 @@
         <v>251</v>
       </c>
       <c r="L22">
-        <v>2.0672282720381219</v>
+        <v>2.1926901847120215</v>
       </c>
       <c r="M22">
-        <v>0.1897242685700597</v>
+        <v>0.18550629799122259</v>
       </c>
     </row>
     <row r="23" spans="2:13">
@@ -6895,10 +6895,10 @@
         <v>252</v>
       </c>
       <c r="L23">
-        <v>6.2367051121823778</v>
+        <v>6.3183450599935256</v>
       </c>
       <c r="M23">
-        <v>0.19008013066509069</v>
+        <v>0.19209496103447071</v>
       </c>
     </row>
     <row r="24" spans="2:13">
@@ -7537,7 +7537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{368140A0-F7F0-47A5-8C5D-12FF8C8CA629}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FF4053A-0DE9-4BD0-8AD6-3A602A59FFDE}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7652,10 +7652,10 @@
         <v>333</v>
       </c>
       <c r="L11">
-        <v>26.081770464705624</v>
+        <v>6.1151684514715345</v>
       </c>
       <c r="M11">
-        <v>0.33938741610056822</v>
+        <v>0.44244733217755411</v>
       </c>
       <c r="O11" t="s">
         <v>171</v>
@@ -7720,10 +7720,10 @@
         <v>334</v>
       </c>
       <c r="L12">
-        <v>28.326303899090867</v>
+        <v>4.1221966299799098</v>
       </c>
       <c r="M12">
-        <v>0.31672699232591051</v>
+        <v>0.47272019788829328</v>
       </c>
       <c r="O12" t="s">
         <v>171</v>
@@ -7788,10 +7788,10 @@
         <v>335</v>
       </c>
       <c r="L13">
-        <v>36.748148815624823</v>
+        <v>6.7028485191473308E-2</v>
       </c>
       <c r="M13">
-        <v>0.24124293159761159</v>
+        <v>0.41432793234675691</v>
       </c>
       <c r="O13" t="s">
         <v>171</v>
@@ -7856,10 +7856,10 @@
         <v>336</v>
       </c>
       <c r="L14">
-        <v>33.851015501811965</v>
+        <v>1.3102559495532347</v>
       </c>
       <c r="M14">
-        <v>0.17836569756942919</v>
+        <v>0.51823166137173471</v>
       </c>
       <c r="O14" t="s">
         <v>171</v>
@@ -7924,10 +7924,10 @@
         <v>337</v>
       </c>
       <c r="L15">
-        <v>29.76120824924126</v>
+        <v>27.131882337818411</v>
       </c>
       <c r="M15">
-        <v>0.1835874284667649</v>
+        <v>0.13421919246645389</v>
       </c>
       <c r="O15" t="s">
         <v>171</v>
@@ -7992,10 +7992,10 @@
         <v>338</v>
       </c>
       <c r="L16">
-        <v>13.047413180463023</v>
+        <v>36.154364232779898</v>
       </c>
       <c r="M16">
-        <v>0.11846842726897321</v>
+        <v>0.17081469208919761</v>
       </c>
       <c r="O16" t="s">
         <v>171</v>
@@ -8060,10 +8060,10 @@
         <v>339</v>
       </c>
       <c r="L17">
-        <v>23.637816650626842</v>
+        <v>25.382671197199805</v>
       </c>
       <c r="M17">
-        <v>0.1537391571572389</v>
+        <v>0.21663633167034491</v>
       </c>
       <c r="O17" t="s">
         <v>171</v>
@@ -8128,10 +8128,10 @@
         <v>340</v>
       </c>
       <c r="L18">
-        <v>50.076680799526407</v>
+        <v>12.622398873979849</v>
       </c>
       <c r="M18">
-        <v>0.19002505627190239</v>
+        <v>0.21492245874046481</v>
       </c>
       <c r="O18" t="s">
         <v>171</v>
@@ -8196,10 +8196,10 @@
         <v>341</v>
       </c>
       <c r="L19">
-        <v>22.504679657777121</v>
+        <v>25.14604307789013</v>
       </c>
       <c r="M19">
-        <v>0.43998684438339841</v>
+        <v>0.2214146377764582</v>
       </c>
       <c r="O19" t="s">
         <v>171</v>
@@ -8264,10 +8264,10 @@
         <v>342</v>
       </c>
       <c r="L20">
-        <v>39.022668784713879</v>
+        <v>7.5025171344716721</v>
       </c>
       <c r="M20">
-        <v>0.30226720130549178</v>
+        <v>0.102078386690078</v>
       </c>
       <c r="O20" t="s">
         <v>171</v>
@@ -8332,10 +8332,10 @@
         <v>343</v>
       </c>
       <c r="L21">
-        <v>12.527007796473459</v>
+        <v>49.463010296199585</v>
       </c>
       <c r="M21">
-        <v>0.26335249621019208</v>
+        <v>0.21899976682577069</v>
       </c>
       <c r="O21" t="s">
         <v>171</v>
@@ -8400,10 +8400,10 @@
         <v>344</v>
       </c>
       <c r="L22">
-        <v>22.322239264526591</v>
+        <v>7.0903888161806279</v>
       </c>
       <c r="M22">
-        <v>0.24546553943130331</v>
+        <v>0.126349887785319</v>
       </c>
       <c r="O22" t="s">
         <v>171</v>
@@ -8468,10 +8468,10 @@
         <v>345</v>
       </c>
       <c r="L23">
-        <v>6.1151684514715345</v>
+        <v>16.970662525397827</v>
       </c>
       <c r="M23">
-        <v>0.44244733217755411</v>
+        <v>0.2876476609673595</v>
       </c>
       <c r="O23" t="s">
         <v>171</v>
@@ -8536,10 +8536,10 @@
         <v>346</v>
       </c>
       <c r="L24">
-        <v>4.1221966299799098</v>
+        <v>2.5242004930684354</v>
       </c>
       <c r="M24">
-        <v>0.47272019788829328</v>
+        <v>9.3541201112904898E-2</v>
       </c>
       <c r="O24" t="s">
         <v>171</v>
@@ -8604,10 +8604,10 @@
         <v>347</v>
       </c>
       <c r="L25">
-        <v>6.7028485191473308E-2</v>
+        <v>5.5071261071764246</v>
       </c>
       <c r="M25">
-        <v>0.41432793234675691</v>
+        <v>0.34206800892605482</v>
       </c>
       <c r="O25" t="s">
         <v>171</v>
@@ -8672,10 +8672,10 @@
         <v>348</v>
       </c>
       <c r="L26">
-        <v>1.3102559495532347</v>
+        <v>8.4886449615793467</v>
       </c>
       <c r="M26">
-        <v>0.51823166137173471</v>
+        <v>0.33231574315319728</v>
       </c>
       <c r="O26" t="s">
         <v>171</v>
@@ -8740,10 +8740,10 @@
         <v>349</v>
       </c>
       <c r="L27">
-        <v>51.171736048895305</v>
+        <v>8.4075540995285696</v>
       </c>
       <c r="M27">
-        <v>0.1753269736233318</v>
+        <v>0.28011366210530497</v>
       </c>
       <c r="O27" t="s">
         <v>171</v>
@@ -8808,10 +8808,10 @@
         <v>350</v>
       </c>
       <c r="L28">
-        <v>27.131882337818411</v>
+        <v>15.703622047270191</v>
       </c>
       <c r="M28">
-        <v>0.13421919246645389</v>
+        <v>0.2902999058993756</v>
       </c>
       <c r="O28" t="s">
         <v>171</v>
@@ -8876,10 +8876,10 @@
         <v>351</v>
       </c>
       <c r="L29">
-        <v>8.7915989873091043</v>
+        <v>24.074478129461852</v>
       </c>
       <c r="M29">
-        <v>0.33157900311052629</v>
+        <v>0.32175887833734967</v>
       </c>
       <c r="O29" t="s">
         <v>171</v>
@@ -8944,10 +8944,10 @@
         <v>352</v>
       </c>
       <c r="L30">
-        <v>26.915511431987859</v>
+        <v>12.527007796473459</v>
       </c>
       <c r="M30">
-        <v>0.17204244166879709</v>
+        <v>0.26335249621019208</v>
       </c>
       <c r="O30" t="s">
         <v>171</v>
@@ -9012,10 +9012,10 @@
         <v>353</v>
       </c>
       <c r="L31">
-        <v>7.5025171344716721</v>
+        <v>22.322239264526591</v>
       </c>
       <c r="M31">
-        <v>0.102078386690078</v>
+        <v>0.24546553943130331</v>
       </c>
       <c r="O31" t="s">
         <v>171</v>
@@ -9080,10 +9080,10 @@
         <v>354</v>
       </c>
       <c r="L32">
-        <v>21.853336570084423</v>
+        <v>13.047413180463023</v>
       </c>
       <c r="M32">
-        <v>0.2470260197032213</v>
+        <v>0.11846842726897321</v>
       </c>
       <c r="O32" t="s">
         <v>171</v>
@@ -9148,10 +9148,10 @@
         <v>355</v>
       </c>
       <c r="L33">
-        <v>40.036304639772588</v>
+        <v>23.637816650626842</v>
       </c>
       <c r="M33">
-        <v>0.22158847806059459</v>
+        <v>0.1537391571572389</v>
       </c>
       <c r="O33" t="s">
         <v>171</v>
@@ -9216,10 +9216,10 @@
         <v>356</v>
       </c>
       <c r="L34">
-        <v>7.0903888161806279</v>
+        <v>50.076680799526407</v>
       </c>
       <c r="M34">
-        <v>0.126349887785319</v>
+        <v>0.19002505627190239</v>
       </c>
       <c r="O34" t="s">
         <v>171</v>
@@ -9284,10 +9284,10 @@
         <v>357</v>
       </c>
       <c r="L35">
-        <v>16.970662525397827</v>
+        <v>44.894334115294185</v>
       </c>
       <c r="M35">
-        <v>0.2876476609673595</v>
+        <v>0.26214900595896268</v>
       </c>
       <c r="O35" t="s">
         <v>171</v>
@@ -9352,10 +9352,10 @@
         <v>358</v>
       </c>
       <c r="L36">
-        <v>2.5242004930684354</v>
+        <v>14.358494358107757</v>
       </c>
       <c r="M36">
-        <v>9.3541201112904898E-2</v>
+        <v>0.48737624583080358</v>
       </c>
       <c r="O36" t="s">
         <v>171</v>
@@ -9420,10 +9420,10 @@
         <v>359</v>
       </c>
       <c r="L37">
-        <v>5.5071261071764246</v>
+        <v>39.022668784713879</v>
       </c>
       <c r="M37">
-        <v>0.34206800892605482</v>
+        <v>0.30226720130549178</v>
       </c>
       <c r="O37" t="s">
         <v>171</v>
@@ -9488,10 +9488,10 @@
         <v>360</v>
       </c>
       <c r="L38">
-        <v>8.4886449615793467</v>
+        <v>33.851015501811965</v>
       </c>
       <c r="M38">
-        <v>0.33231574315319728</v>
+        <v>0.17836569756942919</v>
       </c>
       <c r="O38" t="s">
         <v>171</v>
@@ -9556,10 +9556,10 @@
         <v>361</v>
       </c>
       <c r="L39">
-        <v>8.4075540995285696</v>
+        <v>29.76120824924126</v>
       </c>
       <c r="M39">
-        <v>0.28011366210530497</v>
+        <v>0.1835874284667649</v>
       </c>
       <c r="O39" t="s">
         <v>171</v>
@@ -9624,10 +9624,10 @@
         <v>362</v>
       </c>
       <c r="L40">
-        <v>15.703622047270191</v>
+        <v>26.081770464705624</v>
       </c>
       <c r="M40">
-        <v>0.2902999058993756</v>
+        <v>0.33938741610056822</v>
       </c>
       <c r="O40" t="s">
         <v>171</v>
@@ -9692,10 +9692,10 @@
         <v>363</v>
       </c>
       <c r="L41">
-        <v>24.074478129461852</v>
+        <v>28.326303899090867</v>
       </c>
       <c r="M41">
-        <v>0.32175887833734967</v>
+        <v>0.31672699232591051</v>
       </c>
       <c r="O41" t="s">
         <v>171</v>
@@ -10192,7 +10192,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3DBD152-E5F8-40A9-B485-1C866F0478FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7E61A8B-CD21-49E1-9E7C-B547A52208C1}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D9381EA-2956-4B38-BDDC-C48FF7BC7BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{14313848-E9D6-4BEF-A978-E8EA90940790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6399,7 +6399,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9AB1B24-FF36-404D-9650-A001BC968ED5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3F2387E-E909-4DDE-BD94-D2F7C728C49D}">
   <dimension ref="B9:M41"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7537,7 +7537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FF4053A-0DE9-4BD0-8AD6-3A602A59FFDE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0A81C70-740E-44E3-AD4B-68DE7C43F594}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10192,7 +10192,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7E61A8B-CD21-49E1-9E7C-B547A52208C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A14D618-2117-4EA9-AF99-D31E89019D0A}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{14313848-E9D6-4BEF-A978-E8EA90940790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F278295E-CF87-4F90-9936-C887E3270015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6399,7 +6399,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3F2387E-E909-4DDE-BD94-D2F7C728C49D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81B81187-24EB-42E5-ACB2-306A4A4B17F1}">
   <dimension ref="B9:M41"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7537,7 +7537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0A81C70-740E-44E3-AD4B-68DE7C43F594}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{509658F7-2092-4AA5-9FF6-39EE42C42E5D}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10192,7 +10192,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A14D618-2117-4EA9-AF99-D31E89019D0A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{857E82F3-DCCD-4BE9-99BE-185880BFC6FD}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_JPN/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F278295E-CF87-4F90-9936-C887E3270015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3727C688-B7C2-480C-A6D4-E5E65F14A582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6399,7 +6399,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81B81187-24EB-42E5-ACB2-306A4A4B17F1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83593BEE-C6AD-4D04-823B-37D245413923}">
   <dimension ref="B9:M41"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6475,10 +6475,10 @@
         <v>240</v>
       </c>
       <c r="L11">
-        <v>1.0868475837211775</v>
+        <v>1.2695492135139217</v>
       </c>
       <c r="M11">
-        <v>0.18525666908653099</v>
+        <v>0.1768982238146152</v>
       </c>
     </row>
     <row r="12" spans="2:13">
@@ -6510,10 +6510,10 @@
         <v>241</v>
       </c>
       <c r="L12">
-        <v>0.49620812665820685</v>
+        <v>11.170148024550075</v>
       </c>
       <c r="M12">
-        <v>0.18139311086660159</v>
+        <v>0.17820812772092209</v>
       </c>
     </row>
     <row r="13" spans="2:13">
@@ -6545,10 +6545,10 @@
         <v>242</v>
       </c>
       <c r="L13">
-        <v>4.0441125317019988E-2</v>
+        <v>6.0583925239792951</v>
       </c>
       <c r="M13">
-        <v>0.20223864817792889</v>
+        <v>0.17190415393703271</v>
       </c>
     </row>
     <row r="14" spans="2:13">
@@ -6580,10 +6580,10 @@
         <v>243</v>
       </c>
       <c r="L14">
-        <v>3.1156738745546861</v>
+        <v>4.9429022151581998</v>
       </c>
       <c r="M14">
-        <v>0.1844401710515986</v>
+        <v>0.17623300047483759</v>
       </c>
     </row>
     <row r="15" spans="2:13">
@@ -6615,10 +6615,10 @@
         <v>244</v>
       </c>
       <c r="L15">
-        <v>1.0095122884700507</v>
+        <v>3.1087651703643377</v>
       </c>
       <c r="M15">
-        <v>0.18575864794618849</v>
+        <v>0.1713626664711283</v>
       </c>
     </row>
     <row r="16" spans="2:13">
@@ -6650,10 +6650,10 @@
         <v>245</v>
       </c>
       <c r="L16">
-        <v>9.6014343718961292</v>
+        <v>7.6858099243981899</v>
       </c>
       <c r="M16">
-        <v>0.1799742763899051</v>
+        <v>0.16962307707337801</v>
       </c>
     </row>
     <row r="17" spans="2:13">
@@ -6685,10 +6685,10 @@
         <v>246</v>
       </c>
       <c r="L17">
-        <v>11.664406830498095</v>
+        <v>6.8708538922649831</v>
       </c>
       <c r="M17">
-        <v>0.20214793379564561</v>
+        <v>0.17252690554813149</v>
       </c>
     </row>
     <row r="18" spans="2:13">
@@ -6720,10 +6720,10 @@
         <v>247</v>
       </c>
       <c r="L18">
-        <v>11.049590277797785</v>
+        <v>1.8808781416844131</v>
       </c>
       <c r="M18">
-        <v>0.19454864451673889</v>
+        <v>0.17266493010223849</v>
       </c>
     </row>
     <row r="19" spans="2:13">
@@ -6755,10 +6755,10 @@
         <v>248</v>
       </c>
       <c r="L19">
-        <v>2.0672282720381219</v>
+        <v>2.234130084558998</v>
       </c>
       <c r="M19">
-        <v>0.1897242685700597</v>
+        <v>0.17375166762337191</v>
       </c>
     </row>
     <row r="20" spans="2:13">
@@ -6790,10 +6790,10 @@
         <v>249</v>
       </c>
       <c r="L20">
-        <v>6.2367051121823778</v>
+        <v>8.2308495959667809</v>
       </c>
       <c r="M20">
-        <v>0.19008013066509069</v>
+        <v>0.1872946834989149</v>
       </c>
     </row>
     <row r="21" spans="2:13">
@@ -6825,10 +6825,10 @@
         <v>250</v>
       </c>
       <c r="L21">
-        <v>3.4507474395717592</v>
+        <v>12.207707960945804</v>
       </c>
       <c r="M21">
-        <v>0.18572183333239789</v>
+        <v>0.1885277185926072</v>
       </c>
     </row>
     <row r="22" spans="2:13">
@@ -6860,10 +6860,10 @@
         <v>251</v>
       </c>
       <c r="L22">
-        <v>2.1926901847120215</v>
+        <v>11.84836321250885</v>
       </c>
       <c r="M22">
-        <v>0.18550629799122259</v>
+        <v>0.18764376746668049</v>
       </c>
     </row>
     <row r="23" spans="2:13">
@@ -6895,10 +6895,10 @@
         <v>252</v>
       </c>
       <c r="L23">
-        <v>6.3183450599935256</v>
+        <v>6.311418285235062</v>
       </c>
       <c r="M23">
-        <v>0.19209496103447071</v>
+        <v>0.1693068332707558</v>
       </c>
     </row>
     <row r="24" spans="2:13">
@@ -6930,10 +6930,10 @@
         <v>253</v>
       </c>
       <c r="L24">
-        <v>4.9429022151581998</v>
+        <v>0.59280478309309115</v>
       </c>
       <c r="M24">
-        <v>0.17623300047483759</v>
+        <v>0.18856710274390229</v>
       </c>
     </row>
     <row r="25" spans="2:13">
@@ -6965,10 +6965,10 @@
         <v>254</v>
       </c>
       <c r="L25">
-        <v>6.0583925239792951</v>
+        <v>6.614368021654732</v>
       </c>
       <c r="M25">
-        <v>0.17190415393703271</v>
+        <v>0.1892871810641478</v>
       </c>
     </row>
     <row r="26" spans="2:13">
@@ -7000,10 +7000,10 @@
         <v>255</v>
       </c>
       <c r="L26">
-        <v>8.8562728829669233</v>
+        <v>9.4700882153505201</v>
       </c>
       <c r="M26">
-        <v>0.17852540925562671</v>
+        <v>0.17932962385242079</v>
       </c>
     </row>
     <row r="27" spans="2:13">
@@ -7035,10 +7035,10 @@
         <v>256</v>
       </c>
       <c r="L27">
-        <v>3.1087651703643377</v>
+        <v>5.819871101459503</v>
       </c>
       <c r="M27">
-        <v>0.1713626664711283</v>
+        <v>0.1668865544761739</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7070,10 +7070,10 @@
         <v>257</v>
       </c>
       <c r="L28">
-        <v>7.6858099243981899</v>
+        <v>7.4335447943742894</v>
       </c>
       <c r="M28">
-        <v>0.16962307707337801</v>
+        <v>0.17297840533466791</v>
       </c>
     </row>
     <row r="29" spans="2:13">
@@ -7105,10 +7105,10 @@
         <v>258</v>
       </c>
       <c r="L29">
-        <v>8.8290491423659851</v>
+        <v>0.11366418204482304</v>
       </c>
       <c r="M29">
-        <v>0.17384629516416941</v>
+        <v>0.18364651891835679</v>
       </c>
     </row>
     <row r="30" spans="2:13">
@@ -7140,10 +7140,10 @@
         <v>259</v>
       </c>
       <c r="L30">
-        <v>3.8593591895550672</v>
+        <v>0.97318340167635442</v>
       </c>
       <c r="M30">
-        <v>0.17433358698743889</v>
+        <v>0.18544472860493169</v>
       </c>
     </row>
     <row r="31" spans="2:13">
@@ -7175,10 +7175,10 @@
         <v>260</v>
       </c>
       <c r="L31">
-        <v>8.2308495959667809</v>
+        <v>0.49620812665820685</v>
       </c>
       <c r="M31">
-        <v>0.1872946834989149</v>
+        <v>0.18139311086660159</v>
       </c>
     </row>
     <row r="32" spans="2:13">
@@ -7210,10 +7210,10 @@
         <v>261</v>
       </c>
       <c r="L32">
-        <v>4.1919248573917418</v>
+        <v>4.0441125317019988E-2</v>
       </c>
       <c r="M32">
-        <v>0.1839798063486249</v>
+        <v>0.20223864817792889</v>
       </c>
     </row>
     <row r="33" spans="2:13">
@@ -7245,10 +7245,10 @@
         <v>262</v>
       </c>
       <c r="L33">
-        <v>12.207707960945804</v>
+        <v>3.1156738745546861</v>
       </c>
       <c r="M33">
-        <v>0.1885277185926072</v>
+        <v>0.1844401710515986</v>
       </c>
     </row>
     <row r="34" spans="2:13">
@@ -7280,10 +7280,10 @@
         <v>263</v>
       </c>
       <c r="L34">
-        <v>11.84836321250885</v>
+        <v>1.0095122884700507</v>
       </c>
       <c r="M34">
-        <v>0.18764376746668049</v>
+        <v>0.18575864794618849</v>
       </c>
     </row>
     <row r="35" spans="2:13">
@@ -7315,10 +7315,10 @@
         <v>264</v>
       </c>
       <c r="L35">
-        <v>6.614368021654732</v>
+        <v>9.6014343718961292</v>
       </c>
       <c r="M35">
-        <v>0.1892871810641478</v>
+        <v>0.1799742763899051</v>
       </c>
     </row>
     <row r="36" spans="2:13">
@@ -7350,10 +7350,10 @@
         <v>265</v>
       </c>
       <c r="L36">
-        <v>2.2140559413717158</v>
+        <v>2.0672282720381219</v>
       </c>
       <c r="M36">
-        <v>0.17924996447431779</v>
+        <v>0.1897242685700597</v>
       </c>
     </row>
     <row r="37" spans="2:13">
@@ -7385,10 +7385,10 @@
         <v>266</v>
       </c>
       <c r="L37">
-        <v>6.2355425421755246</v>
+        <v>6.2367051121823778</v>
       </c>
       <c r="M37">
-        <v>0.1685465489224991</v>
+        <v>0.19008013066509069</v>
       </c>
     </row>
     <row r="38" spans="2:13">
@@ -7420,10 +7420,10 @@
         <v>267</v>
       </c>
       <c r="L38">
-        <v>8.5054017076497139</v>
+        <v>4.1704680526173608</v>
       </c>
       <c r="M38">
-        <v>0.1737818205315152</v>
+        <v>0.18770700242490479</v>
       </c>
     </row>
     <row r="39" spans="2:13">
@@ -7455,10 +7455,10 @@
         <v>268</v>
       </c>
       <c r="L39">
-        <v>4.3103819501195213</v>
+        <v>7.9128107192233994</v>
       </c>
       <c r="M39">
-        <v>0.16638536910986701</v>
+        <v>0.188323251873562</v>
       </c>
     </row>
     <row r="40" spans="2:13">
@@ -7490,10 +7490,10 @@
         <v>269</v>
       </c>
       <c r="L40">
-        <v>4.1704201808042445</v>
+        <v>8.6014499324664992</v>
       </c>
       <c r="M40">
-        <v>0.1729732681063105</v>
+        <v>0.20110764767728459</v>
       </c>
     </row>
     <row r="41" spans="2:13">
@@ -7525,10 +7525,10 @@
         <v>270</v>
       </c>
       <c r="L41">
-        <v>1.8808781416844131</v>
+        <v>13.991051088265927</v>
       </c>
       <c r="M41">
-        <v>0.17266493010223849</v>
+        <v>0.1977098143340752</v>
       </c>
     </row>
   </sheetData>
@@ -7537,7 +7537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{509658F7-2092-4AA5-9FF6-39EE42C42E5D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C587A473-32A5-433F-9054-A843293BA059}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7924,10 +7924,10 @@
         <v>337</v>
       </c>
       <c r="L15">
-        <v>27.131882337818411</v>
+        <v>51.171736048895305</v>
       </c>
       <c r="M15">
-        <v>0.13421919246645389</v>
+        <v>0.1753269736233318</v>
       </c>
       <c r="O15" t="s">
         <v>171</v>
@@ -7992,10 +7992,10 @@
         <v>338</v>
       </c>
       <c r="L16">
-        <v>36.154364232779898</v>
+        <v>27.131882337818411</v>
       </c>
       <c r="M16">
-        <v>0.17081469208919761</v>
+        <v>0.13421919246645389</v>
       </c>
       <c r="O16" t="s">
         <v>171</v>
@@ -8060,10 +8060,10 @@
         <v>339</v>
       </c>
       <c r="L17">
-        <v>25.382671197199805</v>
+        <v>8.7915989873091043</v>
       </c>
       <c r="M17">
-        <v>0.21663633167034491</v>
+        <v>0.33157900311052629</v>
       </c>
       <c r="O17" t="s">
         <v>171</v>
@@ -8128,10 +8128,10 @@
         <v>340</v>
       </c>
       <c r="L18">
-        <v>12.622398873979849</v>
+        <v>26.915511431987859</v>
       </c>
       <c r="M18">
-        <v>0.21492245874046481</v>
+        <v>0.17204244166879709</v>
       </c>
       <c r="O18" t="s">
         <v>171</v>
@@ -8161,10 +8161,10 @@
         <v>459</v>
       </c>
       <c r="Y18">
-        <v>28.478249999999999</v>
+        <v>14.47725</v>
       </c>
       <c r="Z18">
-        <v>0.31013048721759129</v>
+        <v>0.31245285574348192</v>
       </c>
     </row>
     <row r="19" spans="2:26">
@@ -8196,10 +8196,10 @@
         <v>341</v>
       </c>
       <c r="L19">
-        <v>25.14604307789013</v>
+        <v>7.5025171344716721</v>
       </c>
       <c r="M19">
-        <v>0.2214146377764582</v>
+        <v>0.102078386690078</v>
       </c>
       <c r="O19" t="s">
         <v>171</v>
@@ -8229,10 +8229,10 @@
         <v>460</v>
       </c>
       <c r="Y19">
-        <v>22.079249999999998</v>
+        <v>14.000999999999999</v>
       </c>
       <c r="Z19">
-        <v>0.3223061905611202</v>
+        <v>0.30772912233355088</v>
       </c>
     </row>
     <row r="20" spans="2:26">
@@ -8264,10 +8264,10 @@
         <v>342</v>
       </c>
       <c r="L20">
-        <v>7.5025171344716721</v>
+        <v>21.853336570084423</v>
       </c>
       <c r="M20">
-        <v>0.102078386690078</v>
+        <v>0.2470260197032213</v>
       </c>
       <c r="O20" t="s">
         <v>171</v>
@@ -8297,10 +8297,10 @@
         <v>461</v>
       </c>
       <c r="Y20">
-        <v>29.961749999999999</v>
+        <v>22.079249999999998</v>
       </c>
       <c r="Z20">
-        <v>0.33421489525964382</v>
+        <v>0.3223061905611202</v>
       </c>
     </row>
     <row r="21" spans="2:26">
@@ -8332,10 +8332,10 @@
         <v>343</v>
       </c>
       <c r="L21">
-        <v>49.463010296199585</v>
+        <v>40.036304639772588</v>
       </c>
       <c r="M21">
-        <v>0.21899976682577069</v>
+        <v>0.22158847806059459</v>
       </c>
       <c r="O21" t="s">
         <v>171</v>
@@ -8365,10 +8365,10 @@
         <v>462</v>
       </c>
       <c r="Y21">
-        <v>117.89700000000001</v>
+        <v>29.961749999999999</v>
       </c>
       <c r="Z21">
-        <v>0.4454005763280634</v>
+        <v>0.33421489525964382</v>
       </c>
     </row>
     <row r="22" spans="2:26">
@@ -8433,10 +8433,10 @@
         <v>463</v>
       </c>
       <c r="Y22">
-        <v>75.481499999999997</v>
+        <v>117.89700000000001</v>
       </c>
       <c r="Z22">
-        <v>0.39947482218024288</v>
+        <v>0.4454005763280634</v>
       </c>
     </row>
     <row r="23" spans="2:26">
@@ -8501,10 +8501,10 @@
         <v>464</v>
       </c>
       <c r="Y23">
-        <v>10.68975</v>
+        <v>75.481499999999997</v>
       </c>
       <c r="Z23">
-        <v>0.2858957309818449</v>
+        <v>0.39947482218024288</v>
       </c>
     </row>
     <row r="24" spans="2:26">
@@ -8569,10 +8569,10 @@
         <v>465</v>
       </c>
       <c r="Y24">
-        <v>82.607249999999993</v>
+        <v>10.68975</v>
       </c>
       <c r="Z24">
-        <v>0.4138948789420363</v>
+        <v>0.2858957309818449</v>
       </c>
     </row>
     <row r="25" spans="2:26">
@@ -8637,10 +8637,10 @@
         <v>466</v>
       </c>
       <c r="Y25">
-        <v>28.239750000000001</v>
+        <v>82.607249999999993</v>
       </c>
       <c r="Z25">
-        <v>0.39283819950969068</v>
+        <v>0.4138948789420363</v>
       </c>
     </row>
     <row r="26" spans="2:26">
@@ -8705,10 +8705,10 @@
         <v>467</v>
       </c>
       <c r="Y26">
-        <v>1.9132499999999999</v>
+        <v>22.785</v>
       </c>
       <c r="Z26">
-        <v>0.24373705543466159</v>
+        <v>0.35144265618738502</v>
       </c>
     </row>
     <row r="27" spans="2:26">
@@ -8841,10 +8841,10 @@
         <v>469</v>
       </c>
       <c r="Y28">
-        <v>38.451000000000001</v>
+        <v>28.239750000000001</v>
       </c>
       <c r="Z28">
-        <v>0.41699608360155571</v>
+        <v>0.39283819950969068</v>
       </c>
     </row>
     <row r="29" spans="2:26">
@@ -8909,10 +8909,10 @@
         <v>470</v>
       </c>
       <c r="Y29">
-        <v>64.533749999999998</v>
+        <v>38.15925</v>
       </c>
       <c r="Z29">
-        <v>0.49947203939427631</v>
+        <v>0.42518909184060127</v>
       </c>
     </row>
     <row r="30" spans="2:26">
@@ -8977,10 +8977,10 @@
         <v>471</v>
       </c>
       <c r="Y30">
-        <v>44.370750000000001</v>
+        <v>3.38625</v>
       </c>
       <c r="Z30">
-        <v>0.45077590772414738</v>
+        <v>0.27397097122901398</v>
       </c>
     </row>
     <row r="31" spans="2:26">
@@ -9045,10 +9045,10 @@
         <v>472</v>
       </c>
       <c r="Y31">
-        <v>38.15925</v>
+        <v>30.597750000000001</v>
       </c>
       <c r="Z31">
-        <v>0.42518909184060127</v>
+        <v>0.45321604354945533</v>
       </c>
     </row>
     <row r="32" spans="2:26">
@@ -9113,10 +9113,10 @@
         <v>473</v>
       </c>
       <c r="Y32">
-        <v>3.38625</v>
+        <v>98.024249999999995</v>
       </c>
       <c r="Z32">
-        <v>0.27397097122901398</v>
+        <v>0.48508660660688818</v>
       </c>
     </row>
     <row r="33" spans="2:26">
@@ -9181,10 +9181,10 @@
         <v>474</v>
       </c>
       <c r="Y33">
-        <v>30.597750000000001</v>
+        <v>28.459499999999998</v>
       </c>
       <c r="Z33">
-        <v>0.45321604354945533</v>
+        <v>0.46298928100882142</v>
       </c>
     </row>
     <row r="34" spans="2:26">
@@ -10192,7 +10192,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{857E82F3-DCCD-4BE9-99BE-185880BFC6FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01AD1CAD-2BAF-4F40-BA3C-C5B4B8FDE942}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
